--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -227,7 +227,7 @@
     <t xml:space="preserve">October Junior Competition Sixes</t>
   </si>
   <si>
-    <t xml:space="preserve">Frankie</t>
+    <t xml:space="preserve">Frankie Wright</t>
   </si>
   <si>
     <t xml:space="preserve">November 9 Hole</t>
@@ -3417,7 +3417,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="51" t="s">
         <v>73</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="I78" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J78" s="0"/>
+      <c r="J78" s="13"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="51" t="s">
@@ -3493,7 +3493,7 @@
       <c r="I79" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J79" s="0"/>
+      <c r="J79" s="13"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="51" t="s">
@@ -3519,7 +3519,7 @@
       <c r="I80" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J80" s="0"/>
+      <c r="J80" s="13"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="51" t="s">
@@ -3545,7 +3545,7 @@
       <c r="I81" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J81" s="0"/>
+      <c r="J81" s="13"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="51" t="s">
@@ -3571,7 +3571,7 @@
       <c r="I82" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J82" s="0"/>
+      <c r="J82" s="13"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="51" t="s">
@@ -3597,7 +3597,7 @@
       <c r="I83" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J83" s="0"/>
+      <c r="J83" s="13"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="51" t="s">
@@ -3623,7 +3623,7 @@
       <c r="I84" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J84" s="0"/>
+      <c r="J84" s="13"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="51" t="s">
@@ -3649,7 +3649,7 @@
       <c r="I85" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="J85" s="0"/>
+      <c r="J85" s="13"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="51" t="s">
@@ -3675,7 +3675,7 @@
       <c r="I86" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J86" s="0"/>
+      <c r="J86" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="51" t="s">
@@ -3701,7 +3701,7 @@
       <c r="I87" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J87" s="0"/>
+      <c r="J87" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I77"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -264,7 +264,7 @@
     <t>Eira Hooper</t>
   </si>
   <si>
-    <t>10 May 2026 | 13:00 - 14:00 Tee Times | Spring Round 1</t>
+    <t>10 May 2026 | 13:00 - 14:00 Tee Times | Spring Round 2</t>
   </si>
 </sst>
 </file>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="80">
   <si>
     <t>Name</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>10 May 2026 | 13:00 - 14:00 Tee Times | Spring Round 2</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
 </sst>
 </file>
@@ -919,7 +922,7 @@
     <col min="10" max="16384" width="10.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5">
+    <row r="1" spans="1:10" ht="16.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -947,8 +950,11 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="I2" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
@@ -997,8 +1006,11 @@
       <c r="I3" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
@@ -1022,8 +1034,11 @@
       <c r="I4" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -1047,8 +1062,11 @@
       <c r="I5" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1090,11 @@
       <c r="I6" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1097,8 +1118,11 @@
       <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1122,8 +1146,11 @@
       <c r="I8" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1147,8 +1174,11 @@
       <c r="I9" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1172,8 +1202,11 @@
       <c r="I10" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1197,8 +1230,11 @@
       <c r="I11" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1258,11 @@
       <c r="I12" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
@@ -1247,8 +1286,11 @@
       <c r="I13" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J13" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.5" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
@@ -1272,8 +1314,11 @@
       <c r="I14" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J14" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -1297,8 +1342,11 @@
       <c r="I15" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
@@ -1322,8 +1370,11 @@
       <c r="I16" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J16" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
@@ -1347,8 +1398,11 @@
       <c r="I17" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J17" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
@@ -1372,8 +1426,11 @@
       <c r="I18" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J18" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
@@ -1397,8 +1454,11 @@
       <c r="I19" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>34</v>
       </c>
@@ -1422,8 +1482,11 @@
       <c r="I20" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J20" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>35</v>
       </c>
@@ -1447,8 +1510,11 @@
       <c r="I21" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J21" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>38</v>
       </c>
@@ -1472,8 +1538,11 @@
       <c r="I22" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J22" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
         <v>25</v>
       </c>
@@ -1497,8 +1566,11 @@
       <c r="I23" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J23" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="A24" s="14" t="s">
         <v>12</v>
       </c>
@@ -1522,8 +1594,11 @@
       <c r="I24" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J24" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
         <v>32</v>
       </c>
@@ -1547,8 +1622,11 @@
       <c r="I25" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J25" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
         <v>34</v>
       </c>
@@ -1572,8 +1650,11 @@
       <c r="I26" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J26" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>35</v>
       </c>
@@ -1597,8 +1678,11 @@
       <c r="I27" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J27" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>18</v>
       </c>
@@ -1622,8 +1706,11 @@
       <c r="I28" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J28" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>38</v>
       </c>
@@ -1647,8 +1734,11 @@
       <c r="I29" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J29" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
         <v>25</v>
       </c>
@@ -1672,8 +1762,11 @@
       <c r="I30" s="20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J30" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
       <c r="A31" s="20" t="s">
         <v>41</v>
       </c>
@@ -1697,8 +1790,11 @@
       <c r="I31" s="20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J31" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
         <v>12</v>
       </c>
@@ -1722,8 +1818,11 @@
       <c r="I32" s="20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J32" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
         <v>15</v>
       </c>
@@ -1747,8 +1846,11 @@
       <c r="I33" s="23" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1">
+      <c r="J33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1">
       <c r="A34" s="23" t="s">
         <v>44</v>
       </c>
@@ -1772,8 +1874,11 @@
       <c r="I34" s="23" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="15" customHeight="1">
+      <c r="J34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
         <v>25</v>
       </c>
@@ -1797,8 +1902,11 @@
       <c r="I35" s="29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" customHeight="1">
+      <c r="J35" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
         <v>41</v>
       </c>
@@ -1822,8 +1930,11 @@
       <c r="I36" s="29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" customHeight="1">
+      <c r="J36" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
         <v>32</v>
       </c>
@@ -1847,8 +1958,11 @@
       <c r="I37" s="29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" customHeight="1">
+      <c r="J37" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
@@ -1872,8 +1986,11 @@
       <c r="I38" s="29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" customHeight="1">
+      <c r="J38" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" customHeight="1">
       <c r="A39" s="26" t="s">
         <v>9</v>
       </c>
@@ -1897,8 +2014,11 @@
       <c r="I39" s="29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" customHeight="1">
+      <c r="J39" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1">
       <c r="A40" s="30" t="s">
         <v>46</v>
       </c>
@@ -1922,8 +2042,11 @@
       <c r="I40" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" customHeight="1">
+      <c r="J40" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
         <v>35</v>
       </c>
@@ -1947,8 +2070,11 @@
       <c r="I41" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="15" customHeight="1">
+      <c r="J41" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
         <v>44</v>
       </c>
@@ -1972,8 +2098,11 @@
       <c r="I42" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1">
+      <c r="J42" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1">
       <c r="A43" s="32" t="s">
         <v>49</v>
       </c>
@@ -1997,8 +2126,11 @@
       <c r="I43" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="15" customHeight="1">
+      <c r="J43" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
         <v>50</v>
       </c>
@@ -2022,8 +2154,11 @@
       <c r="I44" s="32" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" customHeight="1">
+      <c r="J44" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
         <v>30</v>
       </c>
@@ -2047,8 +2182,11 @@
       <c r="I45" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" customHeight="1">
+      <c r="J45" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
         <v>12</v>
       </c>
@@ -2072,8 +2210,11 @@
       <c r="I46" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" customHeight="1">
+      <c r="J46" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
         <v>31</v>
       </c>
@@ -2097,8 +2238,11 @@
       <c r="I47" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" customHeight="1">
+      <c r="J47" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
         <v>46</v>
       </c>
@@ -2122,8 +2266,11 @@
       <c r="I48" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1">
+      <c r="J48" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
         <v>15</v>
       </c>
@@ -2147,8 +2294,11 @@
       <c r="I49" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1">
+      <c r="J49" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
         <v>44</v>
       </c>
@@ -2172,8 +2322,11 @@
       <c r="I50" s="17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" ht="15" customHeight="1">
+      <c r="J50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
         <v>32</v>
       </c>
@@ -2197,8 +2350,11 @@
       <c r="I51" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1">
+      <c r="J51" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
         <v>35</v>
       </c>
@@ -2222,8 +2378,11 @@
       <c r="I52" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1">
+      <c r="J52" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" customHeight="1">
       <c r="A53" s="34" t="s">
         <v>56</v>
       </c>
@@ -2247,8 +2406,11 @@
       <c r="I53" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1">
+      <c r="J53" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
         <v>57</v>
       </c>
@@ -2272,8 +2434,11 @@
       <c r="I54" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1">
+      <c r="J54" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
         <v>58</v>
       </c>
@@ -2297,8 +2462,11 @@
       <c r="I55" s="34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1">
+      <c r="J55" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
         <v>25</v>
       </c>
@@ -2322,8 +2490,11 @@
       <c r="I56" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" ht="15" customHeight="1">
+      <c r="J56" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
         <v>32</v>
       </c>
@@ -2347,8 +2518,11 @@
       <c r="I57" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1">
+      <c r="J57" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
         <v>12</v>
       </c>
@@ -2372,8 +2546,11 @@
       <c r="I58" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1">
+      <c r="J58" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
         <v>30</v>
       </c>
@@ -2397,8 +2574,11 @@
       <c r="I59" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1">
+      <c r="J59" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
         <v>31</v>
       </c>
@@ -2422,8 +2602,11 @@
       <c r="I60" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1">
+      <c r="J60" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
         <v>44</v>
       </c>
@@ -2447,8 +2630,11 @@
       <c r="I61" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" ht="15" customHeight="1">
+      <c r="J61" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
         <v>46</v>
       </c>
@@ -2472,8 +2658,11 @@
       <c r="I62" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1">
+      <c r="J62" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
         <v>49</v>
       </c>
@@ -2497,8 +2686,11 @@
       <c r="I63" s="37" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="15" customHeight="1">
+      <c r="J63" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
         <v>35</v>
       </c>
@@ -2522,6 +2714,9 @@
       <c r="I64" s="39" t="s">
         <v>63</v>
       </c>
+      <c r="J64" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="39" t="s">
@@ -2547,6 +2742,9 @@
       <c r="I65" s="39" t="s">
         <v>63</v>
       </c>
+      <c r="J65" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
@@ -2572,6 +2770,9 @@
       <c r="I66" s="39" t="s">
         <v>63</v>
       </c>
+      <c r="J66" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
@@ -2597,6 +2798,9 @@
       <c r="I67" s="39" t="s">
         <v>63</v>
       </c>
+      <c r="J67" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="41" t="s">
@@ -2622,6 +2826,9 @@
       <c r="I68" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J68" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="41" t="s">
@@ -2647,6 +2854,9 @@
       <c r="I69" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J69" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="41" t="s">
@@ -2672,6 +2882,9 @@
       <c r="I70" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J70" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="41" t="s">
@@ -2697,6 +2910,9 @@
       <c r="I71" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J71" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="41" t="s">
@@ -2722,6 +2938,9 @@
       <c r="I72" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J72" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="41" t="s">
@@ -2747,6 +2966,9 @@
       <c r="I73" s="41" t="s">
         <v>67</v>
       </c>
+      <c r="J73" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="43" t="s">
@@ -2772,6 +2994,9 @@
       <c r="I74" s="43" t="s">
         <v>69</v>
       </c>
+      <c r="J74" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="43" t="s">
@@ -2797,6 +3022,9 @@
       <c r="I75" s="43" t="s">
         <v>69</v>
       </c>
+      <c r="J75" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="43" t="s">
@@ -2821,6 +3049,9 @@
       </c>
       <c r="I76" s="43" t="s">
         <v>69</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3117,7 +3348,7 @@
   </sheetData>
   <autoFilter ref="A1:I86"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -252,9 +252,6 @@
     <t>Current Season</t>
   </si>
   <si>
-    <t>✅</t>
-  </si>
-  <si>
     <t>Mason Tubb</t>
   </si>
   <si>
@@ -268,6 +265,9 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -951,7 +951,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -979,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1007,7 +1007,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1035,7 +1035,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1063,7 +1063,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1091,7 +1091,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1147,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1175,7 +1175,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1203,7 +1203,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1231,7 +1231,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1259,7 +1259,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1287,7 +1287,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1">
@@ -1315,7 +1315,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1">
@@ -1343,7 +1343,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1">
@@ -1371,7 +1371,7 @@
         <v>28</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
@@ -1399,7 +1399,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
@@ -1427,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1">
@@ -1455,7 +1455,7 @@
         <v>28</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
@@ -1483,7 +1483,7 @@
         <v>28</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
@@ -1511,7 +1511,7 @@
         <v>37</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1">
@@ -1539,7 +1539,7 @@
         <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
@@ -1567,7 +1567,7 @@
         <v>11</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
@@ -1595,7 +1595,7 @@
         <v>11</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1">
@@ -1623,7 +1623,7 @@
         <v>11</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
@@ -1651,7 +1651,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1">
@@ -1679,7 +1679,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
@@ -1707,7 +1707,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1">
@@ -1735,7 +1735,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
@@ -1763,7 +1763,7 @@
         <v>21</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
@@ -1791,7 +1791,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
@@ -1819,7 +1819,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1">
@@ -1847,7 +1847,7 @@
         <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1">
@@ -1875,7 +1875,7 @@
         <v>43</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
@@ -1903,7 +1903,7 @@
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
@@ -1931,7 +1931,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
@@ -1959,7 +1959,7 @@
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1">
@@ -1987,7 +1987,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1">
@@ -2015,7 +2015,7 @@
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1">
@@ -2043,7 +2043,7 @@
         <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1">
@@ -2071,7 +2071,7 @@
         <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1">
@@ -2099,7 +2099,7 @@
         <v>48</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1">
@@ -2127,7 +2127,7 @@
         <v>48</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1">
@@ -2155,7 +2155,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
@@ -2183,7 +2183,7 @@
         <v>53</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1">
@@ -2211,7 +2211,7 @@
         <v>53</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1">
@@ -2239,7 +2239,7 @@
         <v>53</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1">
@@ -2267,7 +2267,7 @@
         <v>53</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1">
@@ -2295,7 +2295,7 @@
         <v>53</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1">
@@ -2351,7 +2351,7 @@
         <v>55</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1">
@@ -2379,7 +2379,7 @@
         <v>55</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1">
@@ -2407,7 +2407,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1">
@@ -2435,7 +2435,7 @@
         <v>55</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1">
@@ -2463,7 +2463,7 @@
         <v>55</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1">
@@ -2491,7 +2491,7 @@
         <v>61</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1">
@@ -2519,7 +2519,7 @@
         <v>61</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1">
@@ -2547,7 +2547,7 @@
         <v>61</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1">
@@ -2575,7 +2575,7 @@
         <v>61</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1">
@@ -2603,7 +2603,7 @@
         <v>61</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1">
@@ -2631,7 +2631,7 @@
         <v>61</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1">
@@ -2659,7 +2659,7 @@
         <v>61</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1">
@@ -2687,7 +2687,7 @@
         <v>61</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
@@ -2715,7 +2715,7 @@
         <v>63</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1">
@@ -2743,7 +2743,7 @@
         <v>63</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
@@ -2771,7 +2771,7 @@
         <v>63</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
@@ -2799,7 +2799,7 @@
         <v>63</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2827,7 +2827,7 @@
         <v>67</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2855,7 +2855,7 @@
         <v>67</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2883,7 +2883,7 @@
         <v>67</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2911,7 +2911,7 @@
         <v>67</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2939,7 +2939,7 @@
         <v>67</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2967,7 +2967,7 @@
         <v>67</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2995,7 +2995,7 @@
         <v>69</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3023,7 +3023,7 @@
         <v>69</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3051,7 +3051,7 @@
         <v>69</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3079,7 +3079,7 @@
         <v>28</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3107,7 +3107,7 @@
         <v>28</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3135,7 +3135,7 @@
         <v>28</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3163,12 +3163,12 @@
         <v>28</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B81" s="45">
         <v>54</v>
@@ -3191,7 +3191,7 @@
         <v>37</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3219,7 +3219,7 @@
         <v>37</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3247,12 +3247,12 @@
         <v>37</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B84" s="45">
         <v>50</v>
@@ -3275,12 +3275,12 @@
         <v>37</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" s="45">
         <v>46</v>
@@ -3303,7 +3303,7 @@
         <v>37</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3331,7 +3331,7 @@
         <v>37</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="48" customFormat="1"/>
@@ -3388,7 +3388,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3084,7 +3084,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B78" s="45">
         <v>42</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B79" s="45">
         <v>53</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -268,6 +268,18 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>May Sixes</t>
+  </si>
+  <si>
+    <t>May Junior Competition Sixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issac Hibbert </t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -539,7 +551,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -631,6 +643,8 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="60% - Accent1 2" xfId="1"/>
@@ -912,11 +926,11 @@
   <cols>
     <col min="1" max="1" width="22.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" style="2" customWidth="1"/>
     <col min="9" max="9" width="38.90625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="10.1796875" style="1"/>
@@ -1035,7 +1049,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1063,7 +1077,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1091,7 +1105,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1119,7 +1133,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1147,7 +1161,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1203,7 +1217,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1259,7 +1273,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1315,7 +1329,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1">
@@ -1455,7 +1469,7 @@
         <v>28</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
@@ -1539,7 +1553,7 @@
         <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
@@ -1735,7 +1749,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
@@ -1791,7 +1805,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
@@ -1847,7 +1861,7 @@
         <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1">
@@ -1931,7 +1945,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
@@ -2155,7 +2169,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
@@ -2295,7 +2309,7 @@
         <v>53</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
@@ -2463,7 +2477,7 @@
         <v>55</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1">
@@ -2743,7 +2757,7 @@
         <v>63</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
@@ -2771,7 +2785,7 @@
         <v>63</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
@@ -2883,7 +2897,7 @@
         <v>67</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3334,10 +3348,98 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="48" customFormat="1"/>
-    <row r="88" spans="1:10" s="48" customFormat="1"/>
-    <row r="89" spans="1:10" s="48" customFormat="1"/>
-    <row r="90" spans="1:10" s="48" customFormat="1"/>
+    <row r="87" spans="1:10" s="48" customFormat="1">
+      <c r="A87" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B87" s="53">
+        <v>27</v>
+      </c>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G87" s="53"/>
+      <c r="H87" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I87" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J87" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="48" customFormat="1">
+      <c r="A88" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B88" s="53">
+        <v>32</v>
+      </c>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G88" s="53"/>
+      <c r="H88" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I88" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J88" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="48" customFormat="1">
+      <c r="A89" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="B89" s="53"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G89" s="53"/>
+      <c r="H89" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I89" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J89" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="48" customFormat="1">
+      <c r="A90" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B90" s="53"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G90" s="53"/>
+      <c r="H90" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I90" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J90" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="91" spans="1:10" s="48" customFormat="1"/>
     <row r="92" spans="1:10" s="48" customFormat="1"/>
     <row r="93" spans="1:10" s="48" customFormat="1"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$90</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -921,6 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J97"/>
   <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14"/>
   <cols>
@@ -993,10 +994,10 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
@@ -1024,7 +1025,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
@@ -1052,7 +1053,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -1080,7 +1081,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1108,7 +1109,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1164,7 +1165,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" hidden="1">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1192,7 +1193,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1221,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
@@ -1304,7 +1305,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.5" customHeight="1">
+    <row r="14" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
@@ -1332,7 +1333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.5" customHeight="1">
+    <row r="15" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -1360,7 +1361,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.5" customHeight="1">
+    <row r="16" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
@@ -1388,7 +1389,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1">
+    <row r="18" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
@@ -1444,7 +1445,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1">
+    <row r="19" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+    <row r="20" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>34</v>
       </c>
@@ -1500,7 +1501,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+    <row r="21" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>35</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+    <row r="22" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>38</v>
       </c>
@@ -1556,7 +1557,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+    <row r="23" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A23" s="14" t="s">
         <v>25</v>
       </c>
@@ -1584,7 +1585,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1">
+    <row r="24" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A24" s="14" t="s">
         <v>12</v>
       </c>
@@ -1612,7 +1613,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+    <row r="25" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A25" s="14" t="s">
         <v>32</v>
       </c>
@@ -1640,7 +1641,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+    <row r="26" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A26" s="14" t="s">
         <v>34</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+    <row r="27" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>35</v>
       </c>
@@ -1696,7 +1697,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+    <row r="28" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>18</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>38</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+    <row r="30" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A30" s="20" t="s">
         <v>25</v>
       </c>
@@ -1780,7 +1781,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+    <row r="31" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A31" s="20" t="s">
         <v>41</v>
       </c>
@@ -1808,7 +1809,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+    <row r="32" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A32" s="20" t="s">
         <v>12</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+    <row r="33" spans="1:10" ht="13.5" hidden="1" customHeight="1">
       <c r="A33" s="23" t="s">
         <v>15</v>
       </c>
@@ -1864,7 +1865,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1">
+    <row r="34" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A34" s="23" t="s">
         <v>44</v>
       </c>
@@ -1892,7 +1893,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1">
+    <row r="35" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A35" s="26" t="s">
         <v>25</v>
       </c>
@@ -1920,7 +1921,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1">
+    <row r="36" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A36" s="26" t="s">
         <v>41</v>
       </c>
@@ -1948,7 +1949,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1">
+    <row r="37" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A37" s="26" t="s">
         <v>32</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1">
+    <row r="38" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
@@ -2029,10 +2030,10 @@
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A40" s="30" t="s">
         <v>46</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1">
+    <row r="41" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A41" s="32" t="s">
         <v>35</v>
       </c>
@@ -2088,7 +2089,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1">
+    <row r="42" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A42" s="32" t="s">
         <v>44</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1">
+    <row r="43" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A43" s="32" t="s">
         <v>49</v>
       </c>
@@ -2144,7 +2145,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1">
+    <row r="44" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A44" s="32" t="s">
         <v>50</v>
       </c>
@@ -2172,7 +2173,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1">
+    <row r="45" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A45" s="17" t="s">
         <v>30</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1">
+    <row r="46" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A46" s="17" t="s">
         <v>12</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1">
+    <row r="47" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A47" s="17" t="s">
         <v>31</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1">
+    <row r="48" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A48" s="17" t="s">
         <v>46</v>
       </c>
@@ -2284,7 +2285,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1">
+    <row r="49" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A49" s="17" t="s">
         <v>15</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1">
+    <row r="50" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A50" s="17" t="s">
         <v>44</v>
       </c>
@@ -2340,7 +2341,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1">
+    <row r="51" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A51" s="34" t="s">
         <v>32</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1">
+    <row r="52" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A52" s="34" t="s">
         <v>35</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1">
+    <row r="53" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A53" s="34" t="s">
         <v>56</v>
       </c>
@@ -2424,7 +2425,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1">
+    <row r="54" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A54" s="34" t="s">
         <v>57</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1">
+    <row r="55" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A55" s="34" t="s">
         <v>58</v>
       </c>
@@ -2480,7 +2481,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1">
+    <row r="56" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A56" s="37" t="s">
         <v>25</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1">
+    <row r="57" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A57" s="37" t="s">
         <v>32</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1">
+    <row r="58" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A58" s="37" t="s">
         <v>12</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1">
+    <row r="59" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A59" s="37" t="s">
         <v>30</v>
       </c>
@@ -2592,7 +2593,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1">
+    <row r="60" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A60" s="37" t="s">
         <v>31</v>
       </c>
@@ -2620,7 +2621,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1">
+    <row r="61" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A61" s="37" t="s">
         <v>44</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1">
+    <row r="62" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A62" s="37" t="s">
         <v>46</v>
       </c>
@@ -2676,7 +2677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1">
+    <row r="63" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A63" s="37" t="s">
         <v>49</v>
       </c>
@@ -2704,7 +2705,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1">
+    <row r="64" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A64" s="39" t="s">
         <v>35</v>
       </c>
@@ -2732,7 +2733,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1">
+    <row r="65" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A65" s="39" t="s">
         <v>64</v>
       </c>
@@ -2760,7 +2761,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1">
+    <row r="66" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A66" s="39" t="s">
         <v>58</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1">
+    <row r="67" spans="1:10" ht="15" hidden="1" customHeight="1">
       <c r="A67" s="39" t="s">
         <v>57</v>
       </c>
@@ -2816,7 +2817,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="41" t="s">
         <v>25</v>
       </c>
@@ -2844,7 +2845,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="41" t="s">
         <v>30</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="41" t="s">
         <v>29</v>
       </c>
@@ -2900,7 +2901,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="41" t="s">
         <v>31</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" hidden="1">
       <c r="A72" s="41" t="s">
         <v>12</v>
       </c>
@@ -2956,7 +2957,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="41" t="s">
         <v>44</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="43" t="s">
         <v>35</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="43" t="s">
         <v>32</v>
       </c>
@@ -3040,7 +3041,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="43" t="s">
         <v>56</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="45" t="s">
         <v>25</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="45" t="s">
         <v>30</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="45" t="s">
         <v>31</v>
       </c>
@@ -3152,7 +3153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="45" t="s">
         <v>44</v>
       </c>
@@ -3180,7 +3181,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="45" t="s">
         <v>74</v>
       </c>
@@ -3208,7 +3209,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="45" t="s">
         <v>32</v>
       </c>
@@ -3236,7 +3237,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="45" t="s">
         <v>35</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="45" t="s">
         <v>75</v>
       </c>
@@ -3292,7 +3293,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="45" t="s">
         <v>76</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="45" t="s">
         <v>57</v>
       </c>
@@ -3348,7 +3349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="48" customFormat="1">
+    <row r="87" spans="1:10" s="48" customFormat="1" hidden="1">
       <c r="A87" s="53" t="s">
         <v>32</v>
       </c>
@@ -3372,7 +3373,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="48" customFormat="1">
+    <row r="88" spans="1:10" s="48" customFormat="1" hidden="1">
       <c r="A88" s="53" t="s">
         <v>35</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="48" customFormat="1">
+    <row r="89" spans="1:10" s="48" customFormat="1" hidden="1">
       <c r="A89" s="53" t="s">
         <v>74</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="48" customFormat="1">
+    <row r="90" spans="1:10" s="48" customFormat="1" hidden="1">
       <c r="A90" s="53" t="s">
         <v>82</v>
       </c>
@@ -3448,7 +3449,13 @@
     <row r="96" spans="1:10" s="48" customFormat="1"/>
     <row r="97" s="48" customFormat="1"/>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
+  <autoFilter ref="A1:I90">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="William Whitehead"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -280,6 +280,15 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>Leo Hall</t>
+  </si>
+  <si>
+    <t>May 9 Hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May Junior Competition </t>
   </si>
 </sst>
 </file>
@@ -344,7 +353,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +498,12 @@
         <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -551,7 +566,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -645,6 +660,8 @@
     <xf numFmtId="49" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="4" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="60% - Accent1 2" xfId="1"/>
@@ -921,20 +938,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J97"/>
-  <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14"/>
+  <dimension ref="A1:J105"/>
+  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="38.90625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.1796875" style="1"/>
+    <col min="7" max="7" width="1.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="38.85546875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5">
@@ -997,7 +1013,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1">
+    <row r="3" spans="1:10">
       <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
@@ -1025,7 +1041,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
@@ -1053,7 +1069,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1">
+    <row r="5" spans="1:10">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -1081,7 +1097,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1109,7 +1125,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1">
+    <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1137,7 +1153,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1">
+    <row r="8" spans="1:10">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1165,7 +1181,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1193,7 +1209,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1221,7 +1237,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1277,7 +1293,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1">
+    <row r="13" spans="1:10">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
@@ -1305,7 +1321,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:10" ht="13.5" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
@@ -1333,7 +1349,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:10" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -1361,7 +1377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:10" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
@@ -1389,7 +1405,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
@@ -1417,7 +1433,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
@@ -1445,7 +1461,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
@@ -1473,7 +1489,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>34</v>
       </c>
@@ -1501,7 +1517,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>35</v>
       </c>
@@ -1529,7 +1545,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>38</v>
       </c>
@@ -1557,7 +1573,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
         <v>25</v>
       </c>
@@ -1585,7 +1601,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="A24" s="14" t="s">
         <v>12</v>
       </c>
@@ -1613,7 +1629,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
         <v>32</v>
       </c>
@@ -1641,7 +1657,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
         <v>34</v>
       </c>
@@ -1669,7 +1685,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
       <c r="A27" s="17" t="s">
         <v>35</v>
       </c>
@@ -1697,7 +1713,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="17" t="s">
         <v>18</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>38</v>
       </c>
@@ -1753,7 +1769,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
         <v>25</v>
       </c>
@@ -1781,7 +1797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
       <c r="A31" s="20" t="s">
         <v>41</v>
       </c>
@@ -1809,7 +1825,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
         <v>12</v>
       </c>
@@ -1837,7 +1853,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="13.5" hidden="1" customHeight="1">
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
         <v>15</v>
       </c>
@@ -1865,7 +1881,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="34" spans="1:10" ht="15" customHeight="1">
       <c r="A34" s="23" t="s">
         <v>44</v>
       </c>
@@ -1893,7 +1909,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="35" spans="1:10" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
         <v>25</v>
       </c>
@@ -1921,7 +1937,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="36" spans="1:10" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
         <v>41</v>
       </c>
@@ -1949,7 +1965,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="37" spans="1:10" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
         <v>32</v>
       </c>
@@ -1977,7 +1993,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="38" spans="1:10" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2049,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="40" spans="1:10" ht="15" customHeight="1">
       <c r="A40" s="30" t="s">
         <v>46</v>
       </c>
@@ -2061,7 +2077,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="41" spans="1:10" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
         <v>35</v>
       </c>
@@ -2089,7 +2105,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="42" spans="1:10" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
         <v>44</v>
       </c>
@@ -2117,7 +2133,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="43" spans="1:10" ht="15" customHeight="1">
       <c r="A43" s="32" t="s">
         <v>49</v>
       </c>
@@ -2145,7 +2161,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
         <v>50</v>
       </c>
@@ -2173,7 +2189,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
         <v>30</v>
       </c>
@@ -2201,7 +2217,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="46" spans="1:10" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
         <v>12</v>
       </c>
@@ -2229,7 +2245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="47" spans="1:10" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
         <v>31</v>
       </c>
@@ -2257,7 +2273,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="48" spans="1:10" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
         <v>46</v>
       </c>
@@ -2285,7 +2301,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="49" spans="1:10" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
         <v>15</v>
       </c>
@@ -2313,7 +2329,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="50" spans="1:10" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
         <v>44</v>
       </c>
@@ -2341,7 +2357,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="51" spans="1:10" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
         <v>32</v>
       </c>
@@ -2369,7 +2385,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="52" spans="1:10" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
         <v>35</v>
       </c>
@@ -2397,7 +2413,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="53" spans="1:10" ht="15" customHeight="1">
       <c r="A53" s="34" t="s">
         <v>56</v>
       </c>
@@ -2425,7 +2441,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="54" spans="1:10" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
         <v>57</v>
       </c>
@@ -2453,7 +2469,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="55" spans="1:10" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
         <v>58</v>
       </c>
@@ -2478,10 +2494,10 @@
         <v>55</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15" hidden="1" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
         <v>25</v>
       </c>
@@ -2509,7 +2525,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
         <v>32</v>
       </c>
@@ -2537,7 +2553,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
         <v>12</v>
       </c>
@@ -2565,7 +2581,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
         <v>30</v>
       </c>
@@ -2593,7 +2609,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
         <v>31</v>
       </c>
@@ -2621,7 +2637,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
         <v>44</v>
       </c>
@@ -2649,7 +2665,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
         <v>46</v>
       </c>
@@ -2677,7 +2693,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
         <v>49</v>
       </c>
@@ -2705,7 +2721,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
         <v>35</v>
       </c>
@@ -2733,7 +2749,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="39" t="s">
         <v>64</v>
       </c>
@@ -2761,7 +2777,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15" hidden="1" customHeight="1">
+    <row r="66" spans="1:10" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
         <v>58</v>
       </c>
@@ -2786,10 +2802,10 @@
         <v>63</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="15" hidden="1" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
         <v>57</v>
       </c>
@@ -2817,7 +2833,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1">
+    <row r="68" spans="1:10">
       <c r="A68" s="41" t="s">
         <v>25</v>
       </c>
@@ -2845,7 +2861,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1">
+    <row r="69" spans="1:10">
       <c r="A69" s="41" t="s">
         <v>30</v>
       </c>
@@ -2873,7 +2889,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1">
+    <row r="70" spans="1:10">
       <c r="A70" s="41" t="s">
         <v>29</v>
       </c>
@@ -2901,7 +2917,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1">
+    <row r="71" spans="1:10">
       <c r="A71" s="41" t="s">
         <v>31</v>
       </c>
@@ -2929,7 +2945,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1">
+    <row r="72" spans="1:10">
       <c r="A72" s="41" t="s">
         <v>12</v>
       </c>
@@ -2957,7 +2973,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1">
+    <row r="73" spans="1:10">
       <c r="A73" s="41" t="s">
         <v>44</v>
       </c>
@@ -2985,7 +3001,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10">
       <c r="A74" s="43" t="s">
         <v>35</v>
       </c>
@@ -3013,7 +3029,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10">
       <c r="A75" s="43" t="s">
         <v>32</v>
       </c>
@@ -3041,7 +3057,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10">
       <c r="A76" s="43" t="s">
         <v>56</v>
       </c>
@@ -3069,7 +3085,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1">
+    <row r="77" spans="1:10">
       <c r="A77" s="45" t="s">
         <v>25</v>
       </c>
@@ -3097,7 +3113,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1">
+    <row r="78" spans="1:10">
       <c r="A78" s="45" t="s">
         <v>30</v>
       </c>
@@ -3125,7 +3141,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1">
+    <row r="79" spans="1:10">
       <c r="A79" s="45" t="s">
         <v>31</v>
       </c>
@@ -3153,7 +3169,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1">
+    <row r="80" spans="1:10">
       <c r="A80" s="45" t="s">
         <v>44</v>
       </c>
@@ -3181,7 +3197,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1">
+    <row r="81" spans="1:10">
       <c r="A81" s="45" t="s">
         <v>74</v>
       </c>
@@ -3209,7 +3225,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1">
+    <row r="82" spans="1:10">
       <c r="A82" s="45" t="s">
         <v>32</v>
       </c>
@@ -3237,7 +3253,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1">
+    <row r="83" spans="1:10">
       <c r="A83" s="45" t="s">
         <v>35</v>
       </c>
@@ -3265,7 +3281,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10">
       <c r="A84" s="45" t="s">
         <v>75</v>
       </c>
@@ -3293,7 +3309,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10">
       <c r="A85" s="45" t="s">
         <v>76</v>
       </c>
@@ -3321,7 +3337,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10">
       <c r="A86" s="45" t="s">
         <v>57</v>
       </c>
@@ -3349,113 +3365,444 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="48" customFormat="1" hidden="1">
-      <c r="A87" s="53" t="s">
+    <row r="87" spans="1:10" s="48" customFormat="1">
+      <c r="A87" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="53">
+      <c r="B87" s="55">
         <v>27</v>
       </c>
-      <c r="C87" s="53"/>
-      <c r="D87" s="53"/>
-      <c r="E87" s="53"/>
-      <c r="F87" s="53" t="s">
+      <c r="C87" s="55"/>
+      <c r="D87" s="55">
+        <v>1</v>
+      </c>
+      <c r="E87" s="55">
+        <v>10</v>
+      </c>
+      <c r="F87" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="G87" s="53"/>
-      <c r="H87" s="54">
+      <c r="G87" s="55"/>
+      <c r="H87" s="56">
         <v>46152</v>
       </c>
-      <c r="I87" s="53" t="s">
+      <c r="I87" s="55" t="s">
         <v>81</v>
       </c>
       <c r="J87" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="48" customFormat="1" hidden="1">
-      <c r="A88" s="53" t="s">
+    <row r="88" spans="1:10" s="48" customFormat="1">
+      <c r="A88" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B88" s="53">
+      <c r="B88" s="55">
         <v>32</v>
       </c>
-      <c r="C88" s="53"/>
-      <c r="D88" s="53"/>
-      <c r="E88" s="53"/>
-      <c r="F88" s="53" t="s">
+      <c r="C88" s="55"/>
+      <c r="D88" s="55">
+        <v>2</v>
+      </c>
+      <c r="E88" s="55">
+        <v>9</v>
+      </c>
+      <c r="F88" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="G88" s="53"/>
-      <c r="H88" s="54">
+      <c r="G88" s="55"/>
+      <c r="H88" s="56">
         <v>46152</v>
       </c>
-      <c r="I88" s="53" t="s">
+      <c r="I88" s="55" t="s">
         <v>81</v>
       </c>
       <c r="J88" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="48" customFormat="1" hidden="1">
-      <c r="A89" s="53" t="s">
+    <row r="89" spans="1:10" s="48" customFormat="1">
+      <c r="A89" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="B89" s="53"/>
-      <c r="C89" s="53"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53" t="s">
+      <c r="B89" s="55">
+        <v>37</v>
+      </c>
+      <c r="C89" s="55"/>
+      <c r="D89" s="55">
+        <v>4</v>
+      </c>
+      <c r="E89" s="55">
+        <v>7</v>
+      </c>
+      <c r="F89" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="G89" s="53"/>
-      <c r="H89" s="54">
+      <c r="G89" s="55"/>
+      <c r="H89" s="56">
         <v>46152</v>
       </c>
-      <c r="I89" s="53" t="s">
+      <c r="I89" s="55" t="s">
         <v>81</v>
       </c>
       <c r="J89" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="48" customFormat="1" hidden="1">
-      <c r="A90" s="53" t="s">
+    <row r="90" spans="1:10" s="48" customFormat="1">
+      <c r="A90" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="B90" s="53"/>
-      <c r="C90" s="53"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53" t="s">
+      <c r="B90" s="55">
+        <v>49</v>
+      </c>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55">
+        <v>9</v>
+      </c>
+      <c r="E90" s="55">
+        <v>3</v>
+      </c>
+      <c r="F90" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="G90" s="53"/>
-      <c r="H90" s="54">
+      <c r="G90" s="55"/>
+      <c r="H90" s="56">
         <v>46152</v>
       </c>
-      <c r="I90" s="53" t="s">
+      <c r="I90" s="55" t="s">
         <v>81</v>
       </c>
       <c r="J90" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="48" customFormat="1"/>
-    <row r="92" spans="1:10" s="48" customFormat="1"/>
-    <row r="93" spans="1:10" s="48" customFormat="1"/>
-    <row r="94" spans="1:10" s="48" customFormat="1"/>
-    <row r="95" spans="1:10" s="48" customFormat="1"/>
-    <row r="96" spans="1:10" s="48" customFormat="1"/>
-    <row r="97" s="48" customFormat="1"/>
+    <row r="91" spans="1:10" s="48" customFormat="1">
+      <c r="A91" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" s="55">
+        <v>38</v>
+      </c>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55">
+        <v>3</v>
+      </c>
+      <c r="E91" s="55">
+        <v>8</v>
+      </c>
+      <c r="F91" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G91" s="55"/>
+      <c r="H91" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I91" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J91" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="48" customFormat="1">
+      <c r="A92" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="55">
+        <v>44</v>
+      </c>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55">
+        <v>5</v>
+      </c>
+      <c r="E92" s="55">
+        <v>7</v>
+      </c>
+      <c r="F92" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G92" s="55"/>
+      <c r="H92" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I92" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J92" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" s="48" customFormat="1">
+      <c r="A93" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" s="55">
+        <v>46</v>
+      </c>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55">
+        <v>6</v>
+      </c>
+      <c r="E93" s="55">
+        <v>6</v>
+      </c>
+      <c r="F93" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G93" s="55"/>
+      <c r="H93" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I93" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J93" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" s="48" customFormat="1">
+      <c r="A94" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" s="55">
+        <v>46</v>
+      </c>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55">
+        <v>7</v>
+      </c>
+      <c r="E94" s="55">
+        <v>5</v>
+      </c>
+      <c r="F94" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G94" s="55"/>
+      <c r="H94" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I94" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J94" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" s="48" customFormat="1">
+      <c r="A95" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95" s="55">
+        <v>46</v>
+      </c>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55">
+        <v>8</v>
+      </c>
+      <c r="E95" s="55">
+        <v>4</v>
+      </c>
+      <c r="F95" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G95" s="55"/>
+      <c r="H95" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I95" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J95" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" s="48" customFormat="1">
+      <c r="A96" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" s="55">
+        <v>46</v>
+      </c>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55">
+        <v>1</v>
+      </c>
+      <c r="E96" s="55">
+        <v>10</v>
+      </c>
+      <c r="F96" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G96" s="55"/>
+      <c r="H96" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I96" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="J96" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" s="48" customFormat="1">
+      <c r="A97" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" s="55">
+        <v>48</v>
+      </c>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55">
+        <v>2</v>
+      </c>
+      <c r="E97" s="55">
+        <v>9</v>
+      </c>
+      <c r="F97" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G97" s="55"/>
+      <c r="H97" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I97" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J97" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" s="55">
+        <v>53</v>
+      </c>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55">
+        <v>3</v>
+      </c>
+      <c r="E98" s="55">
+        <v>8</v>
+      </c>
+      <c r="F98" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G98" s="55"/>
+      <c r="H98" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I98" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J98" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B99" s="55">
+        <v>72</v>
+      </c>
+      <c r="C99" s="55"/>
+      <c r="D99" s="55">
+        <v>4</v>
+      </c>
+      <c r="E99" s="55">
+        <v>7</v>
+      </c>
+      <c r="F99" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G99" s="55"/>
+      <c r="H99" s="56">
+        <v>46152</v>
+      </c>
+      <c r="I99" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="53"/>
+      <c r="B100" s="53"/>
+      <c r="C100" s="53"/>
+      <c r="D100" s="53"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
+      <c r="H100" s="54"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="48"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="53"/>
+      <c r="B101" s="53"/>
+      <c r="C101" s="53"/>
+      <c r="D101" s="53"/>
+      <c r="E101" s="53"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53"/>
+      <c r="H101" s="54"/>
+      <c r="I101" s="53"/>
+      <c r="J101" s="48"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="53"/>
+      <c r="B102" s="53"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="53"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="54"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="48"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="53"/>
+      <c r="B103" s="53"/>
+      <c r="C103" s="53"/>
+      <c r="D103" s="53"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="54"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="48"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="53"/>
+      <c r="B104" s="53"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="54"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="48"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="53"/>
+      <c r="B105" s="53"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="53"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="54"/>
+      <c r="I105" s="53"/>
+      <c r="J105" s="48"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I90">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="William Whitehead"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I90"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -3467,11 +3814,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.453125" style="49" customWidth="1"/>
-    <col min="2" max="2" width="60.453125" style="49" customWidth="1"/>
-    <col min="3" max="16384" width="10.1796875" style="49"/>
+    <col min="1" max="1" width="21.42578125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="60.42578125" style="49" customWidth="1"/>
+    <col min="3" max="16384" width="10.140625" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1">

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$99</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -255,9 +255,6 @@
     <t>Mason Tubb</t>
   </si>
   <si>
-    <t>Mollie McMinn</t>
-  </si>
-  <si>
     <t>Eira Hooper</t>
   </si>
   <si>
@@ -289,6 +286,9 @@
   </si>
   <si>
     <t xml:space="preserve">May Junior Competition </t>
+  </si>
+  <si>
+    <t>Mollie Williams</t>
   </si>
 </sst>
 </file>
@@ -982,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1066,7 +1066,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1094,7 +1094,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1150,7 +1150,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1178,7 +1178,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1206,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1234,7 +1234,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1262,7 +1262,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1290,7 +1290,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1318,7 +1318,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1">
@@ -1346,7 +1346,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1">
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1">
@@ -1402,7 +1402,7 @@
         <v>28</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
@@ -1430,7 +1430,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
@@ -1458,7 +1458,7 @@
         <v>28</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1">
@@ -1486,7 +1486,7 @@
         <v>28</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
@@ -1514,7 +1514,7 @@
         <v>28</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
@@ -1542,7 +1542,7 @@
         <v>37</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1">
@@ -1570,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
@@ -1598,7 +1598,7 @@
         <v>11</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
@@ -1626,7 +1626,7 @@
         <v>11</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1">
@@ -1654,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
@@ -1682,7 +1682,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1">
@@ -1710,7 +1710,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1">
@@ -1766,7 +1766,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
@@ -1794,7 +1794,7 @@
         <v>21</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
@@ -1822,7 +1822,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
@@ -1850,7 +1850,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1">
@@ -1878,7 +1878,7 @@
         <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1">
@@ -1906,7 +1906,7 @@
         <v>43</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
@@ -1934,7 +1934,7 @@
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
@@ -1962,7 +1962,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
@@ -1990,7 +1990,7 @@
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1">
@@ -2018,7 +2018,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1">
@@ -2046,7 +2046,7 @@
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1">
@@ -2074,7 +2074,7 @@
         <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1">
@@ -2102,7 +2102,7 @@
         <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1">
@@ -2130,7 +2130,7 @@
         <v>48</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1">
@@ -2158,7 +2158,7 @@
         <v>48</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1">
@@ -2186,7 +2186,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
@@ -2214,7 +2214,7 @@
         <v>53</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1">
@@ -2242,7 +2242,7 @@
         <v>53</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1">
@@ -2270,7 +2270,7 @@
         <v>53</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1">
@@ -2298,7 +2298,7 @@
         <v>53</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1">
@@ -2326,7 +2326,7 @@
         <v>53</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
@@ -2354,7 +2354,7 @@
         <v>53</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1">
@@ -2382,7 +2382,7 @@
         <v>55</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1">
@@ -2410,7 +2410,7 @@
         <v>55</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1">
@@ -2438,7 +2438,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1">
@@ -2466,7 +2466,7 @@
         <v>55</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1">
@@ -2494,7 +2494,7 @@
         <v>55</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1">
@@ -2522,7 +2522,7 @@
         <v>61</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1">
@@ -2550,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1">
@@ -2578,7 +2578,7 @@
         <v>61</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1">
@@ -2606,7 +2606,7 @@
         <v>61</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1">
@@ -2634,7 +2634,7 @@
         <v>61</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1">
@@ -2662,7 +2662,7 @@
         <v>61</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1">
@@ -2690,7 +2690,7 @@
         <v>61</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1">
@@ -2718,7 +2718,7 @@
         <v>61</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
@@ -2746,7 +2746,7 @@
         <v>63</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1">
@@ -2774,7 +2774,7 @@
         <v>63</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
@@ -2802,7 +2802,7 @@
         <v>63</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
@@ -2830,7 +2830,7 @@
         <v>63</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2858,7 +2858,7 @@
         <v>67</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2886,7 +2886,7 @@
         <v>67</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2914,7 +2914,7 @@
         <v>67</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2942,7 +2942,7 @@
         <v>67</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2970,7 +2970,7 @@
         <v>67</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2998,7 +2998,7 @@
         <v>67</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3026,7 +3026,7 @@
         <v>69</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3054,7 +3054,7 @@
         <v>69</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3082,7 +3082,7 @@
         <v>69</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3110,7 +3110,7 @@
         <v>28</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3138,7 +3138,7 @@
         <v>28</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3166,7 +3166,7 @@
         <v>28</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3194,7 +3194,7 @@
         <v>28</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3222,7 +3222,7 @@
         <v>37</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3250,7 +3250,7 @@
         <v>37</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3278,12 +3278,12 @@
         <v>37</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="45" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B84" s="45">
         <v>50</v>
@@ -3306,12 +3306,12 @@
         <v>37</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B85" s="45">
         <v>46</v>
@@ -3334,7 +3334,7 @@
         <v>37</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3362,7 +3362,7 @@
         <v>37</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="48" customFormat="1">
@@ -3380,17 +3380,17 @@
         <v>10</v>
       </c>
       <c r="F87" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G87" s="55"/>
       <c r="H87" s="56">
         <v>46152</v>
       </c>
       <c r="I87" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="48" customFormat="1">
@@ -3408,17 +3408,17 @@
         <v>9</v>
       </c>
       <c r="F88" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G88" s="55"/>
       <c r="H88" s="56">
         <v>46152</v>
       </c>
       <c r="I88" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J88" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="48" customFormat="1">
@@ -3436,22 +3436,22 @@
         <v>7</v>
       </c>
       <c r="F89" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G89" s="55"/>
       <c r="H89" s="56">
         <v>46152</v>
       </c>
       <c r="I89" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J89" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="48" customFormat="1">
       <c r="A90" s="55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B90" s="55">
         <v>49</v>
@@ -3464,22 +3464,22 @@
         <v>3</v>
       </c>
       <c r="F90" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G90" s="55"/>
       <c r="H90" s="56">
         <v>46152</v>
       </c>
       <c r="I90" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J90" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="48" customFormat="1">
       <c r="A91" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91" s="55">
         <v>38</v>
@@ -3492,17 +3492,17 @@
         <v>8</v>
       </c>
       <c r="F91" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G91" s="55"/>
       <c r="H91" s="56">
         <v>46152</v>
       </c>
       <c r="I91" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J91" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:10" s="48" customFormat="1">
@@ -3520,22 +3520,22 @@
         <v>7</v>
       </c>
       <c r="F92" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G92" s="55"/>
       <c r="H92" s="56">
         <v>46152</v>
       </c>
       <c r="I92" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J92" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:10" s="48" customFormat="1">
       <c r="A93" s="55" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B93" s="55">
         <v>46</v>
@@ -3548,17 +3548,17 @@
         <v>6</v>
       </c>
       <c r="F93" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G93" s="55"/>
       <c r="H93" s="56">
         <v>46152</v>
       </c>
       <c r="I93" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J93" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:10" s="48" customFormat="1">
@@ -3576,22 +3576,22 @@
         <v>5</v>
       </c>
       <c r="F94" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G94" s="55"/>
       <c r="H94" s="56">
         <v>46152</v>
       </c>
       <c r="I94" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J94" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:10" s="48" customFormat="1">
       <c r="A95" s="55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B95" s="55">
         <v>46</v>
@@ -3604,17 +3604,17 @@
         <v>4</v>
       </c>
       <c r="F95" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G95" s="55"/>
       <c r="H95" s="56">
         <v>46152</v>
       </c>
       <c r="I95" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J95" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="48" customFormat="1">
@@ -3632,17 +3632,17 @@
         <v>10</v>
       </c>
       <c r="F96" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G96" s="55"/>
       <c r="H96" s="56">
         <v>46152</v>
       </c>
       <c r="I96" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J96" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:10" s="48" customFormat="1">
@@ -3660,17 +3660,17 @@
         <v>9</v>
       </c>
       <c r="F97" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G97" s="55"/>
       <c r="H97" s="56">
         <v>46152</v>
       </c>
       <c r="I97" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J97" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3688,17 +3688,17 @@
         <v>8</v>
       </c>
       <c r="F98" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G98" s="55"/>
       <c r="H98" s="56">
         <v>46152</v>
       </c>
       <c r="I98" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J98" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -3716,17 +3716,17 @@
         <v>7</v>
       </c>
       <c r="F99" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G99" s="55"/>
       <c r="H99" s="56">
         <v>46152</v>
       </c>
       <c r="I99" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3802,7 +3802,7 @@
       <c r="J105" s="48"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:I99"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -3844,7 +3844,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3667,7 +3667,7 @@
         <v>46152</v>
       </c>
       <c r="I97" s="55" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J97" s="48" t="s">
         <v>78</v>
@@ -3695,7 +3695,7 @@
         <v>46152</v>
       </c>
       <c r="I98" s="55" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J98" s="48" t="s">
         <v>78</v>
@@ -3723,7 +3723,7 @@
         <v>46152</v>
       </c>
       <c r="I99" s="55" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J99" s="48" t="s">
         <v>78</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -258,9 +258,6 @@
     <t>Eira Hooper</t>
   </si>
   <si>
-    <t>10 May 2026 | 13:00 - 14:00 Tee Times | Spring Round 2</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -289,6 +286,9 @@
   </si>
   <si>
     <t>Mollie Williams</t>
+  </si>
+  <si>
+    <t>14 June 2026 | 13:00 - 14:00 Tee Times | Summer Round 1</t>
   </si>
 </sst>
 </file>
@@ -982,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1066,7 +1066,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1094,7 +1094,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1150,7 +1150,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1178,7 +1178,7 @@
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1206,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1234,7 +1234,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1262,7 +1262,7 @@
         <v>24</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1290,7 +1290,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1318,7 +1318,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1">
@@ -1346,7 +1346,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1">
@@ -1374,7 +1374,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1">
@@ -1402,7 +1402,7 @@
         <v>28</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1">
@@ -1430,7 +1430,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1">
@@ -1458,7 +1458,7 @@
         <v>28</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1">
@@ -1486,7 +1486,7 @@
         <v>28</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
@@ -1514,7 +1514,7 @@
         <v>28</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1">
@@ -1542,7 +1542,7 @@
         <v>37</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1">
@@ -1570,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
@@ -1598,7 +1598,7 @@
         <v>11</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
@@ -1626,7 +1626,7 @@
         <v>11</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1">
@@ -1654,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
@@ -1682,7 +1682,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1">
@@ -1710,7 +1710,7 @@
         <v>17</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
@@ -1738,7 +1738,7 @@
         <v>17</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1">
@@ -1766,7 +1766,7 @@
         <v>17</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
@@ -1794,7 +1794,7 @@
         <v>21</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
@@ -1822,7 +1822,7 @@
         <v>21</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
@@ -1850,7 +1850,7 @@
         <v>21</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1">
@@ -1878,7 +1878,7 @@
         <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1">
@@ -1906,7 +1906,7 @@
         <v>43</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
@@ -1934,7 +1934,7 @@
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
@@ -1962,7 +1962,7 @@
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
@@ -1990,7 +1990,7 @@
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1">
@@ -2018,7 +2018,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1">
@@ -2046,7 +2046,7 @@
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1">
@@ -2074,7 +2074,7 @@
         <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1">
@@ -2102,7 +2102,7 @@
         <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1">
@@ -2130,7 +2130,7 @@
         <v>48</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1">
@@ -2158,7 +2158,7 @@
         <v>48</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1">
@@ -2186,7 +2186,7 @@
         <v>48</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
@@ -2214,7 +2214,7 @@
         <v>53</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1">
@@ -2242,7 +2242,7 @@
         <v>53</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1">
@@ -2270,7 +2270,7 @@
         <v>53</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1">
@@ -2298,7 +2298,7 @@
         <v>53</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1">
@@ -2326,7 +2326,7 @@
         <v>53</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
@@ -2354,7 +2354,7 @@
         <v>53</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1">
@@ -2382,7 +2382,7 @@
         <v>55</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1">
@@ -2410,7 +2410,7 @@
         <v>55</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1">
@@ -2438,7 +2438,7 @@
         <v>55</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1">
@@ -2466,7 +2466,7 @@
         <v>55</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1">
@@ -2494,7 +2494,7 @@
         <v>55</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1">
@@ -2522,7 +2522,7 @@
         <v>61</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1">
@@ -2550,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1">
@@ -2578,7 +2578,7 @@
         <v>61</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1">
@@ -2606,7 +2606,7 @@
         <v>61</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1">
@@ -2634,7 +2634,7 @@
         <v>61</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1">
@@ -2662,7 +2662,7 @@
         <v>61</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1">
@@ -2690,7 +2690,7 @@
         <v>61</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1">
@@ -2718,7 +2718,7 @@
         <v>61</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
@@ -2746,7 +2746,7 @@
         <v>63</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1">
@@ -2774,7 +2774,7 @@
         <v>63</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
@@ -2802,7 +2802,7 @@
         <v>63</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
@@ -2830,7 +2830,7 @@
         <v>63</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2858,7 +2858,7 @@
         <v>67</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2886,7 +2886,7 @@
         <v>67</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2914,7 +2914,7 @@
         <v>67</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2942,7 +2942,7 @@
         <v>67</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2970,7 +2970,7 @@
         <v>67</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2998,7 +2998,7 @@
         <v>67</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3026,7 +3026,7 @@
         <v>69</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3054,7 +3054,7 @@
         <v>69</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3082,7 +3082,7 @@
         <v>69</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3110,7 +3110,7 @@
         <v>28</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3138,7 +3138,7 @@
         <v>28</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3166,7 +3166,7 @@
         <v>28</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3194,7 +3194,7 @@
         <v>28</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3222,7 +3222,7 @@
         <v>37</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3250,7 +3250,7 @@
         <v>37</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3278,12 +3278,12 @@
         <v>37</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B84" s="45">
         <v>50</v>
@@ -3306,7 +3306,7 @@
         <v>37</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3334,7 +3334,7 @@
         <v>37</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3362,7 +3362,7 @@
         <v>37</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="48" customFormat="1">
@@ -3380,17 +3380,17 @@
         <v>10</v>
       </c>
       <c r="F87" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G87" s="55"/>
       <c r="H87" s="56">
         <v>46152</v>
       </c>
       <c r="I87" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J87" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="48" customFormat="1">
@@ -3408,17 +3408,17 @@
         <v>9</v>
       </c>
       <c r="F88" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G88" s="55"/>
       <c r="H88" s="56">
         <v>46152</v>
       </c>
       <c r="I88" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J88" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="48" customFormat="1">
@@ -3436,22 +3436,22 @@
         <v>7</v>
       </c>
       <c r="F89" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G89" s="55"/>
       <c r="H89" s="56">
         <v>46152</v>
       </c>
       <c r="I89" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J89" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="48" customFormat="1">
       <c r="A90" s="55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" s="55">
         <v>49</v>
@@ -3464,22 +3464,22 @@
         <v>3</v>
       </c>
       <c r="F90" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G90" s="55"/>
       <c r="H90" s="56">
         <v>46152</v>
       </c>
       <c r="I90" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J90" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="48" customFormat="1">
       <c r="A91" s="55" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B91" s="55">
         <v>38</v>
@@ -3492,17 +3492,17 @@
         <v>8</v>
       </c>
       <c r="F91" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G91" s="55"/>
       <c r="H91" s="56">
         <v>46152</v>
       </c>
       <c r="I91" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J91" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:10" s="48" customFormat="1">
@@ -3520,22 +3520,22 @@
         <v>7</v>
       </c>
       <c r="F92" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G92" s="55"/>
       <c r="H92" s="56">
         <v>46152</v>
       </c>
       <c r="I92" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J92" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:10" s="48" customFormat="1">
       <c r="A93" s="55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B93" s="55">
         <v>46</v>
@@ -3548,17 +3548,17 @@
         <v>6</v>
       </c>
       <c r="F93" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G93" s="55"/>
       <c r="H93" s="56">
         <v>46152</v>
       </c>
       <c r="I93" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J93" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:10" s="48" customFormat="1">
@@ -3576,17 +3576,17 @@
         <v>5</v>
       </c>
       <c r="F94" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G94" s="55"/>
       <c r="H94" s="56">
         <v>46152</v>
       </c>
       <c r="I94" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J94" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:10" s="48" customFormat="1">
@@ -3604,17 +3604,17 @@
         <v>4</v>
       </c>
       <c r="F95" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G95" s="55"/>
       <c r="H95" s="56">
         <v>46152</v>
       </c>
       <c r="I95" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J95" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="48" customFormat="1">
@@ -3632,17 +3632,17 @@
         <v>10</v>
       </c>
       <c r="F96" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G96" s="55"/>
       <c r="H96" s="56">
         <v>46152</v>
       </c>
       <c r="I96" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J96" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:10" s="48" customFormat="1">
@@ -3660,17 +3660,17 @@
         <v>9</v>
       </c>
       <c r="F97" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G97" s="55"/>
       <c r="H97" s="56">
         <v>46152</v>
       </c>
       <c r="I97" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J97" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3688,17 +3688,17 @@
         <v>8</v>
       </c>
       <c r="F98" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G98" s="55"/>
       <c r="H98" s="56">
         <v>46152</v>
       </c>
       <c r="I98" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J98" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -3716,17 +3716,17 @@
         <v>7</v>
       </c>
       <c r="F99" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G99" s="55"/>
       <c r="H99" s="56">
         <v>46152</v>
       </c>
       <c r="I99" s="55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J99" s="48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3844,7 +3844,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="89">
   <si>
     <t>Name</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>14 June 2026 | 13:00 - 14:00 Tee Times | Summer Round 1</t>
+  </si>
+  <si>
+    <t>April Junior Competition Sixes Beginners</t>
+  </si>
+  <si>
+    <t>April Sixes -Beginners</t>
   </si>
 </sst>
 </file>
@@ -353,7 +359,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +510,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -566,7 +578,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -662,6 +674,11 @@
     <xf numFmtId="15" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="15" fontId="4" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="4" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="4" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="60% - Accent1 2" xfId="1"/>
@@ -939,18 +956,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J105"/>
-  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="38.85546875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.140625" style="1"/>
+    <col min="3" max="3" width="7.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="38.81640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.1796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5">
@@ -3198,27 +3215,27 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="45" t="s">
+      <c r="A81" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="B81" s="45">
+      <c r="B81" s="57">
         <v>54</v>
       </c>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45">
-        <v>6</v>
-      </c>
-      <c r="E81" s="45">
-        <v>5</v>
-      </c>
-      <c r="F81" s="47" t="s">
+      <c r="C81" s="57"/>
+      <c r="D81" s="57">
+        <v>3</v>
+      </c>
+      <c r="E81" s="57">
+        <v>8</v>
+      </c>
+      <c r="F81" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="G81" s="45"/>
-      <c r="H81" s="46">
+      <c r="G81" s="57"/>
+      <c r="H81" s="59">
         <v>46124</v>
       </c>
-      <c r="I81" s="47" t="s">
+      <c r="I81" s="58" t="s">
         <v>37</v>
       </c>
       <c r="J81" s="1" t="s">
@@ -3226,140 +3243,140 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="45" t="s">
+      <c r="A82" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B82" s="45">
+      <c r="B82" s="57">
         <v>30</v>
       </c>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45">
+      <c r="C82" s="57"/>
+      <c r="D82" s="57">
+        <v>1</v>
+      </c>
+      <c r="E82" s="57">
+        <v>9</v>
+      </c>
+      <c r="F82" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82" s="57"/>
+      <c r="H82" s="59">
+        <v>46124</v>
+      </c>
+      <c r="I82" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B83" s="57">
+        <v>39</v>
+      </c>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57">
         <v>2</v>
       </c>
-      <c r="E82" s="45">
+      <c r="E83" s="57">
+        <v>10</v>
+      </c>
+      <c r="F83" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G83" s="57"/>
+      <c r="H83" s="59">
+        <v>46124</v>
+      </c>
+      <c r="I83" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="57">
+        <v>50</v>
+      </c>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57">
+        <v>3</v>
+      </c>
+      <c r="E84" s="57">
+        <v>8</v>
+      </c>
+      <c r="F84" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G84" s="57"/>
+      <c r="H84" s="59">
+        <v>46124</v>
+      </c>
+      <c r="I84" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" s="57">
+        <v>46</v>
+      </c>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57">
+        <v>2</v>
+      </c>
+      <c r="E85" s="57">
         <v>9</v>
       </c>
-      <c r="F82" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G82" s="45"/>
-      <c r="H82" s="46">
+      <c r="F85" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G85" s="57"/>
+      <c r="H85" s="59">
         <v>46124</v>
       </c>
-      <c r="I82" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="45">
-        <v>39</v>
-      </c>
-      <c r="C83" s="45"/>
-      <c r="D83" s="45">
-        <v>5</v>
-      </c>
-      <c r="E83" s="45">
-        <v>6</v>
-      </c>
-      <c r="F83" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G83" s="45"/>
-      <c r="H83" s="46">
+      <c r="I85" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B86" s="57">
+        <v>43</v>
+      </c>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57">
+        <v>1</v>
+      </c>
+      <c r="E86" s="57">
+        <v>10</v>
+      </c>
+      <c r="F86" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G86" s="57"/>
+      <c r="H86" s="59">
         <v>46124</v>
       </c>
-      <c r="I83" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="45">
-        <v>50</v>
-      </c>
-      <c r="C84" s="45"/>
-      <c r="D84" s="45">
-        <v>4</v>
-      </c>
-      <c r="E84" s="45">
-        <v>7</v>
-      </c>
-      <c r="F84" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G84" s="45"/>
-      <c r="H84" s="46">
-        <v>46124</v>
-      </c>
-      <c r="I84" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="B85" s="45">
-        <v>46</v>
-      </c>
-      <c r="C85" s="45"/>
-      <c r="D85" s="45">
-        <v>1</v>
-      </c>
-      <c r="E85" s="45">
-        <v>10</v>
-      </c>
-      <c r="F85" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G85" s="45"/>
-      <c r="H85" s="46">
-        <v>46124</v>
-      </c>
-      <c r="I85" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="B86" s="45">
-        <v>43</v>
-      </c>
-      <c r="C86" s="45"/>
-      <c r="D86" s="45">
-        <v>3</v>
-      </c>
-      <c r="E86" s="45">
-        <v>8</v>
-      </c>
-      <c r="F86" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="45"/>
-      <c r="H86" s="46">
-        <v>46124</v>
-      </c>
-      <c r="I86" s="47" t="s">
-        <v>37</v>
+      <c r="I86" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>77</v>
@@ -3814,11 +3831,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" style="49" customWidth="1"/>
-    <col min="2" max="2" width="60.42578125" style="49" customWidth="1"/>
-    <col min="3" max="16384" width="10.140625" style="49"/>
+    <col min="1" max="1" width="21.453125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="60.453125" style="49" customWidth="1"/>
+    <col min="3" max="16384" width="10.1796875" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1">

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3254,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="57">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" s="58" t="s">
         <v>36</v>
@@ -3282,7 +3282,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="57">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F83" s="58" t="s">
         <v>36</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$99</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="92">
   <si>
     <t>Name</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Score</t>
   </si>
   <si>
-    <t>Stableford Points</t>
-  </si>
-  <si>
     <t>Position</t>
   </si>
   <si>
@@ -295,6 +292,18 @@
   </si>
   <si>
     <t>April Sixes -Beginners</t>
+  </si>
+  <si>
+    <t>May Junior Competition Sixes Beginners</t>
+  </si>
+  <si>
+    <t>May Sixes - Beginners</t>
+  </si>
+  <si>
+    <t>Playing Handicap</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -304,7 +313,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-809]dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -358,8 +367,14 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="JetBrains Mono"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,6 +531,24 @@
         <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -578,7 +611,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -670,8 +703,6 @@
     <xf numFmtId="49" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="15" fontId="4" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -679,6 +710,15 @@
     <xf numFmtId="164" fontId="4" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="4" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="9" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="60% - Accent1 2" xfId="1"/>
@@ -955,22 +995,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="10.1796875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="38.81640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.1796875" style="1"/>
+    <col min="3" max="3" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="38.81640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5">
+    <row r="1" spans="1:11" ht="16.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -978,2848 +1019,2910 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="B2" s="6">
         <v>40</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="6">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="6">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="B3" s="6">
         <v>64</v>
       </c>
       <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6">
         <v>4</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="6">
         <v>5</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>48</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="6">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="6">
         <v>52</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
         <v>3</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6">
         <v>51</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="6">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="K6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="B7" s="6">
         <v>49</v>
       </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7">
+        <v>45449</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7">
-        <v>45449</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="6">
         <v>58</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>6</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7">
+        <v>45501</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7">
-        <v>45501</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="6">
         <v>55</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
         <v>2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7">
+        <v>45501</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7">
-        <v>45501</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="K9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="B10" s="6">
         <v>39</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7">
+        <v>45501</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7">
-        <v>45501</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6">
         <v>53</v>
       </c>
       <c r="C11" s="6"/>
-      <c r="D11" s="6">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
         <v>2</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <v>8</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7">
+        <v>45522</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7">
-        <v>45522</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="6">
         <v>46</v>
       </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="6">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <v>10</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7">
+        <v>45522</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="7">
-        <v>45522</v>
-      </c>
-      <c r="I12" s="6" t="s">
+      <c r="K12" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="B13" s="9">
         <v>47</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="9">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9">
         <v>1</v>
       </c>
-      <c r="E13" s="9">
+      <c r="F13" s="9">
         <v>10</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10" t="s">
+      <c r="J13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="K13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A14" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="B14" s="9">
         <v>53</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="9">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9">
         <v>2</v>
       </c>
-      <c r="E14" s="9">
+      <c r="F14" s="9">
         <v>8</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10" t="s">
+      <c r="J14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K14" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="9">
         <v>55</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="9">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9">
         <v>3</v>
       </c>
-      <c r="E15" s="9">
+      <c r="F15" s="9">
         <v>6</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10" t="s">
+      <c r="J15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="9">
         <v>56</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="9">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9">
         <v>4</v>
       </c>
-      <c r="E16" s="9">
+      <c r="F16" s="9">
         <v>5</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10" t="s">
+      <c r="J16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9">
         <v>60</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="9">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9">
         <v>5</v>
       </c>
-      <c r="E17" s="9">
+      <c r="F17" s="9">
         <v>4</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10" t="s">
+      <c r="J17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="9">
         <v>74</v>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="9">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9">
         <v>6</v>
       </c>
-      <c r="E18" s="9">
+      <c r="F18" s="9">
         <v>3</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10" t="s">
+      <c r="J18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="9">
         <v>78</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="9">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9">
         <v>7</v>
       </c>
-      <c r="E19" s="9">
+      <c r="F19" s="9">
         <v>2</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10" t="s">
+      <c r="J19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K19" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="9">
         <v>79</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="9">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9">
         <v>8</v>
       </c>
-      <c r="E20" s="9">
+      <c r="F20" s="9">
         <v>1</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="12">
         <v>30</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="12">
+      <c r="D21" s="12"/>
+      <c r="E21" s="12">
         <v>1</v>
       </c>
-      <c r="E21" s="12">
+      <c r="F21" s="12">
         <v>10</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" s="11" t="s">
+      <c r="K21" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A22" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="B22" s="12">
         <v>45</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="12">
+      <c r="D22" s="12"/>
+      <c r="E22" s="12">
         <v>2</v>
       </c>
-      <c r="E22" s="12">
+      <c r="F22" s="12">
         <v>8</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="15">
         <v>50</v>
       </c>
       <c r="C23" s="15"/>
-      <c r="D23" s="15">
+      <c r="D23" s="15"/>
+      <c r="E23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
+      <c r="F23" s="15">
         <v>10</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="G23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="14" t="s">
+      <c r="K23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A24" s="14" t="s">
         <v>11</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>12</v>
       </c>
       <c r="B24" s="15">
         <v>57</v>
       </c>
       <c r="C24" s="15"/>
-      <c r="D24" s="15">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15">
         <v>2</v>
       </c>
-      <c r="E24" s="15">
+      <c r="F24" s="15">
         <v>8</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K24" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="15">
         <v>65</v>
       </c>
       <c r="C25" s="15"/>
-      <c r="D25" s="15">
+      <c r="D25" s="15"/>
+      <c r="E25" s="15">
         <v>3</v>
       </c>
-      <c r="E25" s="15">
+      <c r="F25" s="15">
         <v>6</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="G25" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K25" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="15">
+        <v>76</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15">
+        <v>4</v>
+      </c>
+      <c r="F26" s="15">
+        <v>5</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A27" s="17" t="s">
         <v>34</v>
-      </c>
-      <c r="B26" s="15">
-        <v>76</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15">
-        <v>4</v>
-      </c>
-      <c r="E26" s="15">
-        <v>5</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A27" s="17" t="s">
-        <v>35</v>
       </c>
       <c r="B27" s="18">
         <v>30</v>
       </c>
       <c r="C27" s="18"/>
-      <c r="D27" s="18">
+      <c r="D27" s="18"/>
+      <c r="E27" s="18">
         <v>1</v>
       </c>
-      <c r="E27" s="18">
+      <c r="F27" s="18">
         <v>10</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="G27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J27" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="17" t="s">
+      <c r="K27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A28" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="B28" s="18">
         <v>47</v>
       </c>
       <c r="C28" s="18"/>
-      <c r="D28" s="18">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18">
         <v>2</v>
       </c>
-      <c r="E28" s="18">
+      <c r="F28" s="18">
         <v>8</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="G28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K28" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="18">
         <v>53</v>
       </c>
       <c r="C29" s="18"/>
-      <c r="D29" s="18">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18">
         <v>3</v>
       </c>
-      <c r="E29" s="18">
+      <c r="F29" s="18">
         <v>6</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="G29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K29" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="21">
         <v>45</v>
       </c>
       <c r="C30" s="21"/>
-      <c r="D30" s="21">
+      <c r="D30" s="21"/>
+      <c r="E30" s="21">
         <v>1</v>
       </c>
-      <c r="E30" s="21">
+      <c r="F30" s="21">
         <v>10</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="G30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22" t="s">
+      <c r="K30" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A31" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="B31" s="21">
         <v>47</v>
       </c>
       <c r="C31" s="21"/>
-      <c r="D31" s="21">
+      <c r="D31" s="21"/>
+      <c r="E31" s="21">
         <v>2</v>
       </c>
-      <c r="E31" s="21">
+      <c r="F31" s="21">
         <v>8</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="G31" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K31" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" s="21">
         <v>58</v>
       </c>
       <c r="C32" s="21"/>
-      <c r="D32" s="21">
+      <c r="D32" s="21"/>
+      <c r="E32" s="21">
         <v>3</v>
       </c>
-      <c r="E32" s="21">
+      <c r="F32" s="21">
         <v>6</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="G32" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="21"/>
+      <c r="I32" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="21"/>
-      <c r="H32" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="K32" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" s="24">
         <v>28</v>
       </c>
       <c r="C33" s="24"/>
-      <c r="D33" s="24">
+      <c r="D33" s="24"/>
+      <c r="E33" s="24">
         <v>1</v>
       </c>
-      <c r="E33" s="24">
+      <c r="F33" s="24">
         <v>10</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="G33" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" s="24"/>
+      <c r="I33" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="24"/>
-      <c r="H33" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33" s="23" t="s">
+      <c r="K33" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15" customHeight="1">
+      <c r="A34" s="23" t="s">
         <v>43</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1">
-      <c r="A34" s="23" t="s">
-        <v>44</v>
       </c>
       <c r="B34" s="24">
         <v>44</v>
       </c>
       <c r="C34" s="24"/>
-      <c r="D34" s="24">
+      <c r="D34" s="24"/>
+      <c r="E34" s="24">
         <v>2</v>
       </c>
-      <c r="E34" s="24">
+      <c r="F34" s="24">
         <v>8</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="G34" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="24"/>
+      <c r="I34" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1">
+      <c r="K34" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" s="27">
         <v>38</v>
       </c>
       <c r="C35" s="27"/>
-      <c r="D35" s="27">
+      <c r="D35" s="27"/>
+      <c r="E35" s="27">
         <v>1</v>
       </c>
-      <c r="E35" s="27">
+      <c r="F35" s="27">
         <v>10</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="G35" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1">
+      <c r="K35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="27">
         <v>60</v>
       </c>
       <c r="C36" s="27"/>
-      <c r="D36" s="27">
+      <c r="D36" s="27"/>
+      <c r="E36" s="27">
         <v>5</v>
       </c>
-      <c r="E36" s="27">
+      <c r="F36" s="27">
         <v>4</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="G36" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="27"/>
+      <c r="I36" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1">
+      <c r="K36" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" s="27">
         <v>56</v>
       </c>
       <c r="C37" s="27"/>
-      <c r="D37" s="27">
+      <c r="D37" s="27"/>
+      <c r="E37" s="27">
         <v>4</v>
       </c>
-      <c r="E37" s="27">
+      <c r="F37" s="27">
         <v>5</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="G37" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1">
+      <c r="K37" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" s="27">
         <v>47</v>
       </c>
       <c r="C38" s="27"/>
-      <c r="D38" s="27">
+      <c r="D38" s="27"/>
+      <c r="E38" s="27">
         <v>3</v>
       </c>
-      <c r="E38" s="27">
+      <c r="F38" s="27">
         <v>6</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="G38" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="27"/>
+      <c r="I38" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G38" s="27"/>
-      <c r="H38" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1">
+      <c r="K38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B39" s="27">
         <v>44</v>
       </c>
       <c r="C39" s="27"/>
-      <c r="D39" s="27">
+      <c r="D39" s="27"/>
+      <c r="E39" s="27">
         <v>2</v>
       </c>
-      <c r="E39" s="27">
+      <c r="F39" s="27">
         <v>8</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="G39" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="27"/>
+      <c r="I39" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="27"/>
-      <c r="H39" s="28" t="s">
+      <c r="K39" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15" customHeight="1">
+      <c r="A40" s="30" t="s">
         <v>45</v>
-      </c>
-      <c r="I39" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>46</v>
       </c>
       <c r="B40" s="31">
         <v>32</v>
       </c>
       <c r="C40" s="31"/>
-      <c r="D40" s="31">
+      <c r="D40" s="31"/>
+      <c r="E40" s="31">
         <v>1</v>
       </c>
-      <c r="E40" s="31">
+      <c r="F40" s="31">
         <v>10</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="G40" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="31"/>
+      <c r="I40" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G40" s="31"/>
-      <c r="H40" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1">
+      <c r="K40" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41" s="31">
         <v>34</v>
       </c>
       <c r="C41" s="31"/>
-      <c r="D41" s="31">
+      <c r="D41" s="31"/>
+      <c r="E41" s="31">
         <v>2</v>
       </c>
-      <c r="E41" s="31">
+      <c r="F41" s="31">
         <v>8</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="G41" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="31"/>
+      <c r="I41" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I41" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1">
+      <c r="K41" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="31">
         <v>35</v>
       </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="31">
+      <c r="D42" s="31"/>
+      <c r="E42" s="31">
         <v>3</v>
       </c>
-      <c r="E42" s="31">
+      <c r="F42" s="31">
         <v>6</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="G42" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" s="31"/>
+      <c r="I42" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J42" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G42" s="31"/>
-      <c r="H42" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I42" s="32" t="s">
+      <c r="K42" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15" customHeight="1">
+      <c r="A43" s="32" t="s">
         <v>48</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1">
-      <c r="A43" s="32" t="s">
-        <v>49</v>
       </c>
       <c r="B43" s="31">
         <v>39</v>
       </c>
       <c r="C43" s="31"/>
-      <c r="D43" s="31">
+      <c r="D43" s="31"/>
+      <c r="E43" s="31">
         <v>4</v>
       </c>
-      <c r="E43" s="31">
+      <c r="F43" s="31">
         <v>5</v>
       </c>
-      <c r="F43" s="32" t="s">
+      <c r="G43" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="31"/>
+      <c r="I43" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1">
+      <c r="K43" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="31">
         <v>46</v>
       </c>
       <c r="C44" s="31"/>
-      <c r="D44" s="31">
+      <c r="D44" s="31"/>
+      <c r="E44" s="31">
         <v>5</v>
       </c>
-      <c r="E44" s="31">
+      <c r="F44" s="31">
         <v>4</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="G44" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" s="31"/>
+      <c r="I44" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="31"/>
-      <c r="H44" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1">
+      <c r="K44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="18">
         <v>49</v>
       </c>
       <c r="C45" s="18"/>
-      <c r="D45" s="18">
+      <c r="D45" s="18"/>
+      <c r="E45" s="18">
         <v>1</v>
       </c>
-      <c r="E45" s="18">
+      <c r="F45" s="18">
         <v>10</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="G45" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G45" s="18"/>
-      <c r="H45" s="19" t="s">
+      <c r="J45" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I45" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1">
+      <c r="K45" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" s="18">
         <v>49</v>
       </c>
       <c r="C46" s="18"/>
-      <c r="D46" s="18">
+      <c r="D46" s="18"/>
+      <c r="E46" s="18">
         <v>2</v>
       </c>
-      <c r="E46" s="18">
+      <c r="F46" s="18">
         <v>8</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="G46" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="18"/>
-      <c r="H46" s="19" t="s">
+      <c r="J46" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1">
+      <c r="K46" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" s="18">
         <v>53</v>
       </c>
       <c r="C47" s="18"/>
-      <c r="D47" s="18">
+      <c r="D47" s="18"/>
+      <c r="E47" s="18">
         <v>3</v>
       </c>
-      <c r="E47" s="18">
+      <c r="F47" s="18">
         <v>6</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="G47" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19" t="s">
+      <c r="J47" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I47" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1">
+      <c r="K47" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="18">
         <v>58</v>
       </c>
       <c r="C48" s="18"/>
-      <c r="D48" s="18">
+      <c r="D48" s="18"/>
+      <c r="E48" s="18">
         <v>4</v>
       </c>
-      <c r="E48" s="18">
+      <c r="F48" s="18">
         <v>5</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="G48" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G48" s="18"/>
-      <c r="H48" s="19" t="s">
+      <c r="J48" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1">
+      <c r="K48" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" s="18">
         <v>61</v>
       </c>
       <c r="C49" s="18"/>
-      <c r="D49" s="18">
+      <c r="D49" s="18"/>
+      <c r="E49" s="18">
         <v>5</v>
       </c>
-      <c r="E49" s="18">
+      <c r="F49" s="18">
         <v>4</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="G49" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H49" s="18"/>
+      <c r="I49" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19" t="s">
+      <c r="J49" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I49" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1">
+      <c r="K49" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="18">
         <v>63</v>
       </c>
       <c r="C50" s="18"/>
-      <c r="D50" s="18">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18">
         <v>6</v>
       </c>
-      <c r="E50" s="18">
+      <c r="F50" s="18">
         <v>3</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="G50" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" s="18"/>
+      <c r="I50" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G50" s="18"/>
-      <c r="H50" s="19" t="s">
+      <c r="J50" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I50" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1">
+      <c r="K50" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" s="35">
         <v>33</v>
       </c>
       <c r="C51" s="35"/>
-      <c r="D51" s="35">
+      <c r="D51" s="35"/>
+      <c r="E51" s="35">
         <v>1</v>
       </c>
-      <c r="E51" s="35">
+      <c r="F51" s="35">
         <v>10</v>
       </c>
-      <c r="F51" s="35" t="s">
+      <c r="G51" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H51" s="35"/>
+      <c r="I51" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G51" s="35"/>
-      <c r="H51" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I51" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1">
+      <c r="K51" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B52" s="35">
         <v>41</v>
       </c>
       <c r="C52" s="35"/>
-      <c r="D52" s="35">
+      <c r="D52" s="35"/>
+      <c r="E52" s="35">
         <v>3</v>
       </c>
-      <c r="E52" s="35">
+      <c r="F52" s="35">
         <v>6</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="G52" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H52" s="35"/>
+      <c r="I52" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J52" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G52" s="35"/>
-      <c r="H52" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I52" s="34" t="s">
+      <c r="K52" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15" customHeight="1">
+      <c r="A53" s="34" t="s">
         <v>55</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1">
-      <c r="A53" s="34" t="s">
-        <v>56</v>
       </c>
       <c r="B53" s="35">
         <v>38</v>
       </c>
       <c r="C53" s="35"/>
-      <c r="D53" s="35">
+      <c r="D53" s="35"/>
+      <c r="E53" s="35">
         <v>2</v>
       </c>
-      <c r="E53" s="35">
+      <c r="F53" s="35">
         <v>8</v>
       </c>
-      <c r="F53" s="35" t="s">
+      <c r="G53" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H53" s="35"/>
+      <c r="I53" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G53" s="35"/>
-      <c r="H53" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I53" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1">
+      <c r="K53" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="35">
         <v>44</v>
       </c>
       <c r="C54" s="35"/>
-      <c r="D54" s="35">
+      <c r="D54" s="35"/>
+      <c r="E54" s="35">
         <v>4</v>
       </c>
-      <c r="E54" s="35">
+      <c r="F54" s="35">
         <v>5</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="G54" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" s="35"/>
+      <c r="I54" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J54" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G54" s="35"/>
-      <c r="H54" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I54" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1">
+      <c r="K54" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="35">
         <v>51</v>
       </c>
       <c r="C55" s="35"/>
-      <c r="D55" s="35">
+      <c r="D55" s="35"/>
+      <c r="E55" s="35">
         <v>5</v>
       </c>
-      <c r="E55" s="35">
+      <c r="F55" s="35">
         <v>4</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="G55" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="35"/>
+      <c r="I55" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J55" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="G55" s="35"/>
-      <c r="H55" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="I55" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1">
+      <c r="K55" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" s="37">
         <v>45</v>
       </c>
       <c r="C56" s="37"/>
-      <c r="D56" s="37">
+      <c r="D56" s="37"/>
+      <c r="E56" s="37">
         <v>1</v>
       </c>
-      <c r="E56" s="37">
+      <c r="F56" s="37">
         <v>10</v>
       </c>
-      <c r="F56" s="37" t="s">
+      <c r="G56" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H56" s="37"/>
+      <c r="I56" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="37"/>
-      <c r="H56" s="38" t="s">
+      <c r="J56" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I56" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1">
+      <c r="K56" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B57" s="37">
         <v>58</v>
       </c>
       <c r="C57" s="37"/>
-      <c r="D57" s="37">
+      <c r="D57" s="37"/>
+      <c r="E57" s="37">
         <v>6</v>
       </c>
-      <c r="E57" s="37">
+      <c r="F57" s="37">
         <v>3</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="G57" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H57" s="37"/>
+      <c r="I57" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G57" s="37"/>
-      <c r="H57" s="38" t="s">
+      <c r="J57" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1">
+      <c r="K57" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="37">
         <v>56</v>
       </c>
       <c r="C58" s="37"/>
-      <c r="D58" s="37">
+      <c r="D58" s="37"/>
+      <c r="E58" s="37">
         <v>5</v>
       </c>
-      <c r="E58" s="37">
+      <c r="F58" s="37">
         <v>4</v>
       </c>
-      <c r="F58" s="37" t="s">
+      <c r="G58" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H58" s="37"/>
+      <c r="I58" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G58" s="37"/>
-      <c r="H58" s="38" t="s">
+      <c r="J58" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I58" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1">
+      <c r="K58" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" s="37">
         <v>48</v>
       </c>
       <c r="C59" s="37"/>
-      <c r="D59" s="37">
+      <c r="D59" s="37"/>
+      <c r="E59" s="37">
         <v>2</v>
       </c>
-      <c r="E59" s="37">
+      <c r="F59" s="37">
         <v>8</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="G59" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H59" s="37"/>
+      <c r="I59" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G59" s="37"/>
-      <c r="H59" s="38" t="s">
+      <c r="J59" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I59" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1">
+      <c r="K59" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B60" s="37">
         <v>51</v>
       </c>
       <c r="C60" s="37"/>
-      <c r="D60" s="37">
+      <c r="D60" s="37"/>
+      <c r="E60" s="37">
         <v>3</v>
       </c>
-      <c r="E60" s="37">
+      <c r="F60" s="37">
         <v>6</v>
       </c>
-      <c r="F60" s="37" t="s">
+      <c r="G60" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H60" s="37"/>
+      <c r="I60" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G60" s="37"/>
-      <c r="H60" s="38" t="s">
+      <c r="J60" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1">
+      <c r="K60" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="37">
         <v>66</v>
       </c>
       <c r="C61" s="37"/>
-      <c r="D61" s="37">
+      <c r="D61" s="37"/>
+      <c r="E61" s="37">
         <v>8</v>
       </c>
-      <c r="E61" s="37">
+      <c r="F61" s="37">
         <v>1</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="G61" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61" s="37"/>
+      <c r="I61" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G61" s="37"/>
-      <c r="H61" s="38" t="s">
+      <c r="J61" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1">
+      <c r="K61" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" s="37">
         <v>62</v>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="37">
+      <c r="D62" s="37"/>
+      <c r="E62" s="37">
         <v>7</v>
       </c>
-      <c r="E62" s="37">
+      <c r="F62" s="37">
         <v>2</v>
       </c>
-      <c r="F62" s="37" t="s">
+      <c r="G62" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H62" s="37"/>
+      <c r="I62" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="37"/>
-      <c r="H62" s="38" t="s">
+      <c r="J62" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I62" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1">
+      <c r="K62" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" s="37">
         <v>55</v>
       </c>
       <c r="C63" s="37"/>
-      <c r="D63" s="37">
+      <c r="D63" s="37"/>
+      <c r="E63" s="37">
         <v>4</v>
       </c>
-      <c r="E63" s="37">
+      <c r="F63" s="37">
         <v>5</v>
       </c>
-      <c r="F63" s="37" t="s">
+      <c r="G63" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H63" s="37"/>
+      <c r="I63" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="G63" s="37"/>
-      <c r="H63" s="38" t="s">
+      <c r="J63" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I63" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1">
+      <c r="K63" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B64" s="39">
         <v>32</v>
       </c>
       <c r="C64" s="39"/>
-      <c r="D64" s="39">
+      <c r="D64" s="39"/>
+      <c r="E64" s="39">
         <v>1</v>
       </c>
-      <c r="E64" s="39">
+      <c r="F64" s="39">
         <v>10</v>
       </c>
-      <c r="F64" s="39" t="s">
+      <c r="G64" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H64" s="39"/>
+      <c r="I64" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J64" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G64" s="39"/>
-      <c r="H64" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I64" s="39" t="s">
+      <c r="K64" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="15" customHeight="1">
+      <c r="A65" s="39" t="s">
         <v>63</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1">
-      <c r="A65" s="39" t="s">
-        <v>64</v>
       </c>
       <c r="B65" s="39">
         <v>34</v>
       </c>
       <c r="C65" s="39"/>
-      <c r="D65" s="39">
+      <c r="D65" s="39"/>
+      <c r="E65" s="39">
         <v>2</v>
       </c>
-      <c r="E65" s="39">
+      <c r="F65" s="39">
         <v>8</v>
       </c>
-      <c r="F65" s="39" t="s">
+      <c r="G65" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H65" s="39"/>
+      <c r="I65" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J65" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G65" s="39"/>
-      <c r="H65" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I65" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1">
+      <c r="K65" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B66" s="39">
         <v>49</v>
       </c>
       <c r="C66" s="39"/>
-      <c r="D66" s="39">
+      <c r="D66" s="39"/>
+      <c r="E66" s="39">
         <v>4</v>
       </c>
-      <c r="E66" s="39">
+      <c r="F66" s="39">
         <v>5</v>
       </c>
-      <c r="F66" s="39" t="s">
+      <c r="G66" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" s="39"/>
+      <c r="I66" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J66" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G66" s="39"/>
-      <c r="H66" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I66" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1">
+      <c r="K66" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="39">
         <v>37</v>
       </c>
       <c r="C67" s="39"/>
-      <c r="D67" s="39">
+      <c r="D67" s="39"/>
+      <c r="E67" s="39">
         <v>3</v>
       </c>
-      <c r="E67" s="39">
+      <c r="F67" s="39">
         <v>6</v>
       </c>
-      <c r="F67" s="39" t="s">
+      <c r="G67" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H67" s="39"/>
+      <c r="I67" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J67" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G67" s="39"/>
-      <c r="H67" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="I67" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="K67" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" s="41">
         <v>47</v>
       </c>
       <c r="C68" s="41"/>
-      <c r="D68" s="41">
+      <c r="D68" s="41"/>
+      <c r="E68" s="41">
         <v>1</v>
       </c>
-      <c r="E68" s="41">
+      <c r="F68" s="41">
         <v>10</v>
       </c>
-      <c r="F68" s="41" t="s">
+      <c r="G68" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H68" s="41"/>
+      <c r="I68" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G68" s="41"/>
-      <c r="H68" s="42" t="s">
+      <c r="J68" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I68" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="K68" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B69" s="41">
         <v>48</v>
       </c>
       <c r="C69" s="41"/>
-      <c r="D69" s="41">
+      <c r="D69" s="41"/>
+      <c r="E69" s="41">
         <v>2</v>
       </c>
-      <c r="E69" s="41">
+      <c r="F69" s="41">
         <v>8</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="G69" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H69" s="41"/>
+      <c r="I69" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G69" s="41"/>
-      <c r="H69" s="42" t="s">
+      <c r="J69" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I69" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="K69" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B70" s="41">
         <v>48</v>
       </c>
       <c r="C70" s="41"/>
-      <c r="D70" s="41">
+      <c r="D70" s="41"/>
+      <c r="E70" s="41">
         <v>3</v>
       </c>
-      <c r="E70" s="41">
+      <c r="F70" s="41">
         <v>6</v>
       </c>
-      <c r="F70" s="41" t="s">
+      <c r="G70" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H70" s="41"/>
+      <c r="I70" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G70" s="41"/>
-      <c r="H70" s="42" t="s">
+      <c r="J70" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I70" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+      <c r="K70" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" s="41">
         <v>49</v>
       </c>
       <c r="C71" s="41"/>
-      <c r="D71" s="41">
+      <c r="D71" s="41"/>
+      <c r="E71" s="41">
         <v>4</v>
       </c>
-      <c r="E71" s="41">
+      <c r="F71" s="41">
         <v>5</v>
       </c>
-      <c r="F71" s="41" t="s">
+      <c r="G71" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H71" s="41"/>
+      <c r="I71" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G71" s="41"/>
-      <c r="H71" s="42" t="s">
+      <c r="J71" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I71" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="K71" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="41">
         <v>52</v>
       </c>
       <c r="C72" s="41"/>
-      <c r="D72" s="41">
+      <c r="D72" s="41"/>
+      <c r="E72" s="41">
         <v>5</v>
       </c>
-      <c r="E72" s="41">
+      <c r="F72" s="41">
         <v>4</v>
       </c>
-      <c r="F72" s="41" t="s">
+      <c r="G72" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H72" s="41"/>
+      <c r="I72" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G72" s="41"/>
-      <c r="H72" s="42" t="s">
+      <c r="J72" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I72" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="K72" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B73" s="41">
         <v>62</v>
       </c>
       <c r="C73" s="41"/>
-      <c r="D73" s="41">
+      <c r="D73" s="41"/>
+      <c r="E73" s="41">
         <v>6</v>
       </c>
-      <c r="E73" s="41">
+      <c r="F73" s="41">
         <v>3</v>
       </c>
-      <c r="F73" s="41" t="s">
+      <c r="G73" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="H73" s="41"/>
+      <c r="I73" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G73" s="41"/>
-      <c r="H73" s="42" t="s">
+      <c r="J73" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="I73" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="K73" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B74" s="43">
         <v>30</v>
       </c>
       <c r="C74" s="43"/>
-      <c r="D74" s="43">
+      <c r="D74" s="43"/>
+      <c r="E74" s="43">
         <v>1</v>
       </c>
-      <c r="E74" s="43">
+      <c r="F74" s="43">
         <v>10</v>
       </c>
-      <c r="F74" s="43" t="s">
+      <c r="G74" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H74" s="43"/>
+      <c r="I74" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="J74" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G74" s="43"/>
-      <c r="H74" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="I74" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="K74" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B75" s="43">
         <v>34</v>
       </c>
       <c r="C75" s="43"/>
-      <c r="D75" s="43">
+      <c r="D75" s="43"/>
+      <c r="E75" s="43">
         <v>2</v>
       </c>
-      <c r="E75" s="43">
+      <c r="F75" s="43">
         <v>8</v>
       </c>
-      <c r="F75" s="43" t="s">
+      <c r="G75" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H75" s="43"/>
+      <c r="I75" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="J75" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G75" s="43"/>
-      <c r="H75" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="I75" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+      <c r="K75" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B76" s="43">
         <v>41</v>
       </c>
       <c r="C76" s="43"/>
-      <c r="D76" s="43">
+      <c r="D76" s="43"/>
+      <c r="E76" s="43">
         <v>3</v>
       </c>
-      <c r="E76" s="43">
+      <c r="F76" s="43">
         <v>6</v>
       </c>
-      <c r="F76" s="43" t="s">
+      <c r="G76" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H76" s="43"/>
+      <c r="I76" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="J76" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G76" s="43"/>
-      <c r="H76" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="I76" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+      <c r="K76" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B77" s="45">
         <v>44</v>
       </c>
       <c r="C77" s="45"/>
-      <c r="D77" s="45">
+      <c r="D77" s="45"/>
+      <c r="E77" s="45">
         <v>2</v>
       </c>
-      <c r="E77" s="45">
+      <c r="F77" s="45">
         <v>9</v>
       </c>
-      <c r="F77" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="45"/>
-      <c r="H77" s="46">
+      <c r="G77" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" s="45"/>
+      <c r="I77" s="46">
         <v>46124</v>
       </c>
-      <c r="I77" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="J77" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B78" s="45">
         <v>42</v>
       </c>
       <c r="C78" s="45"/>
-      <c r="D78" s="45">
+      <c r="D78" s="45"/>
+      <c r="E78" s="45">
         <v>1</v>
       </c>
-      <c r="E78" s="45">
+      <c r="F78" s="45">
         <v>10</v>
       </c>
-      <c r="F78" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="45"/>
-      <c r="H78" s="46">
+      <c r="G78" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" s="45"/>
+      <c r="I78" s="46">
         <v>46124</v>
       </c>
-      <c r="I78" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="J78" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B79" s="45">
         <v>53</v>
       </c>
       <c r="C79" s="45"/>
-      <c r="D79" s="45">
+      <c r="D79" s="45"/>
+      <c r="E79" s="45">
         <v>3</v>
       </c>
-      <c r="E79" s="45">
+      <c r="F79" s="45">
         <v>8</v>
       </c>
-      <c r="F79" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="45"/>
-      <c r="H79" s="46">
+      <c r="G79" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" s="45"/>
+      <c r="I79" s="46">
         <v>46124</v>
       </c>
-      <c r="I79" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="J79" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" s="45">
         <v>62</v>
       </c>
       <c r="C80" s="45"/>
-      <c r="D80" s="45">
+      <c r="D80" s="45"/>
+      <c r="E80" s="45">
         <v>4</v>
       </c>
-      <c r="E80" s="45">
+      <c r="F80" s="45">
         <v>7</v>
       </c>
-      <c r="F80" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="45"/>
-      <c r="H80" s="46">
+      <c r="G80" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" s="45"/>
+      <c r="I80" s="46">
         <v>46124</v>
       </c>
-      <c r="I80" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B81" s="55">
+        <v>54</v>
+      </c>
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55">
+        <v>3</v>
+      </c>
+      <c r="F81" s="55">
+        <v>8</v>
+      </c>
+      <c r="G81" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81" s="55"/>
+      <c r="I81" s="57">
+        <v>46124</v>
+      </c>
+      <c r="J81" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82" s="55">
+        <v>30</v>
+      </c>
+      <c r="C82" s="55"/>
+      <c r="D82" s="55"/>
+      <c r="E82" s="55">
+        <v>1</v>
+      </c>
+      <c r="F82" s="55">
+        <v>10</v>
+      </c>
+      <c r="G82" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H82" s="55"/>
+      <c r="I82" s="57">
+        <v>46124</v>
+      </c>
+      <c r="J82" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="55">
+        <v>39</v>
+      </c>
+      <c r="C83" s="55"/>
+      <c r="D83" s="55"/>
+      <c r="E83" s="55">
+        <v>2</v>
+      </c>
+      <c r="F83" s="55">
+        <v>9</v>
+      </c>
+      <c r="G83" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H83" s="55"/>
+      <c r="I83" s="57">
+        <v>46124</v>
+      </c>
+      <c r="J83" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="60">
+        <v>50</v>
+      </c>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60">
+        <v>3</v>
+      </c>
+      <c r="F84" s="60">
+        <v>8</v>
+      </c>
+      <c r="G84" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H84" s="60"/>
+      <c r="I84" s="58">
+        <v>46124</v>
+      </c>
+      <c r="J84" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="K84" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="60">
+        <v>46</v>
+      </c>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60">
+        <v>1</v>
+      </c>
+      <c r="F85" s="60">
+        <v>10</v>
+      </c>
+      <c r="G85" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H85" s="60"/>
+      <c r="I85" s="58">
+        <v>46124</v>
+      </c>
+      <c r="J85" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="K85" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B86" s="60">
+        <v>43</v>
+      </c>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60">
+        <v>2</v>
+      </c>
+      <c r="F86" s="60">
+        <v>9</v>
+      </c>
+      <c r="G86" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H86" s="60"/>
+      <c r="I86" s="58">
+        <v>46124</v>
+      </c>
+      <c r="J86" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="K86" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" s="48" customFormat="1">
+      <c r="A87" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="63">
+        <v>27</v>
+      </c>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63">
+        <v>1</v>
+      </c>
+      <c r="F87" s="63">
+        <v>10</v>
+      </c>
+      <c r="G87" s="63" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" s="57" t="s">
+      <c r="H87" s="63"/>
+      <c r="I87" s="64">
+        <v>46152</v>
+      </c>
+      <c r="J87" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="K87" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" s="48" customFormat="1">
+      <c r="A88" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="63">
+        <v>32</v>
+      </c>
+      <c r="C88" s="63"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="63">
+        <v>2</v>
+      </c>
+      <c r="F88" s="63">
+        <v>9</v>
+      </c>
+      <c r="G88" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H88" s="63"/>
+      <c r="I88" s="64">
+        <v>46152</v>
+      </c>
+      <c r="J88" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="K88" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" s="48" customFormat="1">
+      <c r="A89" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B89" s="63">
+        <v>37</v>
+      </c>
+      <c r="C89" s="63"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63">
+        <v>4</v>
+      </c>
+      <c r="F89" s="63">
+        <v>7</v>
+      </c>
+      <c r="G89" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" s="63"/>
+      <c r="I89" s="64">
+        <v>46152</v>
+      </c>
+      <c r="J89" s="63" t="s">
+        <v>78</v>
+      </c>
+      <c r="K89" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" s="48" customFormat="1">
+      <c r="A90" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B90" s="53">
+        <v>38</v>
+      </c>
+      <c r="C90" s="53">
+        <v>12.5</v>
+      </c>
+      <c r="D90" s="53">
+        <v>25</v>
+      </c>
+      <c r="E90" s="53">
+        <v>5</v>
+      </c>
+      <c r="F90" s="53">
+        <v>5</v>
+      </c>
+      <c r="G90" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H90" s="53"/>
+      <c r="I90" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J90" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K90" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" s="48" customFormat="1">
+      <c r="A91" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" s="53">
+        <v>44</v>
+      </c>
+      <c r="C91" s="53">
+        <v>25</v>
+      </c>
+      <c r="D91" s="53">
+        <v>19</v>
+      </c>
+      <c r="E91" s="53">
+        <v>1</v>
+      </c>
+      <c r="F91" s="53">
+        <v>10</v>
+      </c>
+      <c r="G91" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H91" s="53"/>
+      <c r="I91" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J91" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K91" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" s="48" customFormat="1">
+      <c r="A92" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="53">
+        <v>46</v>
+      </c>
+      <c r="C92" s="53">
+        <v>24</v>
+      </c>
+      <c r="D92" s="53">
+        <v>22</v>
+      </c>
+      <c r="E92" s="53">
+        <v>2</v>
+      </c>
+      <c r="F92" s="53">
+        <v>9</v>
+      </c>
+      <c r="G92" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H92" s="53"/>
+      <c r="I92" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J92" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K92" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" s="48" customFormat="1">
+      <c r="A93" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="53">
+        <v>46</v>
+      </c>
+      <c r="C93" s="53">
+        <v>14</v>
+      </c>
+      <c r="D93" s="53">
+        <v>32</v>
+      </c>
+      <c r="E93" s="53">
+        <v>6</v>
+      </c>
+      <c r="F93" s="53">
+        <v>6</v>
+      </c>
+      <c r="G93" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H93" s="53"/>
+      <c r="I93" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J93" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K93" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" s="48" customFormat="1">
+      <c r="A94" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B81" s="57">
-        <v>54</v>
-      </c>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57">
+      <c r="B94" s="53">
+        <v>46</v>
+      </c>
+      <c r="C94" s="53">
+        <v>24</v>
+      </c>
+      <c r="D94" s="53">
+        <v>22</v>
+      </c>
+      <c r="E94" s="53">
         <v>3</v>
       </c>
-      <c r="E81" s="57">
+      <c r="F94" s="53">
         <v>8</v>
       </c>
-      <c r="F81" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G81" s="57"/>
-      <c r="H81" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I81" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="B82" s="57">
+      <c r="G94" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H94" s="53"/>
+      <c r="I94" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J94" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K94" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" s="48" customFormat="1">
+      <c r="A95" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="53">
+        <v>49</v>
+      </c>
+      <c r="C95" s="53">
+        <v>25</v>
+      </c>
+      <c r="D95" s="53">
+        <v>24</v>
+      </c>
+      <c r="E95" s="53">
+        <v>4</v>
+      </c>
+      <c r="F95" s="53">
+        <v>7</v>
+      </c>
+      <c r="G95" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H95" s="53"/>
+      <c r="I95" s="54">
+        <v>46152</v>
+      </c>
+      <c r="J95" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K95" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" s="48" customFormat="1">
+      <c r="A96" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" s="61">
+        <v>46</v>
+      </c>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61">
+        <v>1</v>
+      </c>
+      <c r="F96" s="61">
+        <v>10</v>
+      </c>
+      <c r="G96" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H96" s="61"/>
+      <c r="I96" s="62">
+        <v>46152</v>
+      </c>
+      <c r="J96" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K96" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" s="48" customFormat="1">
+      <c r="A97" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57">
-        <v>1</v>
-      </c>
-      <c r="E82" s="57">
-        <v>10</v>
-      </c>
-      <c r="F82" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G82" s="57"/>
-      <c r="H82" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I82" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="57">
-        <v>39</v>
-      </c>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57">
+      <c r="B97" s="61">
+        <v>48</v>
+      </c>
+      <c r="C97" s="61"/>
+      <c r="D97" s="61"/>
+      <c r="E97" s="61">
         <v>2</v>
       </c>
-      <c r="E83" s="57">
+      <c r="F97" s="61">
         <v>9</v>
       </c>
-      <c r="F83" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G83" s="57"/>
-      <c r="H83" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I83" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="B84" s="57">
-        <v>50</v>
-      </c>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57">
+      <c r="G97" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H97" s="61"/>
+      <c r="I97" s="62">
+        <v>46152</v>
+      </c>
+      <c r="J97" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K97" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="61">
+        <v>53</v>
+      </c>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61">
         <v>3</v>
       </c>
-      <c r="E84" s="57">
+      <c r="F98" s="61">
         <v>8</v>
       </c>
-      <c r="F84" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="G84" s="57"/>
-      <c r="H84" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I84" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B85" s="57">
-        <v>46</v>
-      </c>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57">
-        <v>2</v>
-      </c>
-      <c r="E85" s="57">
-        <v>9</v>
-      </c>
-      <c r="F85" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="G85" s="57"/>
-      <c r="H85" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I85" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="B86" s="57">
-        <v>43</v>
-      </c>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57">
-        <v>1</v>
-      </c>
-      <c r="E86" s="57">
-        <v>10</v>
-      </c>
-      <c r="F86" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="G86" s="57"/>
-      <c r="H86" s="59">
-        <v>46124</v>
-      </c>
-      <c r="I86" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" s="48" customFormat="1">
-      <c r="A87" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="B87" s="55">
-        <v>27</v>
-      </c>
-      <c r="C87" s="55"/>
-      <c r="D87" s="55">
-        <v>1</v>
-      </c>
-      <c r="E87" s="55">
-        <v>10</v>
-      </c>
-      <c r="F87" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G87" s="55"/>
-      <c r="H87" s="56">
+      <c r="G98" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H98" s="61"/>
+      <c r="I98" s="62">
         <v>46152</v>
       </c>
-      <c r="I87" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J87" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" s="48" customFormat="1">
-      <c r="A88" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B88" s="55">
-        <v>32</v>
-      </c>
-      <c r="C88" s="55"/>
-      <c r="D88" s="55">
-        <v>2</v>
-      </c>
-      <c r="E88" s="55">
-        <v>9</v>
-      </c>
-      <c r="F88" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G88" s="55"/>
-      <c r="H88" s="56">
+      <c r="J98" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="K98" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" s="61">
+        <v>72</v>
+      </c>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61">
+        <v>4</v>
+      </c>
+      <c r="F99" s="61">
+        <v>7</v>
+      </c>
+      <c r="G99" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H99" s="61"/>
+      <c r="I99" s="62">
         <v>46152</v>
       </c>
-      <c r="I88" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J88" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" s="48" customFormat="1">
-      <c r="A89" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="B89" s="55">
-        <v>37</v>
-      </c>
-      <c r="C89" s="55"/>
-      <c r="D89" s="55">
-        <v>4</v>
-      </c>
-      <c r="E89" s="55">
-        <v>7</v>
-      </c>
-      <c r="F89" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G89" s="55"/>
-      <c r="H89" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I89" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J89" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" s="48" customFormat="1">
-      <c r="A90" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="B90" s="55">
-        <v>49</v>
-      </c>
-      <c r="C90" s="55"/>
-      <c r="D90" s="55">
-        <v>9</v>
-      </c>
-      <c r="E90" s="55">
-        <v>3</v>
-      </c>
-      <c r="F90" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G90" s="55"/>
-      <c r="H90" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I90" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J90" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" s="48" customFormat="1">
-      <c r="A91" s="55" t="s">
-        <v>82</v>
-      </c>
-      <c r="B91" s="55">
-        <v>38</v>
-      </c>
-      <c r="C91" s="55"/>
-      <c r="D91" s="55">
-        <v>3</v>
-      </c>
-      <c r="E91" s="55">
-        <v>8</v>
-      </c>
-      <c r="F91" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G91" s="55"/>
-      <c r="H91" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I91" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J91" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" s="48" customFormat="1">
-      <c r="A92" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="B92" s="55">
-        <v>44</v>
-      </c>
-      <c r="C92" s="55"/>
-      <c r="D92" s="55">
-        <v>5</v>
-      </c>
-      <c r="E92" s="55">
-        <v>7</v>
-      </c>
-      <c r="F92" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G92" s="55"/>
-      <c r="H92" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I92" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J92" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" s="48" customFormat="1">
-      <c r="A93" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="B93" s="55">
-        <v>46</v>
-      </c>
-      <c r="C93" s="55"/>
-      <c r="D93" s="55">
-        <v>6</v>
-      </c>
-      <c r="E93" s="55">
-        <v>6</v>
-      </c>
-      <c r="F93" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G93" s="55"/>
-      <c r="H93" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I93" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J93" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" s="48" customFormat="1">
-      <c r="A94" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="B94" s="55">
-        <v>46</v>
-      </c>
-      <c r="C94" s="55"/>
-      <c r="D94" s="55">
-        <v>7</v>
-      </c>
-      <c r="E94" s="55">
-        <v>5</v>
-      </c>
-      <c r="F94" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G94" s="55"/>
-      <c r="H94" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I94" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J94" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" s="48" customFormat="1">
-      <c r="A95" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="B95" s="55">
-        <v>46</v>
-      </c>
-      <c r="C95" s="55"/>
-      <c r="D95" s="55">
-        <v>8</v>
-      </c>
-      <c r="E95" s="55">
-        <v>4</v>
-      </c>
-      <c r="F95" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="G95" s="55"/>
-      <c r="H95" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I95" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="J95" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" s="48" customFormat="1">
-      <c r="A96" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B96" s="55">
-        <v>46</v>
-      </c>
-      <c r="C96" s="55"/>
-      <c r="D96" s="55">
-        <v>1</v>
-      </c>
-      <c r="E96" s="55">
-        <v>10</v>
-      </c>
-      <c r="F96" s="55" t="s">
+      <c r="J99" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="G96" s="55"/>
-      <c r="H96" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I96" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="J96" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" s="48" customFormat="1">
-      <c r="A97" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" s="55">
-        <v>48</v>
-      </c>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55">
-        <v>2</v>
-      </c>
-      <c r="E97" s="55">
-        <v>9</v>
-      </c>
-      <c r="F97" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="G97" s="55"/>
-      <c r="H97" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I97" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="J97" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="B98" s="55">
-        <v>53</v>
-      </c>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55">
-        <v>3</v>
-      </c>
-      <c r="E98" s="55">
-        <v>8</v>
-      </c>
-      <c r="F98" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="G98" s="55"/>
-      <c r="H98" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I98" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="J98" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="B99" s="55">
-        <v>72</v>
-      </c>
-      <c r="C99" s="55"/>
-      <c r="D99" s="55">
-        <v>4</v>
-      </c>
-      <c r="E99" s="55">
-        <v>7</v>
-      </c>
-      <c r="F99" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="G99" s="55"/>
-      <c r="H99" s="56">
-        <v>46152</v>
-      </c>
-      <c r="I99" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="J99" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" s="53"/>
-      <c r="B100" s="53"/>
-      <c r="C100" s="53"/>
-      <c r="D100" s="53"/>
-      <c r="E100" s="53"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
-      <c r="H100" s="54"/>
-      <c r="I100" s="53"/>
-      <c r="J100" s="48"/>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" s="53"/>
-      <c r="B101" s="53"/>
-      <c r="C101" s="53"/>
-      <c r="D101" s="53"/>
-      <c r="E101" s="53"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
-      <c r="H101" s="54"/>
-      <c r="I101" s="53"/>
-      <c r="J101" s="48"/>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="53"/>
-      <c r="B102" s="53"/>
-      <c r="C102" s="53"/>
-      <c r="D102" s="53"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="54"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="48"/>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="53"/>
-      <c r="B103" s="53"/>
-      <c r="C103" s="53"/>
-      <c r="D103" s="53"/>
-      <c r="E103" s="53"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="54"/>
-      <c r="I103" s="53"/>
-      <c r="J103" s="48"/>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="53"/>
-      <c r="B104" s="53"/>
-      <c r="C104" s="53"/>
-      <c r="D104" s="53"/>
-      <c r="E104" s="53"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="54"/>
-      <c r="I104" s="53"/>
-      <c r="J104" s="48"/>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="53"/>
-      <c r="B105" s="53"/>
-      <c r="C105" s="53"/>
-      <c r="D105" s="53"/>
-      <c r="E105" s="53"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="54"/>
-      <c r="I105" s="53"/>
-      <c r="J105" s="48"/>
+      <c r="K99" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="I102" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I99"/>
+  <autoFilter ref="A1:J99"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
@@ -3840,10 +3943,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1">
       <c r="A1" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="50" t="s">
         <v>70</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>71</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -3858,10 +3961,10 @@
     </row>
     <row r="3" spans="1:5" ht="13.5" customHeight="1">
       <c r="A3" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -3869,7 +3972,7 @@
     </row>
     <row r="4" spans="1:5" ht="13.5" customHeight="1">
       <c r="A4" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="51">
         <v>2026</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3431,8 +3431,12 @@
       <c r="B84" s="60">
         <v>50</v>
       </c>
-      <c r="C84" s="60"/>
-      <c r="D84" s="60"/>
+      <c r="C84" s="60">
+        <v>24</v>
+      </c>
+      <c r="D84" s="60">
+        <v>26</v>
+      </c>
       <c r="E84" s="60">
         <v>3</v>
       </c>
@@ -3460,8 +3464,12 @@
       <c r="B85" s="60">
         <v>46</v>
       </c>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
+      <c r="C85" s="60">
+        <v>30</v>
+      </c>
+      <c r="D85" s="60">
+        <v>16</v>
+      </c>
       <c r="E85" s="60">
         <v>1</v>
       </c>
@@ -3489,8 +3497,12 @@
       <c r="B86" s="60">
         <v>43</v>
       </c>
-      <c r="C86" s="60"/>
-      <c r="D86" s="60"/>
+      <c r="C86" s="60">
+        <v>19</v>
+      </c>
+      <c r="D86" s="60">
+        <v>24</v>
+      </c>
       <c r="E86" s="60">
         <v>2</v>
       </c>
@@ -3606,7 +3618,7 @@
         <v>38</v>
       </c>
       <c r="C90" s="53">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="D90" s="53">
         <v>25</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3756,10 +3756,10 @@
         <v>22</v>
       </c>
       <c r="E94" s="53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94" s="53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G94" s="53" t="s">
         <v>89</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -1001,7 +1001,7 @@
     <col min="1" max="1" width="22.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.54296875" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.1796875" style="1" bestFit="1" customWidth="1"/>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -60,9 +60,6 @@
     <t>June 9 Hole</t>
   </si>
   <si>
-    <t>June Junior Competition</t>
-  </si>
-  <si>
     <t>Matthew Owens</t>
   </si>
   <si>
@@ -90,18 +87,12 @@
     <t>July 9 Hole</t>
   </si>
   <si>
-    <t>July Junior Competition</t>
-  </si>
-  <si>
     <t>Parker Holt</t>
   </si>
   <si>
     <t>August 9 Hole</t>
   </si>
   <si>
-    <t xml:space="preserve">August Junior Competition </t>
-  </si>
-  <si>
     <t>Louie Walker</t>
   </si>
   <si>
@@ -111,9 +102,6 @@
     <t>13/04/2025</t>
   </si>
   <si>
-    <t>April Junior Competition</t>
-  </si>
-  <si>
     <t>Tenzing Lo</t>
   </si>
   <si>
@@ -186,9 +174,6 @@
     <t>14/09/2025</t>
   </si>
   <si>
-    <t>September Junior Competition</t>
-  </si>
-  <si>
     <t>September Sixes</t>
   </si>
   <si>
@@ -210,9 +195,6 @@
     <t>19/10/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">October Junior Competition </t>
-  </si>
-  <si>
     <t>October Sixes</t>
   </si>
   <si>
@@ -228,9 +210,6 @@
     <t>09/11/2025</t>
   </si>
   <si>
-    <t>November Junior Competitions</t>
-  </si>
-  <si>
     <t>November Sixes</t>
   </si>
   <si>
@@ -279,9 +258,6 @@
     <t>May 9 Hole</t>
   </si>
   <si>
-    <t xml:space="preserve">May Junior Competition </t>
-  </si>
-  <si>
     <t>Mollie Williams</t>
   </si>
   <si>
@@ -304,6 +280,36 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>April Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April Junior Competition Sixes </t>
+  </si>
+  <si>
+    <t>May Junior Competition -9 Hole</t>
+  </si>
+  <si>
+    <t>June Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t>August Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t>April Junior Competition -9 Hole</t>
+  </si>
+  <si>
+    <t>July Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t>September Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t>October Junior Competition - 9 Hole</t>
+  </si>
+  <si>
+    <t>November Junior Competition -9 Hole</t>
   </si>
 </sst>
 </file>
@@ -1019,10 +1025,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>2</v>
@@ -1043,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1069,15 +1075,15 @@
         <v>45449</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6">
         <v>64</v>
@@ -1098,15 +1104,15 @@
         <v>45449</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6">
         <v>48</v>
@@ -1127,15 +1133,15 @@
         <v>45449</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6">
         <v>52</v>
@@ -1156,15 +1162,15 @@
         <v>45449</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6">
         <v>51</v>
@@ -1178,22 +1184,22 @@
         <v>8</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="7">
         <v>45449</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6">
         <v>49</v>
@@ -1207,22 +1213,22 @@
         <v>10</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7">
         <v>45449</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="6">
         <v>58</v>
@@ -1236,22 +1242,22 @@
         <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7">
         <v>45501</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6">
         <v>55</v>
@@ -1265,22 +1271,22 @@
         <v>8</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7">
         <v>45501</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="6">
         <v>39</v>
@@ -1294,22 +1300,22 @@
         <v>10</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7">
         <v>45501</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6">
         <v>53</v>
@@ -1323,17 +1329,17 @@
         <v>8</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="7">
         <v>45522</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1352,22 +1358,22 @@
         <v>10</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7">
         <v>45522</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" s="9">
         <v>47</v>
@@ -1381,22 +1387,22 @@
         <v>10</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.5" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B14" s="9">
         <v>53</v>
@@ -1410,22 +1416,22 @@
         <v>8</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B15" s="9">
         <v>55</v>
@@ -1439,22 +1445,22 @@
         <v>6</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="9">
         <v>56</v>
@@ -1468,22 +1474,22 @@
         <v>5</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B17" s="9">
         <v>60</v>
@@ -1497,22 +1503,22 @@
         <v>4</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B18" s="9">
         <v>74</v>
@@ -1526,22 +1532,22 @@
         <v>3</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B19" s="9">
         <v>78</v>
@@ -1555,22 +1561,22 @@
         <v>2</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B20" s="9">
         <v>79</v>
@@ -1584,22 +1590,22 @@
         <v>1</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B21" s="12">
         <v>30</v>
@@ -1613,22 +1619,22 @@
         <v>10</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="13.5" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B22" s="12">
         <v>45</v>
@@ -1642,22 +1648,22 @@
         <v>8</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" s="15">
         <v>50</v>
@@ -1675,18 +1681,18 @@
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="15">
         <v>57</v>
@@ -1704,18 +1710,18 @@
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B25" s="15">
         <v>65</v>
@@ -1733,18 +1739,18 @@
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B26" s="15">
         <v>76</v>
@@ -1762,18 +1768,18 @@
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="13.5" customHeight="1">
       <c r="A27" s="17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" s="18">
         <v>30</v>
@@ -1787,22 +1793,22 @@
         <v>10</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" s="18"/>
       <c r="I27" s="19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1">
       <c r="A28" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="18">
         <v>47</v>
@@ -1816,22 +1822,22 @@
         <v>8</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B29" s="18">
         <v>53</v>
@@ -1845,22 +1851,22 @@
         <v>6</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B30" s="21">
         <v>45</v>
@@ -1874,22 +1880,22 @@
         <v>10</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13.5" customHeight="1">
       <c r="A31" s="20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B31" s="21">
         <v>47</v>
@@ -1903,22 +1909,22 @@
         <v>8</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" s="21">
         <v>58</v>
@@ -1932,22 +1938,22 @@
         <v>6</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="24">
         <v>28</v>
@@ -1961,22 +1967,22 @@
         <v>10</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H33" s="24"/>
       <c r="I33" s="25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B34" s="24">
         <v>44</v>
@@ -1990,22 +1996,22 @@
         <v>8</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H34" s="24"/>
       <c r="I34" s="25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J34" s="23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B35" s="27">
         <v>38</v>
@@ -2019,22 +2025,22 @@
         <v>10</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H35" s="27"/>
       <c r="I35" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J35" s="29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B36" s="27">
         <v>60</v>
@@ -2048,22 +2054,22 @@
         <v>4</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B37" s="27">
         <v>56</v>
@@ -2077,22 +2083,22 @@
         <v>5</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H37" s="27"/>
       <c r="I37" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" s="27">
         <v>47</v>
@@ -2106,17 +2112,17 @@
         <v>6</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
@@ -2135,22 +2141,22 @@
         <v>8</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H39" s="27"/>
       <c r="I39" s="28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J39" s="29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B40" s="31">
         <v>32</v>
@@ -2164,22 +2170,22 @@
         <v>10</v>
       </c>
       <c r="G40" s="32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H40" s="31"/>
       <c r="I40" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B41" s="31">
         <v>34</v>
@@ -2193,22 +2199,22 @@
         <v>8</v>
       </c>
       <c r="G41" s="32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J41" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B42" s="31">
         <v>35</v>
@@ -2222,22 +2228,22 @@
         <v>6</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J42" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B43" s="31">
         <v>39</v>
@@ -2251,22 +2257,22 @@
         <v>5</v>
       </c>
       <c r="G43" s="32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H43" s="31"/>
       <c r="I43" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B44" s="31">
         <v>46</v>
@@ -2280,22 +2286,22 @@
         <v>4</v>
       </c>
       <c r="G44" s="32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H44" s="31"/>
       <c r="I44" s="33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J44" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B45" s="18">
         <v>49</v>
@@ -2309,22 +2315,22 @@
         <v>10</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="18">
         <v>49</v>
@@ -2338,22 +2344,22 @@
         <v>8</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B47" s="18">
         <v>53</v>
@@ -2367,22 +2373,22 @@
         <v>6</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B48" s="18">
         <v>58</v>
@@ -2396,22 +2402,22 @@
         <v>5</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="18">
         <v>61</v>
@@ -2425,22 +2431,22 @@
         <v>4</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B50" s="18">
         <v>63</v>
@@ -2454,22 +2460,22 @@
         <v>3</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H50" s="18"/>
       <c r="I50" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B51" s="35">
         <v>33</v>
@@ -2483,22 +2489,22 @@
         <v>10</v>
       </c>
       <c r="G51" s="35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H51" s="35"/>
       <c r="I51" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B52" s="35">
         <v>41</v>
@@ -2512,22 +2518,22 @@
         <v>6</v>
       </c>
       <c r="G52" s="35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H52" s="35"/>
       <c r="I52" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1">
       <c r="A53" s="34" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B53" s="35">
         <v>38</v>
@@ -2541,22 +2547,22 @@
         <v>8</v>
       </c>
       <c r="G53" s="35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H53" s="35"/>
       <c r="I53" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B54" s="35">
         <v>44</v>
@@ -2570,22 +2576,22 @@
         <v>5</v>
       </c>
       <c r="G54" s="35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H54" s="35"/>
       <c r="I54" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J54" s="34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B55" s="35">
         <v>51</v>
@@ -2599,22 +2605,22 @@
         <v>4</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H55" s="35"/>
       <c r="I55" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J55" s="34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B56" s="37">
         <v>45</v>
@@ -2628,22 +2634,22 @@
         <v>10</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H56" s="37"/>
       <c r="I56" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B57" s="37">
         <v>58</v>
@@ -2657,22 +2663,22 @@
         <v>3</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H57" s="37"/>
       <c r="I57" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="37">
         <v>56</v>
@@ -2686,22 +2692,22 @@
         <v>4</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H58" s="37"/>
       <c r="I58" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B59" s="37">
         <v>48</v>
@@ -2715,22 +2721,22 @@
         <v>8</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H59" s="37"/>
       <c r="I59" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B60" s="37">
         <v>51</v>
@@ -2744,22 +2750,22 @@
         <v>6</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H60" s="37"/>
       <c r="I60" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B61" s="37">
         <v>66</v>
@@ -2773,22 +2779,22 @@
         <v>1</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H61" s="37"/>
       <c r="I61" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B62" s="37">
         <v>62</v>
@@ -2802,22 +2808,22 @@
         <v>2</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H62" s="37"/>
       <c r="I62" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B63" s="37">
         <v>55</v>
@@ -2831,22 +2837,22 @@
         <v>5</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H63" s="37"/>
       <c r="I63" s="38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J63" s="37" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B64" s="39">
         <v>32</v>
@@ -2860,22 +2866,22 @@
         <v>10</v>
       </c>
       <c r="G64" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H64" s="39"/>
       <c r="I64" s="40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1">
       <c r="A65" s="39" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B65" s="39">
         <v>34</v>
@@ -2889,22 +2895,22 @@
         <v>8</v>
       </c>
       <c r="G65" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H65" s="39"/>
       <c r="I65" s="40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J65" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B66" s="39">
         <v>49</v>
@@ -2918,22 +2924,22 @@
         <v>5</v>
       </c>
       <c r="G66" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H66" s="39"/>
       <c r="I66" s="40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J66" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B67" s="39">
         <v>37</v>
@@ -2947,22 +2953,22 @@
         <v>6</v>
       </c>
       <c r="G67" s="39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H67" s="39"/>
       <c r="I67" s="40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J67" s="39" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="41" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B68" s="41">
         <v>47</v>
@@ -2976,22 +2982,22 @@
         <v>10</v>
       </c>
       <c r="G68" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H68" s="41"/>
       <c r="I68" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J68" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="41" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B69" s="41">
         <v>48</v>
@@ -3005,22 +3011,22 @@
         <v>8</v>
       </c>
       <c r="G69" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H69" s="41"/>
       <c r="I69" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B70" s="41">
         <v>48</v>
@@ -3034,22 +3040,22 @@
         <v>6</v>
       </c>
       <c r="G70" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H70" s="41"/>
       <c r="I70" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J70" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B71" s="41">
         <v>49</v>
@@ -3063,22 +3069,22 @@
         <v>5</v>
       </c>
       <c r="G71" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J71" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" s="41">
         <v>52</v>
@@ -3092,22 +3098,22 @@
         <v>4</v>
       </c>
       <c r="G72" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H72" s="41"/>
       <c r="I72" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J72" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B73" s="41">
         <v>62</v>
@@ -3121,22 +3127,22 @@
         <v>3</v>
       </c>
       <c r="G73" s="41" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H73" s="41"/>
       <c r="I73" s="42" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J73" s="41" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="43" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B74" s="43">
         <v>30</v>
@@ -3150,22 +3156,22 @@
         <v>10</v>
       </c>
       <c r="G74" s="43" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H74" s="43"/>
       <c r="I74" s="44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J74" s="43" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="43" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B75" s="43">
         <v>34</v>
@@ -3179,22 +3185,22 @@
         <v>8</v>
       </c>
       <c r="G75" s="43" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H75" s="43"/>
       <c r="I75" s="44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J75" s="43" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="43" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B76" s="43">
         <v>41</v>
@@ -3208,22 +3214,22 @@
         <v>6</v>
       </c>
       <c r="G76" s="43" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H76" s="43"/>
       <c r="I76" s="44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J76" s="43" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="45" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B77" s="45">
         <v>44</v>
@@ -3237,22 +3243,22 @@
         <v>9</v>
       </c>
       <c r="G77" s="45" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H77" s="45"/>
       <c r="I77" s="46">
         <v>46124</v>
       </c>
       <c r="J77" s="45" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="45" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B78" s="45">
         <v>42</v>
@@ -3266,22 +3272,22 @@
         <v>10</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H78" s="45"/>
       <c r="I78" s="46">
         <v>46124</v>
       </c>
-      <c r="J78" s="47" t="s">
-        <v>27</v>
+      <c r="J78" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="45" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B79" s="45">
         <v>53</v>
@@ -3295,22 +3301,22 @@
         <v>8</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="46">
         <v>46124</v>
       </c>
-      <c r="J79" s="47" t="s">
-        <v>27</v>
+      <c r="J79" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="45" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B80" s="45">
         <v>62</v>
@@ -3324,22 +3330,22 @@
         <v>7</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H80" s="45"/>
       <c r="I80" s="46">
         <v>46124</v>
       </c>
-      <c r="J80" s="47" t="s">
-        <v>27</v>
+      <c r="J80" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="55" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B81" s="55">
         <v>54</v>
@@ -3353,22 +3359,22 @@
         <v>8</v>
       </c>
       <c r="G81" s="56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H81" s="55"/>
       <c r="I81" s="57">
         <v>46124</v>
       </c>
       <c r="J81" s="56" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="55" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B82" s="55">
         <v>30</v>
@@ -3382,22 +3388,22 @@
         <v>10</v>
       </c>
       <c r="G82" s="56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H82" s="55"/>
       <c r="I82" s="57">
         <v>46124</v>
       </c>
       <c r="J82" s="56" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="55" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B83" s="55">
         <v>39</v>
@@ -3411,22 +3417,22 @@
         <v>9</v>
       </c>
       <c r="G83" s="56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H83" s="55"/>
       <c r="I83" s="57">
         <v>46124</v>
       </c>
       <c r="J83" s="56" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="60" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B84" s="60">
         <v>50</v>
@@ -3444,22 +3450,22 @@
         <v>8</v>
       </c>
       <c r="G84" s="59" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" s="60"/>
       <c r="I84" s="58">
         <v>46124</v>
       </c>
       <c r="J84" s="59" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K84" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="60" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B85" s="60">
         <v>46</v>
@@ -3477,22 +3483,22 @@
         <v>10</v>
       </c>
       <c r="G85" s="59" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" s="60"/>
       <c r="I85" s="58">
         <v>46124</v>
       </c>
       <c r="J85" s="59" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K85" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="60" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B86" s="60">
         <v>43</v>
@@ -3510,22 +3516,22 @@
         <v>9</v>
       </c>
       <c r="G86" s="59" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" s="60"/>
       <c r="I86" s="58">
         <v>46124</v>
       </c>
       <c r="J86" s="59" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K86" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="48" customFormat="1">
       <c r="A87" s="63" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B87" s="63">
         <v>27</v>
@@ -3539,22 +3545,22 @@
         <v>10</v>
       </c>
       <c r="G87" s="63" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H87" s="63"/>
       <c r="I87" s="64">
         <v>46152</v>
       </c>
       <c r="J87" s="63" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="48" customFormat="1">
       <c r="A88" s="63" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B88" s="63">
         <v>32</v>
@@ -3568,22 +3574,22 @@
         <v>9</v>
       </c>
       <c r="G88" s="63" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H88" s="63"/>
       <c r="I88" s="64">
         <v>46152</v>
       </c>
       <c r="J88" s="63" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K88" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="48" customFormat="1">
       <c r="A89" s="63" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B89" s="63">
         <v>37</v>
@@ -3597,22 +3603,22 @@
         <v>7</v>
       </c>
       <c r="G89" s="63" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H89" s="63"/>
       <c r="I89" s="64">
         <v>46152</v>
       </c>
       <c r="J89" s="63" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K89" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="48" customFormat="1">
       <c r="A90" s="53" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B90" s="53">
         <v>38</v>
@@ -3630,22 +3636,22 @@
         <v>5</v>
       </c>
       <c r="G90" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H90" s="53"/>
       <c r="I90" s="54">
         <v>46152</v>
       </c>
       <c r="J90" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K90" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="48" customFormat="1">
       <c r="A91" s="53" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B91" s="53">
         <v>44</v>
@@ -3663,22 +3669,22 @@
         <v>10</v>
       </c>
       <c r="G91" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H91" s="53"/>
       <c r="I91" s="54">
         <v>46152</v>
       </c>
       <c r="J91" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K91" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="48" customFormat="1">
       <c r="A92" s="53" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B92" s="53">
         <v>46</v>
@@ -3696,22 +3702,22 @@
         <v>9</v>
       </c>
       <c r="G92" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H92" s="53"/>
       <c r="I92" s="54">
         <v>46152</v>
       </c>
       <c r="J92" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K92" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="48" customFormat="1">
       <c r="A93" s="53" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B93" s="53">
         <v>46</v>
@@ -3729,22 +3735,22 @@
         <v>6</v>
       </c>
       <c r="G93" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H93" s="53"/>
       <c r="I93" s="54">
         <v>46152</v>
       </c>
       <c r="J93" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K93" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="48" customFormat="1">
       <c r="A94" s="53" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B94" s="53">
         <v>46</v>
@@ -3762,22 +3768,22 @@
         <v>9</v>
       </c>
       <c r="G94" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H94" s="53"/>
       <c r="I94" s="54">
         <v>46152</v>
       </c>
       <c r="J94" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K94" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="48" customFormat="1">
       <c r="A95" s="53" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B95" s="53">
         <v>49</v>
@@ -3795,22 +3801,22 @@
         <v>7</v>
       </c>
       <c r="G95" s="53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H95" s="53"/>
       <c r="I95" s="54">
         <v>46152</v>
       </c>
       <c r="J95" s="53" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K95" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="48" customFormat="1">
       <c r="A96" s="61" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B96" s="61">
         <v>46</v>
@@ -3824,22 +3830,22 @@
         <v>10</v>
       </c>
       <c r="G96" s="61" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H96" s="61"/>
       <c r="I96" s="62">
         <v>46152</v>
       </c>
       <c r="J96" s="61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K96" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="48" customFormat="1">
       <c r="A97" s="61" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B97" s="61">
         <v>48</v>
@@ -3853,22 +3859,22 @@
         <v>9</v>
       </c>
       <c r="G97" s="61" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H97" s="61"/>
       <c r="I97" s="62">
         <v>46152</v>
       </c>
       <c r="J97" s="61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="61" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B98" s="61">
         <v>53</v>
@@ -3882,22 +3888,22 @@
         <v>8</v>
       </c>
       <c r="G98" s="61" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H98" s="61"/>
       <c r="I98" s="62">
         <v>46152</v>
       </c>
       <c r="J98" s="61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K98" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="61" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B99" s="61">
         <v>72</v>
@@ -3911,17 +3917,17 @@
         <v>7</v>
       </c>
       <c r="G99" s="61" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H99" s="61"/>
       <c r="I99" s="62">
         <v>46152</v>
       </c>
       <c r="J99" s="61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -3955,10 +3961,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -3973,10 +3979,10 @@
     </row>
     <row r="3" spans="1:5" ht="13.5" customHeight="1">
       <c r="A3" s="50" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -3984,7 +3990,7 @@
     </row>
     <row r="4" spans="1:5" ht="13.5" customHeight="1">
       <c r="A4" s="51" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B4" s="51">
         <v>2026</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Points</t>
   </si>
   <si>
-    <t>Competition</t>
-  </si>
-  <si>
     <t>Winnings</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>June Sixes</t>
   </si>
   <si>
-    <t>June Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>Harry Taylor</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>April Sixes</t>
   </si>
   <si>
-    <t>April Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>Milo Bearne</t>
   </si>
   <si>
@@ -144,9 +135,6 @@
     <t>July Sixes</t>
   </si>
   <si>
-    <t>July Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>William Bailey</t>
   </si>
   <si>
@@ -159,9 +147,6 @@
     <t>August Sixes</t>
   </si>
   <si>
-    <t>August Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>Bobby Sharples</t>
   </si>
   <si>
@@ -177,9 +162,6 @@
     <t>September Sixes</t>
   </si>
   <si>
-    <t>September Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>Stanley Habershow</t>
   </si>
   <si>
@@ -198,9 +180,6 @@
     <t>October Sixes</t>
   </si>
   <si>
-    <t>October Junior Competition Sixes</t>
-  </si>
-  <si>
     <t>Frankie</t>
   </si>
   <si>
@@ -213,9 +192,6 @@
     <t>November Sixes</t>
   </si>
   <si>
-    <t>November Junior Competitions Sixes</t>
-  </si>
-  <si>
     <t>Key</t>
   </si>
   <si>
@@ -243,9 +219,6 @@
     <t>May Sixes</t>
   </si>
   <si>
-    <t>May Junior Competition Sixes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Issac Hibbert </t>
   </si>
   <si>
@@ -264,15 +237,9 @@
     <t>14 June 2026 | 13:00 - 14:00 Tee Times | Summer Round 1</t>
   </si>
   <si>
-    <t>April Junior Competition Sixes Beginners</t>
-  </si>
-  <si>
     <t>April Sixes -Beginners</t>
   </si>
   <si>
-    <t>May Junior Competition Sixes Beginners</t>
-  </si>
-  <si>
     <t>May Sixes - Beginners</t>
   </si>
   <si>
@@ -282,34 +249,64 @@
     <t>Total</t>
   </si>
   <si>
-    <t>April Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April Junior Competition Sixes </t>
-  </si>
-  <si>
-    <t>May Junior Competition -9 Hole</t>
-  </si>
-  <si>
-    <t>June Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t>August Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t>April Junior Competition -9 Hole</t>
-  </si>
-  <si>
-    <t>July Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t>September Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t>October Junior Competition - 9 Hole</t>
-  </si>
-  <si>
-    <t>November Junior Competition -9 Hole</t>
+    <t>June   - 9 Hole</t>
+  </si>
+  <si>
+    <t>June   Sixes</t>
+  </si>
+  <si>
+    <t>August   - 9 Hole</t>
+  </si>
+  <si>
+    <t>April   -9 Hole</t>
+  </si>
+  <si>
+    <t>April   Sixes</t>
+  </si>
+  <si>
+    <t>July   - 9 Hole</t>
+  </si>
+  <si>
+    <t>July   Sixes</t>
+  </si>
+  <si>
+    <t>August   Sixes</t>
+  </si>
+  <si>
+    <t>September   - 9 Hole</t>
+  </si>
+  <si>
+    <t>September   Sixes</t>
+  </si>
+  <si>
+    <t>October   - 9 Hole</t>
+  </si>
+  <si>
+    <t>October   Sixes</t>
+  </si>
+  <si>
+    <t>November   -9 Hole</t>
+  </si>
+  <si>
+    <t>November  s Sixes</t>
+  </si>
+  <si>
+    <t>April   - 9 Hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April   Sixes </t>
+  </si>
+  <si>
+    <t>May   Sixes</t>
+  </si>
+  <si>
+    <t>May   -9 Hole</t>
+  </si>
+  <si>
+    <t>April   Sixes (Beginners)</t>
+  </si>
+  <si>
+    <t>May   Sixes (Beginners)</t>
   </si>
 </sst>
 </file>
@@ -1025,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>2</v>
@@ -1036,25 +1033,23 @@
       <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="6">
         <v>40</v>
@@ -1068,22 +1063,22 @@
         <v>10</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="7">
         <v>45449</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="6">
         <v>64</v>
@@ -1097,22 +1092,22 @@
         <v>5</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="7">
         <v>45449</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6">
         <v>48</v>
@@ -1126,22 +1121,22 @@
         <v>8</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="7">
         <v>45449</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6">
         <v>52</v>
@@ -1155,22 +1150,22 @@
         <v>6</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="7">
         <v>45449</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6">
         <v>51</v>
@@ -1184,22 +1179,22 @@
         <v>8</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="7">
         <v>45449</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6">
         <v>49</v>
@@ -1213,22 +1208,22 @@
         <v>10</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7">
         <v>45449</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="6">
         <v>58</v>
@@ -1242,22 +1237,22 @@
         <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7">
         <v>45501</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6">
         <v>55</v>
@@ -1271,22 +1266,22 @@
         <v>8</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7">
         <v>45501</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6">
         <v>39</v>
@@ -1300,22 +1295,22 @@
         <v>10</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7">
         <v>45501</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="6">
         <v>53</v>
@@ -1329,22 +1324,22 @@
         <v>8</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="7">
         <v>45522</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6">
         <v>46</v>
@@ -1358,22 +1353,22 @@
         <v>10</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7">
         <v>45522</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="9">
         <v>47</v>
@@ -1387,22 +1382,22 @@
         <v>10</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.5" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="9">
         <v>53</v>
@@ -1416,22 +1411,22 @@
         <v>8</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="9">
         <v>55</v>
@@ -1445,22 +1440,22 @@
         <v>6</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="9">
         <v>56</v>
@@ -1474,22 +1469,22 @@
         <v>5</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="9">
         <v>60</v>
@@ -1503,22 +1498,22 @@
         <v>4</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="9">
         <v>74</v>
@@ -1532,22 +1527,22 @@
         <v>3</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="9">
         <v>78</v>
@@ -1561,22 +1556,22 @@
         <v>2</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="9">
         <v>79</v>
@@ -1590,22 +1585,22 @@
         <v>1</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="12">
         <v>30</v>
@@ -1619,22 +1614,22 @@
         <v>10</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="13.5" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B22" s="12">
         <v>45</v>
@@ -1648,22 +1643,22 @@
         <v>8</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="15">
         <v>50</v>
@@ -1677,22 +1672,22 @@
         <v>10</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="13.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="15">
         <v>57</v>
@@ -1706,22 +1701,22 @@
         <v>8</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="15">
         <v>65</v>
@@ -1735,22 +1730,22 @@
         <v>6</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B26" s="15">
         <v>76</v>
@@ -1764,22 +1759,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="13.5" customHeight="1">
       <c r="A27" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B27" s="18">
         <v>30</v>
@@ -1793,22 +1788,22 @@
         <v>10</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" s="18"/>
       <c r="I27" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1">
       <c r="A28" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B28" s="18">
         <v>47</v>
@@ -1822,22 +1817,22 @@
         <v>8</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B29" s="18">
         <v>53</v>
@@ -1851,22 +1846,22 @@
         <v>6</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B30" s="21">
         <v>45</v>
@@ -1880,22 +1875,22 @@
         <v>10</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="13.5" customHeight="1">
       <c r="A31" s="20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B31" s="21">
         <v>47</v>
@@ -1909,22 +1904,22 @@
         <v>8</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" s="21">
         <v>58</v>
@@ -1938,22 +1933,22 @@
         <v>6</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H32" s="21"/>
       <c r="I32" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="24">
         <v>28</v>
@@ -1967,22 +1962,22 @@
         <v>10</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H33" s="24"/>
       <c r="I33" s="25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34" s="24">
         <v>44</v>
@@ -1996,22 +1991,22 @@
         <v>8</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H34" s="24"/>
       <c r="I34" s="25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J34" s="23" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" s="27">
         <v>38</v>
@@ -2025,22 +2020,22 @@
         <v>10</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H35" s="27"/>
       <c r="I35" s="28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J35" s="29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B36" s="27">
         <v>60</v>
@@ -2054,22 +2049,22 @@
         <v>4</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" s="27">
         <v>56</v>
@@ -2083,22 +2078,22 @@
         <v>5</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H37" s="27"/>
       <c r="I37" s="28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" s="27">
         <v>47</v>
@@ -2112,22 +2107,22 @@
         <v>6</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" s="27">
         <v>44</v>
@@ -2141,22 +2136,22 @@
         <v>8</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H39" s="27"/>
       <c r="I39" s="28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J39" s="29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B40" s="31">
         <v>32</v>
@@ -2170,22 +2165,22 @@
         <v>10</v>
       </c>
       <c r="G40" s="32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H40" s="31"/>
       <c r="I40" s="33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B41" s="31">
         <v>34</v>
@@ -2199,22 +2194,22 @@
         <v>8</v>
       </c>
       <c r="G41" s="32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J41" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B42" s="31">
         <v>35</v>
@@ -2228,22 +2223,22 @@
         <v>6</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J42" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="32" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B43" s="31">
         <v>39</v>
@@ -2257,22 +2252,22 @@
         <v>5</v>
       </c>
       <c r="G43" s="32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H43" s="31"/>
       <c r="I43" s="33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B44" s="31">
         <v>46</v>
@@ -2286,22 +2281,22 @@
         <v>4</v>
       </c>
       <c r="G44" s="32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H44" s="31"/>
       <c r="I44" s="33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J44" s="32" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B45" s="18">
         <v>49</v>
@@ -2315,22 +2310,22 @@
         <v>10</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46" s="18">
         <v>49</v>
@@ -2344,22 +2339,22 @@
         <v>8</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B47" s="18">
         <v>53</v>
@@ -2373,22 +2368,22 @@
         <v>6</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B48" s="18">
         <v>58</v>
@@ -2402,22 +2397,22 @@
         <v>5</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H48" s="18"/>
       <c r="I48" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49" s="18">
         <v>61</v>
@@ -2431,22 +2426,22 @@
         <v>4</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H49" s="18"/>
       <c r="I49" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B50" s="18">
         <v>63</v>
@@ -2460,22 +2455,22 @@
         <v>3</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H50" s="18"/>
       <c r="I50" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B51" s="35">
         <v>33</v>
@@ -2489,22 +2484,22 @@
         <v>10</v>
       </c>
       <c r="G51" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H51" s="35"/>
       <c r="I51" s="36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B52" s="35">
         <v>41</v>
@@ -2518,22 +2513,22 @@
         <v>6</v>
       </c>
       <c r="G52" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H52" s="35"/>
       <c r="I52" s="36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1">
       <c r="A53" s="34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B53" s="35">
         <v>38</v>
@@ -2547,22 +2542,22 @@
         <v>8</v>
       </c>
       <c r="G53" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H53" s="35"/>
       <c r="I53" s="36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B54" s="35">
         <v>44</v>
@@ -2576,22 +2571,22 @@
         <v>5</v>
       </c>
       <c r="G54" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H54" s="35"/>
       <c r="I54" s="36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J54" s="34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B55" s="35">
         <v>51</v>
@@ -2605,22 +2600,22 @@
         <v>4</v>
       </c>
       <c r="G55" s="35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H55" s="35"/>
       <c r="I55" s="36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J55" s="34" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B56" s="37">
         <v>45</v>
@@ -2634,22 +2629,22 @@
         <v>10</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H56" s="37"/>
       <c r="I56" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B57" s="37">
         <v>58</v>
@@ -2663,22 +2658,22 @@
         <v>3</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H57" s="37"/>
       <c r="I57" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" s="37">
         <v>56</v>
@@ -2692,22 +2687,22 @@
         <v>4</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H58" s="37"/>
       <c r="I58" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B59" s="37">
         <v>48</v>
@@ -2721,22 +2716,22 @@
         <v>8</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H59" s="37"/>
       <c r="I59" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B60" s="37">
         <v>51</v>
@@ -2750,22 +2745,22 @@
         <v>6</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H60" s="37"/>
       <c r="I60" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B61" s="37">
         <v>66</v>
@@ -2779,22 +2774,22 @@
         <v>1</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H61" s="37"/>
       <c r="I61" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B62" s="37">
         <v>62</v>
@@ -2808,22 +2803,22 @@
         <v>2</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H62" s="37"/>
       <c r="I62" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B63" s="37">
         <v>55</v>
@@ -2837,22 +2832,22 @@
         <v>5</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H63" s="37"/>
       <c r="I63" s="38" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J63" s="37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B64" s="39">
         <v>32</v>
@@ -2866,22 +2861,22 @@
         <v>10</v>
       </c>
       <c r="G64" s="39" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H64" s="39"/>
       <c r="I64" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1">
       <c r="A65" s="39" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B65" s="39">
         <v>34</v>
@@ -2895,22 +2890,22 @@
         <v>8</v>
       </c>
       <c r="G65" s="39" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H65" s="39"/>
       <c r="I65" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J65" s="39" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B66" s="39">
         <v>49</v>
@@ -2924,22 +2919,22 @@
         <v>5</v>
       </c>
       <c r="G66" s="39" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H66" s="39"/>
       <c r="I66" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J66" s="39" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B67" s="39">
         <v>37</v>
@@ -2953,22 +2948,22 @@
         <v>6</v>
       </c>
       <c r="G67" s="39" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H67" s="39"/>
       <c r="I67" s="40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J67" s="39" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B68" s="41">
         <v>47</v>
@@ -2982,22 +2977,22 @@
         <v>10</v>
       </c>
       <c r="G68" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H68" s="41"/>
       <c r="I68" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J68" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B69" s="41">
         <v>48</v>
@@ -3011,22 +3006,22 @@
         <v>8</v>
       </c>
       <c r="G69" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H69" s="41"/>
       <c r="I69" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B70" s="41">
         <v>48</v>
@@ -3040,22 +3035,22 @@
         <v>6</v>
       </c>
       <c r="G70" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H70" s="41"/>
       <c r="I70" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J70" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B71" s="41">
         <v>49</v>
@@ -3069,22 +3064,22 @@
         <v>5</v>
       </c>
       <c r="G71" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J71" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" s="41">
         <v>52</v>
@@ -3098,22 +3093,22 @@
         <v>4</v>
       </c>
       <c r="G72" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H72" s="41"/>
       <c r="I72" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J72" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="41" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B73" s="41">
         <v>62</v>
@@ -3127,22 +3122,22 @@
         <v>3</v>
       </c>
       <c r="G73" s="41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H73" s="41"/>
       <c r="I73" s="42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J73" s="41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B74" s="43">
         <v>30</v>
@@ -3156,22 +3151,22 @@
         <v>10</v>
       </c>
       <c r="G74" s="43" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H74" s="43"/>
       <c r="I74" s="44" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J74" s="43" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B75" s="43">
         <v>34</v>
@@ -3185,22 +3180,22 @@
         <v>8</v>
       </c>
       <c r="G75" s="43" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H75" s="43"/>
       <c r="I75" s="44" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J75" s="43" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="43" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B76" s="43">
         <v>41</v>
@@ -3214,22 +3209,22 @@
         <v>6</v>
       </c>
       <c r="G76" s="43" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H76" s="43"/>
       <c r="I76" s="44" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J76" s="43" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="45" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B77" s="45">
         <v>44</v>
@@ -3243,22 +3238,22 @@
         <v>9</v>
       </c>
       <c r="G77" s="45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H77" s="45"/>
       <c r="I77" s="46">
         <v>46124</v>
       </c>
       <c r="J77" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B78" s="45">
         <v>42</v>
@@ -3272,22 +3267,22 @@
         <v>10</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H78" s="45"/>
       <c r="I78" s="46">
         <v>46124</v>
       </c>
       <c r="J78" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B79" s="45">
         <v>53</v>
@@ -3301,22 +3296,22 @@
         <v>8</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="46">
         <v>46124</v>
       </c>
       <c r="J79" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="45" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B80" s="45">
         <v>62</v>
@@ -3330,22 +3325,22 @@
         <v>7</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H80" s="45"/>
       <c r="I80" s="46">
         <v>46124</v>
       </c>
       <c r="J80" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="55" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B81" s="55">
         <v>54</v>
@@ -3359,22 +3354,22 @@
         <v>8</v>
       </c>
       <c r="G81" s="56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H81" s="55"/>
       <c r="I81" s="57">
         <v>46124</v>
       </c>
       <c r="J81" s="56" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B82" s="55">
         <v>30</v>
@@ -3388,22 +3383,22 @@
         <v>10</v>
       </c>
       <c r="G82" s="56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H82" s="55"/>
       <c r="I82" s="57">
         <v>46124</v>
       </c>
       <c r="J82" s="56" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B83" s="55">
         <v>39</v>
@@ -3417,22 +3412,22 @@
         <v>9</v>
       </c>
       <c r="G83" s="56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H83" s="55"/>
       <c r="I83" s="57">
         <v>46124</v>
       </c>
       <c r="J83" s="56" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="60" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B84" s="60">
         <v>50</v>
@@ -3450,22 +3445,22 @@
         <v>8</v>
       </c>
       <c r="G84" s="59" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H84" s="60"/>
       <c r="I84" s="58">
         <v>46124</v>
       </c>
       <c r="J84" s="59" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K84" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="60" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B85" s="60">
         <v>46</v>
@@ -3483,22 +3478,22 @@
         <v>10</v>
       </c>
       <c r="G85" s="59" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H85" s="60"/>
       <c r="I85" s="58">
         <v>46124</v>
       </c>
       <c r="J85" s="59" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K85" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="60" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B86" s="60">
         <v>43</v>
@@ -3516,22 +3511,22 @@
         <v>9</v>
       </c>
       <c r="G86" s="59" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H86" s="60"/>
       <c r="I86" s="58">
         <v>46124</v>
       </c>
       <c r="J86" s="59" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K86" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="48" customFormat="1">
       <c r="A87" s="63" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B87" s="63">
         <v>27</v>
@@ -3545,22 +3540,22 @@
         <v>10</v>
       </c>
       <c r="G87" s="63" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H87" s="63"/>
       <c r="I87" s="64">
         <v>46152</v>
       </c>
       <c r="J87" s="63" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="48" customFormat="1">
       <c r="A88" s="63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B88" s="63">
         <v>32</v>
@@ -3574,22 +3569,22 @@
         <v>9</v>
       </c>
       <c r="G88" s="63" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H88" s="63"/>
       <c r="I88" s="64">
         <v>46152</v>
       </c>
       <c r="J88" s="63" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K88" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="48" customFormat="1">
       <c r="A89" s="63" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B89" s="63">
         <v>37</v>
@@ -3603,22 +3598,22 @@
         <v>7</v>
       </c>
       <c r="G89" s="63" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H89" s="63"/>
       <c r="I89" s="64">
         <v>46152</v>
       </c>
       <c r="J89" s="63" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K89" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="48" customFormat="1">
       <c r="A90" s="53" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B90" s="53">
         <v>38</v>
@@ -3636,22 +3631,22 @@
         <v>5</v>
       </c>
       <c r="G90" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H90" s="53"/>
       <c r="I90" s="54">
         <v>46152</v>
       </c>
       <c r="J90" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K90" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="48" customFormat="1">
       <c r="A91" s="53" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B91" s="53">
         <v>44</v>
@@ -3669,22 +3664,22 @@
         <v>10</v>
       </c>
       <c r="G91" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H91" s="53"/>
       <c r="I91" s="54">
         <v>46152</v>
       </c>
       <c r="J91" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K91" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="48" customFormat="1">
       <c r="A92" s="53" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B92" s="53">
         <v>46</v>
@@ -3702,22 +3697,22 @@
         <v>9</v>
       </c>
       <c r="G92" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H92" s="53"/>
       <c r="I92" s="54">
         <v>46152</v>
       </c>
       <c r="J92" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K92" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="48" customFormat="1">
       <c r="A93" s="53" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B93" s="53">
         <v>46</v>
@@ -3735,22 +3730,22 @@
         <v>6</v>
       </c>
       <c r="G93" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H93" s="53"/>
       <c r="I93" s="54">
         <v>46152</v>
       </c>
       <c r="J93" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K93" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="48" customFormat="1">
       <c r="A94" s="53" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B94" s="53">
         <v>46</v>
@@ -3768,22 +3763,22 @@
         <v>9</v>
       </c>
       <c r="G94" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H94" s="53"/>
       <c r="I94" s="54">
         <v>46152</v>
       </c>
       <c r="J94" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K94" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="48" customFormat="1">
       <c r="A95" s="53" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B95" s="53">
         <v>49</v>
@@ -3801,22 +3796,22 @@
         <v>7</v>
       </c>
       <c r="G95" s="53" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H95" s="53"/>
       <c r="I95" s="54">
         <v>46152</v>
       </c>
       <c r="J95" s="53" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K95" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="48" customFormat="1">
       <c r="A96" s="61" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B96" s="61">
         <v>46</v>
@@ -3830,22 +3825,22 @@
         <v>10</v>
       </c>
       <c r="G96" s="61" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H96" s="61"/>
       <c r="I96" s="62">
         <v>46152</v>
       </c>
       <c r="J96" s="61" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K96" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="48" customFormat="1">
       <c r="A97" s="61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B97" s="61">
         <v>48</v>
@@ -3859,22 +3854,22 @@
         <v>9</v>
       </c>
       <c r="G97" s="61" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H97" s="61"/>
       <c r="I97" s="62">
         <v>46152</v>
       </c>
       <c r="J97" s="61" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="61" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B98" s="61">
         <v>53</v>
@@ -3888,22 +3883,22 @@
         <v>8</v>
       </c>
       <c r="G98" s="61" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H98" s="61"/>
       <c r="I98" s="62">
         <v>46152</v>
       </c>
       <c r="J98" s="61" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K98" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B99" s="61">
         <v>72</v>
@@ -3917,17 +3912,17 @@
         <v>7</v>
       </c>
       <c r="G99" s="61" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H99" s="61"/>
       <c r="I99" s="62">
         <v>46152</v>
       </c>
       <c r="J99" s="61" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K99" s="48" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -3961,10 +3956,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13.5" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -3979,10 +3974,10 @@
     </row>
     <row r="3" spans="1:5" ht="13.5" customHeight="1">
       <c r="A3" s="50" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -3990,7 +3985,7 @@
     </row>
     <row r="4" spans="1:5" ht="13.5" customHeight="1">
       <c r="A4" s="51" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B4" s="51">
         <v>2026</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3390,7 +3390,7 @@
         <v>46124</v>
       </c>
       <c r="J82" s="56" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>61</v>
@@ -3419,7 +3419,7 @@
         <v>46124</v>
       </c>
       <c r="J83" s="56" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>61</v>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -3229,8 +3229,12 @@
       <c r="B77" s="45">
         <v>44</v>
       </c>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
+      <c r="C77" s="45">
+        <v>0</v>
+      </c>
+      <c r="D77" s="45">
+        <v>44</v>
+      </c>
       <c r="E77" s="45">
         <v>2</v>
       </c>
@@ -3258,8 +3262,12 @@
       <c r="B78" s="45">
         <v>42</v>
       </c>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
+      <c r="C78" s="45">
+        <v>0</v>
+      </c>
+      <c r="D78" s="45">
+        <v>42</v>
+      </c>
       <c r="E78" s="45">
         <v>1</v>
       </c>
@@ -3287,8 +3295,12 @@
       <c r="B79" s="45">
         <v>53</v>
       </c>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
+      <c r="C79" s="45">
+        <v>0</v>
+      </c>
+      <c r="D79" s="45">
+        <v>53</v>
+      </c>
       <c r="E79" s="45">
         <v>3</v>
       </c>
@@ -3316,8 +3328,12 @@
       <c r="B80" s="45">
         <v>62</v>
       </c>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
+      <c r="C80" s="45">
+        <v>0</v>
+      </c>
+      <c r="D80" s="45">
+        <v>62</v>
+      </c>
       <c r="E80" s="45">
         <v>4</v>
       </c>
@@ -3345,8 +3361,12 @@
       <c r="B81" s="55">
         <v>54</v>
       </c>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
+      <c r="C81" s="55">
+        <v>0</v>
+      </c>
+      <c r="D81" s="55">
+        <v>54</v>
+      </c>
       <c r="E81" s="55">
         <v>3</v>
       </c>
@@ -3374,8 +3394,12 @@
       <c r="B82" s="55">
         <v>30</v>
       </c>
-      <c r="C82" s="55"/>
-      <c r="D82" s="55"/>
+      <c r="C82" s="55">
+        <v>0</v>
+      </c>
+      <c r="D82" s="55">
+        <v>30</v>
+      </c>
       <c r="E82" s="55">
         <v>1</v>
       </c>
@@ -3403,8 +3427,12 @@
       <c r="B83" s="55">
         <v>39</v>
       </c>
-      <c r="C83" s="55"/>
-      <c r="D83" s="55"/>
+      <c r="C83" s="55">
+        <v>0</v>
+      </c>
+      <c r="D83" s="55">
+        <v>39</v>
+      </c>
       <c r="E83" s="55">
         <v>2</v>
       </c>
@@ -3531,8 +3559,12 @@
       <c r="B87" s="63">
         <v>27</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
+      <c r="C87" s="63">
+        <v>0</v>
+      </c>
+      <c r="D87" s="63">
+        <v>27</v>
+      </c>
       <c r="E87" s="63">
         <v>1</v>
       </c>
@@ -3560,8 +3592,12 @@
       <c r="B88" s="63">
         <v>32</v>
       </c>
-      <c r="C88" s="63"/>
-      <c r="D88" s="63"/>
+      <c r="C88" s="63">
+        <v>0</v>
+      </c>
+      <c r="D88" s="63">
+        <v>32</v>
+      </c>
       <c r="E88" s="63">
         <v>2</v>
       </c>
@@ -3589,8 +3625,12 @@
       <c r="B89" s="63">
         <v>37</v>
       </c>
-      <c r="C89" s="63"/>
-      <c r="D89" s="63"/>
+      <c r="C89" s="63">
+        <v>0</v>
+      </c>
+      <c r="D89" s="63">
+        <v>37</v>
+      </c>
       <c r="E89" s="63">
         <v>4</v>
       </c>
@@ -3816,8 +3856,12 @@
       <c r="B96" s="61">
         <v>46</v>
       </c>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
+      <c r="C96" s="61">
+        <v>0</v>
+      </c>
+      <c r="D96" s="61">
+        <v>46</v>
+      </c>
       <c r="E96" s="61">
         <v>1</v>
       </c>
@@ -3845,8 +3889,12 @@
       <c r="B97" s="61">
         <v>48</v>
       </c>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
+      <c r="C97" s="61">
+        <v>0</v>
+      </c>
+      <c r="D97" s="61">
+        <v>48</v>
+      </c>
       <c r="E97" s="61">
         <v>2</v>
       </c>
@@ -3874,8 +3922,12 @@
       <c r="B98" s="61">
         <v>53</v>
       </c>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
+      <c r="C98" s="61">
+        <v>0</v>
+      </c>
+      <c r="D98" s="61">
+        <v>53</v>
+      </c>
       <c r="E98" s="61">
         <v>3</v>
       </c>
@@ -3903,8 +3955,12 @@
       <c r="B99" s="61">
         <v>72</v>
       </c>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
+      <c r="C99" s="61">
+        <v>0</v>
+      </c>
+      <c r="D99" s="61">
+        <v>72</v>
+      </c>
       <c r="E99" s="61">
         <v>4</v>
       </c>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$99</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -1004,14 +1004,15 @@
     <col min="1" max="1" width="22.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.7265625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="38.81640625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.1796875" style="1"/>
+    <col min="4" max="4" width="13.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="38.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" style="1"/>
+    <col min="11" max="11" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.1796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5">
@@ -1025,26 +1026,26 @@
         <v>71</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1055,26 +1056,26 @@
         <v>40</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
       <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7">
+      <c r="G2" s="6"/>
+      <c r="H2" s="7">
         <v>45449</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
@@ -1084,26 +1085,26 @@
         <v>64</v>
       </c>
       <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>4</v>
+      </c>
       <c r="E3" s="6">
-        <v>4</v>
-      </c>
-      <c r="F3" s="6">
         <v>5</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7">
+      <c r="G3" s="6"/>
+      <c r="H3" s="7">
         <v>45449</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
@@ -1113,26 +1114,26 @@
         <v>48</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="D4" s="6">
+        <v>2</v>
+      </c>
       <c r="E4" s="6">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6">
         <v>8</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7">
+      <c r="G4" s="6"/>
+      <c r="H4" s="7">
         <v>45449</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
@@ -1142,26 +1143,26 @@
         <v>52</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
       <c r="E5" s="6">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6">
         <v>6</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7">
+      <c r="G5" s="6"/>
+      <c r="H5" s="7">
         <v>45449</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
@@ -1171,26 +1172,26 @@
         <v>51</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
       <c r="E6" s="6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6">
         <v>8</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7">
+      <c r="G6" s="6"/>
+      <c r="H6" s="7">
         <v>45449</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
@@ -1200,26 +1201,26 @@
         <v>49</v>
       </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
       <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
         <v>10</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7">
+      <c r="G7" s="6"/>
+      <c r="H7" s="7">
         <v>45449</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
@@ -1229,26 +1230,26 @@
         <v>58</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
       <c r="E8" s="6">
-        <v>3</v>
-      </c>
-      <c r="F8" s="6">
         <v>6</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7">
+      <c r="G8" s="6"/>
+      <c r="H8" s="7">
         <v>45501</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
@@ -1258,26 +1259,26 @@
         <v>55</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
       <c r="E9" s="6">
-        <v>2</v>
-      </c>
-      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="7">
+      <c r="G9" s="6"/>
+      <c r="H9" s="7">
         <v>45501</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
@@ -1287,26 +1288,26 @@
         <v>39</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
       <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6">
         <v>10</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7">
+      <c r="G10" s="6"/>
+      <c r="H10" s="7">
         <v>45501</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
@@ -1316,26 +1317,26 @@
         <v>53</v>
       </c>
       <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
       <c r="E11" s="6">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6">
         <v>8</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7">
+      <c r="G11" s="6"/>
+      <c r="H11" s="7">
         <v>45522</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
@@ -1345,26 +1346,26 @@
         <v>46</v>
       </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
       <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6">
         <v>10</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7">
+      <c r="G12" s="6"/>
+      <c r="H12" s="7">
         <v>45522</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="8" t="s">
@@ -1374,26 +1375,26 @@
         <v>47</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
       <c r="E13" s="9">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9">
         <v>10</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="s">
+      <c r="G13" s="9"/>
+      <c r="H13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11" ht="13.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -1403,26 +1404,26 @@
         <v>53</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="9">
+        <v>2</v>
+      </c>
       <c r="E14" s="9">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9">
         <v>8</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="s">
+      <c r="G14" s="9"/>
+      <c r="H14" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="13.5" customHeight="1">
       <c r="A15" s="8" t="s">
@@ -1432,26 +1433,26 @@
         <v>55</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9">
+        <v>3</v>
+      </c>
       <c r="E15" s="9">
-        <v>3</v>
-      </c>
-      <c r="F15" s="9">
         <v>6</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="s">
+      <c r="G15" s="9"/>
+      <c r="H15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:11" ht="13.5" customHeight="1">
       <c r="A16" s="8" t="s">
@@ -1461,26 +1462,26 @@
         <v>56</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="D16" s="9">
+        <v>4</v>
+      </c>
       <c r="E16" s="9">
-        <v>4</v>
-      </c>
-      <c r="F16" s="9">
         <v>5</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="s">
+      <c r="G16" s="9"/>
+      <c r="H16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1">
       <c r="A17" s="8" t="s">
@@ -1490,26 +1491,26 @@
         <v>60</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9">
+        <v>5</v>
+      </c>
       <c r="E17" s="9">
-        <v>5</v>
-      </c>
-      <c r="F17" s="9">
         <v>4</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="s">
+      <c r="G17" s="9"/>
+      <c r="H17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11" ht="13.5" customHeight="1">
       <c r="A18" s="8" t="s">
@@ -1519,26 +1520,26 @@
         <v>74</v>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="D18" s="9">
+        <v>6</v>
+      </c>
       <c r="E18" s="9">
-        <v>6</v>
-      </c>
-      <c r="F18" s="9">
         <v>3</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="s">
+      <c r="G18" s="9"/>
+      <c r="H18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="13.5" customHeight="1">
       <c r="A19" s="8" t="s">
@@ -1548,26 +1549,26 @@
         <v>78</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9">
+        <v>7</v>
+      </c>
       <c r="E19" s="9">
-        <v>7</v>
-      </c>
-      <c r="F19" s="9">
         <v>2</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="s">
+      <c r="G19" s="9"/>
+      <c r="H19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" ht="13.5" customHeight="1">
       <c r="A20" s="8" t="s">
@@ -1577,26 +1578,26 @@
         <v>79</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9">
+        <v>8</v>
+      </c>
       <c r="E20" s="9">
-        <v>8</v>
-      </c>
-      <c r="F20" s="9">
         <v>1</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="13.5" customHeight="1">
       <c r="A21" s="11" t="s">
@@ -1606,26 +1607,26 @@
         <v>30</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="D21" s="12">
+        <v>1</v>
+      </c>
       <c r="E21" s="12">
-        <v>1</v>
-      </c>
-      <c r="F21" s="12">
         <v>10</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13" t="s">
+      <c r="G21" s="12"/>
+      <c r="H21" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="I21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" ht="13.5" customHeight="1">
       <c r="A22" s="11" t="s">
@@ -1635,26 +1636,26 @@
         <v>45</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="D22" s="12">
+        <v>2</v>
+      </c>
       <c r="E22" s="12">
-        <v>2</v>
-      </c>
-      <c r="F22" s="12">
         <v>8</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13" t="s">
+      <c r="G22" s="12"/>
+      <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="I22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="1:11" ht="13.5" customHeight="1">
       <c r="A23" s="14" t="s">
@@ -1664,26 +1665,26 @@
         <v>50</v>
       </c>
       <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
       <c r="E23" s="15">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15">
         <v>10</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="F23" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16" t="s">
+      <c r="G23" s="15"/>
+      <c r="H23" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="I23" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="15"/>
     </row>
     <row r="24" spans="1:11" ht="13.5" customHeight="1">
       <c r="A24" s="14" t="s">
@@ -1693,26 +1694,26 @@
         <v>57</v>
       </c>
       <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
+      <c r="D24" s="15">
+        <v>2</v>
+      </c>
       <c r="E24" s="15">
-        <v>2</v>
-      </c>
-      <c r="F24" s="15">
         <v>8</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16" t="s">
+      <c r="G24" s="15"/>
+      <c r="H24" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="I24" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25" spans="1:11" ht="13.5" customHeight="1">
       <c r="A25" s="14" t="s">
@@ -1722,26 +1723,26 @@
         <v>65</v>
       </c>
       <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
+      <c r="D25" s="15">
+        <v>3</v>
+      </c>
       <c r="E25" s="15">
-        <v>3</v>
-      </c>
-      <c r="F25" s="15">
         <v>6</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="16" t="s">
+      <c r="G25" s="15"/>
+      <c r="H25" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="I25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="13.5" customHeight="1">
       <c r="A26" s="14" t="s">
@@ -1751,26 +1752,26 @@
         <v>76</v>
       </c>
       <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="D26" s="15">
+        <v>4</v>
+      </c>
       <c r="E26" s="15">
-        <v>4</v>
-      </c>
-      <c r="F26" s="15">
         <v>5</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="F26" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="16" t="s">
+      <c r="G26" s="15"/>
+      <c r="H26" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="I26" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" s="15"/>
     </row>
     <row r="27" spans="1:11" ht="13.5" customHeight="1">
       <c r="A27" s="17" t="s">
@@ -1780,26 +1781,26 @@
         <v>30</v>
       </c>
       <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
+      <c r="D27" s="18">
+        <v>1</v>
+      </c>
       <c r="E27" s="18">
-        <v>1</v>
-      </c>
-      <c r="F27" s="18">
         <v>10</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="F27" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="19" t="s">
+      <c r="G27" s="18"/>
+      <c r="H27" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="17" t="s">
+      <c r="I27" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" s="18"/>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1">
       <c r="A28" s="17" t="s">
@@ -1809,26 +1810,26 @@
         <v>47</v>
       </c>
       <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
+      <c r="D28" s="18">
+        <v>2</v>
+      </c>
       <c r="E28" s="18">
-        <v>2</v>
-      </c>
-      <c r="F28" s="18">
         <v>8</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="19" t="s">
+      <c r="G28" s="18"/>
+      <c r="H28" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="17" t="s">
+      <c r="I28" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" s="18"/>
     </row>
     <row r="29" spans="1:11" ht="13.5" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -1838,26 +1839,26 @@
         <v>53</v>
       </c>
       <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
+      <c r="D29" s="18">
+        <v>3</v>
+      </c>
       <c r="E29" s="18">
-        <v>3</v>
-      </c>
-      <c r="F29" s="18">
         <v>6</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="F29" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="19" t="s">
+      <c r="G29" s="18"/>
+      <c r="H29" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="I29" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K29" s="18"/>
     </row>
     <row r="30" spans="1:11" ht="13.5" customHeight="1">
       <c r="A30" s="20" t="s">
@@ -1867,26 +1868,26 @@
         <v>45</v>
       </c>
       <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="21">
+        <v>1</v>
+      </c>
       <c r="E30" s="21">
-        <v>1</v>
-      </c>
-      <c r="F30" s="21">
         <v>10</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="21"/>
-      <c r="I30" s="22" t="s">
+      <c r="G30" s="21"/>
+      <c r="H30" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="20" t="s">
+      <c r="I30" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:11" ht="13.5" customHeight="1">
       <c r="A31" s="20" t="s">
@@ -1896,26 +1897,26 @@
         <v>47</v>
       </c>
       <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="21">
+        <v>2</v>
+      </c>
       <c r="E31" s="21">
-        <v>2</v>
-      </c>
-      <c r="F31" s="21">
         <v>8</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="F31" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="22" t="s">
+      <c r="G31" s="21"/>
+      <c r="H31" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="20" t="s">
+      <c r="I31" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K31" s="21"/>
     </row>
     <row r="32" spans="1:11" ht="13.5" customHeight="1">
       <c r="A32" s="20" t="s">
@@ -1925,26 +1926,26 @@
         <v>58</v>
       </c>
       <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="21">
+        <v>3</v>
+      </c>
       <c r="E32" s="21">
-        <v>3</v>
-      </c>
-      <c r="F32" s="21">
         <v>6</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="F32" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="22" t="s">
+      <c r="G32" s="21"/>
+      <c r="H32" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="20" t="s">
+      <c r="I32" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" s="21"/>
     </row>
     <row r="33" spans="1:11" ht="13.5" customHeight="1">
       <c r="A33" s="23" t="s">
@@ -1954,26 +1955,26 @@
         <v>28</v>
       </c>
       <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
+      <c r="D33" s="24">
+        <v>1</v>
+      </c>
       <c r="E33" s="24">
-        <v>1</v>
-      </c>
-      <c r="F33" s="24">
         <v>10</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="F33" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="24"/>
-      <c r="I33" s="25" t="s">
+      <c r="G33" s="24"/>
+      <c r="H33" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J33" s="23" t="s">
+      <c r="I33" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K33" s="24"/>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="23" t="s">
@@ -1983,26 +1984,26 @@
         <v>44</v>
       </c>
       <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
+      <c r="D34" s="24">
+        <v>2</v>
+      </c>
       <c r="E34" s="24">
-        <v>2</v>
-      </c>
-      <c r="F34" s="24">
         <v>8</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="F34" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="24"/>
-      <c r="I34" s="25" t="s">
+      <c r="G34" s="24"/>
+      <c r="H34" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="I34" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="24"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="26" t="s">
@@ -2012,26 +2013,26 @@
         <v>38</v>
       </c>
       <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="27">
+        <v>1</v>
+      </c>
       <c r="E35" s="27">
-        <v>1</v>
-      </c>
-      <c r="F35" s="27">
         <v>10</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="F35" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="27"/>
-      <c r="I35" s="28" t="s">
+      <c r="G35" s="27"/>
+      <c r="H35" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J35" s="29" t="s">
+      <c r="I35" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K35" s="27"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="26" t="s">
@@ -2041,26 +2042,26 @@
         <v>60</v>
       </c>
       <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="27">
+        <v>5</v>
+      </c>
       <c r="E36" s="27">
-        <v>5</v>
-      </c>
-      <c r="F36" s="27">
         <v>4</v>
       </c>
-      <c r="G36" s="26" t="s">
+      <c r="F36" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28" t="s">
+      <c r="G36" s="27"/>
+      <c r="H36" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="29" t="s">
+      <c r="I36" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K36" s="27"/>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="26" t="s">
@@ -2070,26 +2071,26 @@
         <v>56</v>
       </c>
       <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="27">
+        <v>4</v>
+      </c>
       <c r="E37" s="27">
-        <v>4</v>
-      </c>
-      <c r="F37" s="27">
         <v>5</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="F37" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28" t="s">
+      <c r="G37" s="27"/>
+      <c r="H37" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J37" s="29" t="s">
+      <c r="I37" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K37" s="27"/>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="26" t="s">
@@ -2099,26 +2100,26 @@
         <v>47</v>
       </c>
       <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="27">
+        <v>3</v>
+      </c>
       <c r="E38" s="27">
-        <v>3</v>
-      </c>
-      <c r="F38" s="27">
         <v>6</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="F38" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28" t="s">
+      <c r="G38" s="27"/>
+      <c r="H38" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J38" s="29" t="s">
+      <c r="I38" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38" s="27"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="26" t="s">
@@ -2128,26 +2129,26 @@
         <v>44</v>
       </c>
       <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="27">
+        <v>2</v>
+      </c>
       <c r="E39" s="27">
-        <v>2</v>
-      </c>
-      <c r="F39" s="27">
         <v>8</v>
       </c>
-      <c r="G39" s="26" t="s">
+      <c r="F39" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H39" s="27"/>
-      <c r="I39" s="28" t="s">
+      <c r="G39" s="27"/>
+      <c r="H39" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J39" s="29" t="s">
+      <c r="I39" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K39" s="27"/>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="30" t="s">
@@ -2157,26 +2158,26 @@
         <v>32</v>
       </c>
       <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
+      <c r="D40" s="31">
+        <v>1</v>
+      </c>
       <c r="E40" s="31">
-        <v>1</v>
-      </c>
-      <c r="F40" s="31">
         <v>10</v>
       </c>
-      <c r="G40" s="32" t="s">
+      <c r="F40" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H40" s="31"/>
-      <c r="I40" s="33" t="s">
+      <c r="G40" s="31"/>
+      <c r="H40" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="32" t="s">
+      <c r="I40" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K40" s="31"/>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="32" t="s">
@@ -2186,26 +2187,26 @@
         <v>34</v>
       </c>
       <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="D41" s="31">
+        <v>2</v>
+      </c>
       <c r="E41" s="31">
-        <v>2</v>
-      </c>
-      <c r="F41" s="31">
         <v>8</v>
       </c>
-      <c r="G41" s="32" t="s">
+      <c r="F41" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H41" s="31"/>
-      <c r="I41" s="33" t="s">
+      <c r="G41" s="31"/>
+      <c r="H41" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="32" t="s">
+      <c r="I41" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41" s="31"/>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="32" t="s">
@@ -2215,26 +2216,26 @@
         <v>35</v>
       </c>
       <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
+      <c r="D42" s="31">
+        <v>3</v>
+      </c>
       <c r="E42" s="31">
-        <v>3</v>
-      </c>
-      <c r="F42" s="31">
         <v>6</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="F42" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H42" s="31"/>
-      <c r="I42" s="33" t="s">
+      <c r="G42" s="31"/>
+      <c r="H42" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="J42" s="32" t="s">
+      <c r="I42" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K42" s="31"/>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="32" t="s">
@@ -2244,26 +2245,26 @@
         <v>39</v>
       </c>
       <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+      <c r="D43" s="31">
+        <v>4</v>
+      </c>
       <c r="E43" s="31">
-        <v>4</v>
-      </c>
-      <c r="F43" s="31">
         <v>5</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="F43" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H43" s="31"/>
-      <c r="I43" s="33" t="s">
+      <c r="G43" s="31"/>
+      <c r="H43" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="J43" s="32" t="s">
+      <c r="I43" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K43" s="31"/>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="32" t="s">
@@ -2273,26 +2274,26 @@
         <v>46</v>
       </c>
       <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
+      <c r="D44" s="31">
+        <v>5</v>
+      </c>
       <c r="E44" s="31">
-        <v>5</v>
-      </c>
-      <c r="F44" s="31">
         <v>4</v>
       </c>
-      <c r="G44" s="32" t="s">
+      <c r="F44" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="31"/>
-      <c r="I44" s="33" t="s">
+      <c r="G44" s="31"/>
+      <c r="H44" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="32" t="s">
+      <c r="I44" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K44" s="31"/>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="17" t="s">
@@ -2302,26 +2303,26 @@
         <v>49</v>
       </c>
       <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+      <c r="D45" s="18">
+        <v>1</v>
+      </c>
       <c r="E45" s="18">
-        <v>1</v>
-      </c>
-      <c r="F45" s="18">
         <v>10</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="F45" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H45" s="18"/>
-      <c r="I45" s="19" t="s">
+      <c r="G45" s="18"/>
+      <c r="H45" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="I45" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" s="18"/>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="17" t="s">
@@ -2331,26 +2332,26 @@
         <v>49</v>
       </c>
       <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="D46" s="18">
+        <v>2</v>
+      </c>
       <c r="E46" s="18">
-        <v>2</v>
-      </c>
-      <c r="F46" s="18">
         <v>8</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="F46" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H46" s="18"/>
-      <c r="I46" s="19" t="s">
+      <c r="G46" s="18"/>
+      <c r="H46" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="I46" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K46" s="18"/>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="17" t="s">
@@ -2360,26 +2361,26 @@
         <v>53</v>
       </c>
       <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
+      <c r="D47" s="18">
+        <v>3</v>
+      </c>
       <c r="E47" s="18">
-        <v>3</v>
-      </c>
-      <c r="F47" s="18">
         <v>6</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="F47" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H47" s="18"/>
-      <c r="I47" s="19" t="s">
+      <c r="G47" s="18"/>
+      <c r="H47" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="I47" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K47" s="18"/>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="17" t="s">
@@ -2389,26 +2390,26 @@
         <v>58</v>
       </c>
       <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
+      <c r="D48" s="18">
+        <v>4</v>
+      </c>
       <c r="E48" s="18">
-        <v>4</v>
-      </c>
-      <c r="F48" s="18">
         <v>5</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="F48" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="19" t="s">
+      <c r="G48" s="18"/>
+      <c r="H48" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="I48" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48" s="18"/>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="17" t="s">
@@ -2418,26 +2419,26 @@
         <v>61</v>
       </c>
       <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
+      <c r="D49" s="18">
+        <v>5</v>
+      </c>
       <c r="E49" s="18">
-        <v>5</v>
-      </c>
-      <c r="F49" s="18">
         <v>4</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="F49" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H49" s="18"/>
-      <c r="I49" s="19" t="s">
+      <c r="G49" s="18"/>
+      <c r="H49" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J49" s="17" t="s">
+      <c r="I49" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K49" s="18"/>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="17" t="s">
@@ -2447,26 +2448,26 @@
         <v>63</v>
       </c>
       <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
+      <c r="D50" s="18">
+        <v>6</v>
+      </c>
       <c r="E50" s="18">
-        <v>6</v>
-      </c>
-      <c r="F50" s="18">
         <v>3</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="F50" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H50" s="18"/>
-      <c r="I50" s="19" t="s">
+      <c r="G50" s="18"/>
+      <c r="H50" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J50" s="17" t="s">
+      <c r="I50" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K50" s="18"/>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="34" t="s">
@@ -2476,26 +2477,26 @@
         <v>33</v>
       </c>
       <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
+      <c r="D51" s="35">
+        <v>1</v>
+      </c>
       <c r="E51" s="35">
-        <v>1</v>
-      </c>
-      <c r="F51" s="35">
         <v>10</v>
       </c>
-      <c r="G51" s="35" t="s">
+      <c r="F51" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H51" s="35"/>
-      <c r="I51" s="36" t="s">
+      <c r="G51" s="35"/>
+      <c r="H51" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J51" s="34" t="s">
+      <c r="I51" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K51" s="35"/>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="34" t="s">
@@ -2505,26 +2506,26 @@
         <v>41</v>
       </c>
       <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
+      <c r="D52" s="35">
+        <v>3</v>
+      </c>
       <c r="E52" s="35">
-        <v>3</v>
-      </c>
-      <c r="F52" s="35">
         <v>6</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="F52" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="35"/>
-      <c r="I52" s="36" t="s">
+      <c r="G52" s="35"/>
+      <c r="H52" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="34" t="s">
+      <c r="I52" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" s="35"/>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1">
       <c r="A53" s="34" t="s">
@@ -2534,26 +2535,26 @@
         <v>38</v>
       </c>
       <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
+      <c r="D53" s="35">
+        <v>2</v>
+      </c>
       <c r="E53" s="35">
-        <v>2</v>
-      </c>
-      <c r="F53" s="35">
         <v>8</v>
       </c>
-      <c r="G53" s="35" t="s">
+      <c r="F53" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H53" s="35"/>
-      <c r="I53" s="36" t="s">
+      <c r="G53" s="35"/>
+      <c r="H53" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J53" s="34" t="s">
+      <c r="I53" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K53" s="35"/>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1">
       <c r="A54" s="34" t="s">
@@ -2563,26 +2564,26 @@
         <v>44</v>
       </c>
       <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
+      <c r="D54" s="35">
+        <v>4</v>
+      </c>
       <c r="E54" s="35">
-        <v>4</v>
-      </c>
-      <c r="F54" s="35">
         <v>5</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="F54" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H54" s="35"/>
-      <c r="I54" s="36" t="s">
+      <c r="G54" s="35"/>
+      <c r="H54" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J54" s="34" t="s">
+      <c r="I54" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K54" s="35"/>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1">
       <c r="A55" s="34" t="s">
@@ -2592,26 +2593,26 @@
         <v>51</v>
       </c>
       <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
+      <c r="D55" s="35">
+        <v>5</v>
+      </c>
       <c r="E55" s="35">
-        <v>5</v>
-      </c>
-      <c r="F55" s="35">
         <v>4</v>
       </c>
-      <c r="G55" s="35" t="s">
+      <c r="F55" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H55" s="35"/>
-      <c r="I55" s="36" t="s">
+      <c r="G55" s="35"/>
+      <c r="H55" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="34" t="s">
+      <c r="I55" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K55" s="35"/>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1">
       <c r="A56" s="37" t="s">
@@ -2621,26 +2622,26 @@
         <v>45</v>
       </c>
       <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
+      <c r="D56" s="37">
+        <v>1</v>
+      </c>
       <c r="E56" s="37">
-        <v>1</v>
-      </c>
-      <c r="F56" s="37">
         <v>10</v>
       </c>
-      <c r="G56" s="37" t="s">
+      <c r="F56" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H56" s="37"/>
-      <c r="I56" s="38" t="s">
+      <c r="G56" s="37"/>
+      <c r="H56" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J56" s="37" t="s">
+      <c r="I56" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K56" s="37"/>
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1">
       <c r="A57" s="37" t="s">
@@ -2650,26 +2651,26 @@
         <v>58</v>
       </c>
       <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
+      <c r="D57" s="37">
+        <v>6</v>
+      </c>
       <c r="E57" s="37">
-        <v>6</v>
-      </c>
-      <c r="F57" s="37">
         <v>3</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="F57" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H57" s="37"/>
-      <c r="I57" s="38" t="s">
+      <c r="G57" s="37"/>
+      <c r="H57" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J57" s="37" t="s">
+      <c r="I57" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K57" s="37"/>
     </row>
     <row r="58" spans="1:11" ht="15" customHeight="1">
       <c r="A58" s="37" t="s">
@@ -2679,26 +2680,26 @@
         <v>56</v>
       </c>
       <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
+      <c r="D58" s="37">
+        <v>5</v>
+      </c>
       <c r="E58" s="37">
-        <v>5</v>
-      </c>
-      <c r="F58" s="37">
         <v>4</v>
       </c>
-      <c r="G58" s="37" t="s">
+      <c r="F58" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H58" s="37"/>
-      <c r="I58" s="38" t="s">
+      <c r="G58" s="37"/>
+      <c r="H58" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J58" s="37" t="s">
+      <c r="I58" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K58" s="37"/>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1">
       <c r="A59" s="37" t="s">
@@ -2708,26 +2709,26 @@
         <v>48</v>
       </c>
       <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
+      <c r="D59" s="37">
+        <v>2</v>
+      </c>
       <c r="E59" s="37">
-        <v>2</v>
-      </c>
-      <c r="F59" s="37">
         <v>8</v>
       </c>
-      <c r="G59" s="37" t="s">
+      <c r="F59" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H59" s="37"/>
-      <c r="I59" s="38" t="s">
+      <c r="G59" s="37"/>
+      <c r="H59" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J59" s="37" t="s">
+      <c r="I59" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K59" s="37"/>
     </row>
     <row r="60" spans="1:11" ht="15" customHeight="1">
       <c r="A60" s="37" t="s">
@@ -2737,26 +2738,26 @@
         <v>51</v>
       </c>
       <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
+      <c r="D60" s="37">
+        <v>3</v>
+      </c>
       <c r="E60" s="37">
-        <v>3</v>
-      </c>
-      <c r="F60" s="37">
         <v>6</v>
       </c>
-      <c r="G60" s="37" t="s">
+      <c r="F60" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="37"/>
-      <c r="I60" s="38" t="s">
+      <c r="G60" s="37"/>
+      <c r="H60" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J60" s="37" t="s">
+      <c r="I60" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J60" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K60" s="37"/>
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1">
       <c r="A61" s="37" t="s">
@@ -2766,26 +2767,26 @@
         <v>66</v>
       </c>
       <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
+      <c r="D61" s="37">
+        <v>8</v>
+      </c>
       <c r="E61" s="37">
-        <v>8</v>
-      </c>
-      <c r="F61" s="37">
         <v>1</v>
       </c>
-      <c r="G61" s="37" t="s">
+      <c r="F61" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H61" s="37"/>
-      <c r="I61" s="38" t="s">
+      <c r="G61" s="37"/>
+      <c r="H61" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J61" s="37" t="s">
+      <c r="I61" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J61" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K61" s="37"/>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1">
       <c r="A62" s="37" t="s">
@@ -2795,26 +2796,26 @@
         <v>62</v>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
+      <c r="D62" s="37">
+        <v>7</v>
+      </c>
       <c r="E62" s="37">
-        <v>7</v>
-      </c>
-      <c r="F62" s="37">
         <v>2</v>
       </c>
-      <c r="G62" s="37" t="s">
+      <c r="F62" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H62" s="37"/>
-      <c r="I62" s="38" t="s">
+      <c r="G62" s="37"/>
+      <c r="H62" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="37" t="s">
+      <c r="I62" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K62" s="37"/>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1">
       <c r="A63" s="37" t="s">
@@ -2824,26 +2825,26 @@
         <v>55</v>
       </c>
       <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
+      <c r="D63" s="37">
+        <v>4</v>
+      </c>
       <c r="E63" s="37">
-        <v>4</v>
-      </c>
-      <c r="F63" s="37">
         <v>5</v>
       </c>
-      <c r="G63" s="37" t="s">
+      <c r="F63" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H63" s="37"/>
-      <c r="I63" s="38" t="s">
+      <c r="G63" s="37"/>
+      <c r="H63" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="J63" s="37" t="s">
+      <c r="I63" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63" s="37"/>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1">
       <c r="A64" s="39" t="s">
@@ -2853,26 +2854,26 @@
         <v>32</v>
       </c>
       <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
+      <c r="D64" s="39">
+        <v>1</v>
+      </c>
       <c r="E64" s="39">
-        <v>1</v>
-      </c>
-      <c r="F64" s="39">
         <v>10</v>
       </c>
-      <c r="G64" s="39" t="s">
+      <c r="F64" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="H64" s="39"/>
-      <c r="I64" s="40" t="s">
+      <c r="G64" s="39"/>
+      <c r="H64" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="J64" s="39" t="s">
+      <c r="I64" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J64" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K64" s="39"/>
     </row>
     <row r="65" spans="1:11" ht="15" customHeight="1">
       <c r="A65" s="39" t="s">
@@ -2882,26 +2883,26 @@
         <v>34</v>
       </c>
       <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
+      <c r="D65" s="39">
+        <v>2</v>
+      </c>
       <c r="E65" s="39">
-        <v>2</v>
-      </c>
-      <c r="F65" s="39">
         <v>8</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="F65" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="H65" s="39"/>
-      <c r="I65" s="40" t="s">
+      <c r="G65" s="39"/>
+      <c r="H65" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="J65" s="39" t="s">
+      <c r="I65" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K65" s="39"/>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1">
       <c r="A66" s="39" t="s">
@@ -2911,26 +2912,26 @@
         <v>49</v>
       </c>
       <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
+      <c r="D66" s="39">
+        <v>4</v>
+      </c>
       <c r="E66" s="39">
-        <v>4</v>
-      </c>
-      <c r="F66" s="39">
         <v>5</v>
       </c>
-      <c r="G66" s="39" t="s">
+      <c r="F66" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="H66" s="39"/>
-      <c r="I66" s="40" t="s">
+      <c r="G66" s="39"/>
+      <c r="H66" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="J66" s="39" t="s">
+      <c r="I66" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K66" s="39"/>
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1">
       <c r="A67" s="39" t="s">
@@ -2940,26 +2941,26 @@
         <v>37</v>
       </c>
       <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
+      <c r="D67" s="39">
+        <v>3</v>
+      </c>
       <c r="E67" s="39">
-        <v>3</v>
-      </c>
-      <c r="F67" s="39">
         <v>6</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="F67" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="H67" s="39"/>
-      <c r="I67" s="40" t="s">
+      <c r="G67" s="39"/>
+      <c r="H67" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="J67" s="39" t="s">
+      <c r="I67" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J67" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K67" s="39"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="41" t="s">
@@ -2969,26 +2970,26 @@
         <v>47</v>
       </c>
       <c r="C68" s="41"/>
-      <c r="D68" s="41"/>
+      <c r="D68" s="41">
+        <v>1</v>
+      </c>
       <c r="E68" s="41">
-        <v>1</v>
-      </c>
-      <c r="F68" s="41">
         <v>10</v>
       </c>
-      <c r="G68" s="41" t="s">
+      <c r="F68" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="41"/>
-      <c r="I68" s="42" t="s">
+      <c r="G68" s="41"/>
+      <c r="H68" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="41" t="s">
+      <c r="I68" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K68" s="41"/>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="41" t="s">
@@ -2998,26 +2999,26 @@
         <v>48</v>
       </c>
       <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
+      <c r="D69" s="41">
+        <v>2</v>
+      </c>
       <c r="E69" s="41">
-        <v>2</v>
-      </c>
-      <c r="F69" s="41">
         <v>8</v>
       </c>
-      <c r="G69" s="41" t="s">
+      <c r="F69" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="41"/>
-      <c r="I69" s="42" t="s">
+      <c r="G69" s="41"/>
+      <c r="H69" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J69" s="41" t="s">
+      <c r="I69" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K69" s="41"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="41" t="s">
@@ -3027,26 +3028,26 @@
         <v>48</v>
       </c>
       <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
+      <c r="D70" s="41">
+        <v>3</v>
+      </c>
       <c r="E70" s="41">
-        <v>3</v>
-      </c>
-      <c r="F70" s="41">
         <v>6</v>
       </c>
-      <c r="G70" s="41" t="s">
+      <c r="F70" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="41"/>
-      <c r="I70" s="42" t="s">
+      <c r="G70" s="41"/>
+      <c r="H70" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J70" s="41" t="s">
+      <c r="I70" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K70" s="41"/>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="41" t="s">
@@ -3056,26 +3057,26 @@
         <v>49</v>
       </c>
       <c r="C71" s="41"/>
-      <c r="D71" s="41"/>
+      <c r="D71" s="41">
+        <v>4</v>
+      </c>
       <c r="E71" s="41">
-        <v>4</v>
-      </c>
-      <c r="F71" s="41">
         <v>5</v>
       </c>
-      <c r="G71" s="41" t="s">
+      <c r="F71" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H71" s="41"/>
-      <c r="I71" s="42" t="s">
+      <c r="G71" s="41"/>
+      <c r="H71" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J71" s="41" t="s">
+      <c r="I71" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J71" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K71" s="41"/>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="41" t="s">
@@ -3085,26 +3086,26 @@
         <v>52</v>
       </c>
       <c r="C72" s="41"/>
-      <c r="D72" s="41"/>
+      <c r="D72" s="41">
+        <v>5</v>
+      </c>
       <c r="E72" s="41">
-        <v>5</v>
-      </c>
-      <c r="F72" s="41">
         <v>4</v>
       </c>
-      <c r="G72" s="41" t="s">
+      <c r="F72" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="41"/>
-      <c r="I72" s="42" t="s">
+      <c r="G72" s="41"/>
+      <c r="H72" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J72" s="41" t="s">
+      <c r="I72" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K72" s="41"/>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="41" t="s">
@@ -3114,26 +3115,26 @@
         <v>62</v>
       </c>
       <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
+      <c r="D73" s="41">
+        <v>6</v>
+      </c>
       <c r="E73" s="41">
-        <v>6</v>
-      </c>
-      <c r="F73" s="41">
         <v>3</v>
       </c>
-      <c r="G73" s="41" t="s">
+      <c r="F73" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H73" s="41"/>
-      <c r="I73" s="42" t="s">
+      <c r="G73" s="41"/>
+      <c r="H73" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="J73" s="41" t="s">
+      <c r="I73" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="43" t="s">
@@ -3143,26 +3144,26 @@
         <v>30</v>
       </c>
       <c r="C74" s="43"/>
-      <c r="D74" s="43"/>
+      <c r="D74" s="43">
+        <v>1</v>
+      </c>
       <c r="E74" s="43">
-        <v>1</v>
-      </c>
-      <c r="F74" s="43">
         <v>10</v>
       </c>
-      <c r="G74" s="43" t="s">
+      <c r="F74" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="H74" s="43"/>
-      <c r="I74" s="44" t="s">
+      <c r="G74" s="43"/>
+      <c r="H74" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J74" s="43" t="s">
+      <c r="I74" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K74" s="43"/>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="43" t="s">
@@ -3172,26 +3173,26 @@
         <v>34</v>
       </c>
       <c r="C75" s="43"/>
-      <c r="D75" s="43"/>
+      <c r="D75" s="43">
+        <v>2</v>
+      </c>
       <c r="E75" s="43">
-        <v>2</v>
-      </c>
-      <c r="F75" s="43">
         <v>8</v>
       </c>
-      <c r="G75" s="43" t="s">
+      <c r="F75" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="43"/>
-      <c r="I75" s="44" t="s">
+      <c r="G75" s="43"/>
+      <c r="H75" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J75" s="43" t="s">
+      <c r="I75" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K75" s="43"/>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="43" t="s">
@@ -3201,26 +3202,26 @@
         <v>41</v>
       </c>
       <c r="C76" s="43"/>
-      <c r="D76" s="43"/>
+      <c r="D76" s="43">
+        <v>3</v>
+      </c>
       <c r="E76" s="43">
-        <v>3</v>
-      </c>
-      <c r="F76" s="43">
         <v>6</v>
       </c>
-      <c r="G76" s="43" t="s">
+      <c r="F76" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="H76" s="43"/>
-      <c r="I76" s="44" t="s">
+      <c r="G76" s="43"/>
+      <c r="H76" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J76" s="43" t="s">
+      <c r="I76" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="J76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K76" s="43"/>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="45" t="s">
@@ -3233,26 +3234,26 @@
         <v>0</v>
       </c>
       <c r="D77" s="45">
+        <v>2</v>
+      </c>
+      <c r="E77" s="45">
+        <v>9</v>
+      </c>
+      <c r="F77" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="45"/>
+      <c r="H77" s="46">
+        <v>46124</v>
+      </c>
+      <c r="I77" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K77" s="45">
         <v>44</v>
-      </c>
-      <c r="E77" s="45">
-        <v>2</v>
-      </c>
-      <c r="F77" s="45">
-        <v>9</v>
-      </c>
-      <c r="G77" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="45"/>
-      <c r="I77" s="46">
-        <v>46124</v>
-      </c>
-      <c r="J77" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3266,26 +3267,26 @@
         <v>0</v>
       </c>
       <c r="D78" s="45">
+        <v>1</v>
+      </c>
+      <c r="E78" s="45">
+        <v>10</v>
+      </c>
+      <c r="F78" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="45"/>
+      <c r="H78" s="46">
+        <v>46124</v>
+      </c>
+      <c r="I78" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K78" s="45">
         <v>42</v>
-      </c>
-      <c r="E78" s="45">
-        <v>1</v>
-      </c>
-      <c r="F78" s="45">
-        <v>10</v>
-      </c>
-      <c r="G78" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="45"/>
-      <c r="I78" s="46">
-        <v>46124</v>
-      </c>
-      <c r="J78" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3299,26 +3300,26 @@
         <v>0</v>
       </c>
       <c r="D79" s="45">
+        <v>3</v>
+      </c>
+      <c r="E79" s="45">
+        <v>8</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="45"/>
+      <c r="H79" s="46">
+        <v>46124</v>
+      </c>
+      <c r="I79" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K79" s="45">
         <v>53</v>
-      </c>
-      <c r="E79" s="45">
-        <v>3</v>
-      </c>
-      <c r="F79" s="45">
-        <v>8</v>
-      </c>
-      <c r="G79" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="45"/>
-      <c r="I79" s="46">
-        <v>46124</v>
-      </c>
-      <c r="J79" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3332,26 +3333,26 @@
         <v>0</v>
       </c>
       <c r="D80" s="45">
+        <v>4</v>
+      </c>
+      <c r="E80" s="45">
+        <v>7</v>
+      </c>
+      <c r="F80" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="45"/>
+      <c r="H80" s="46">
+        <v>46124</v>
+      </c>
+      <c r="I80" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K80" s="45">
         <v>62</v>
-      </c>
-      <c r="E80" s="45">
-        <v>4</v>
-      </c>
-      <c r="F80" s="45">
-        <v>7</v>
-      </c>
-      <c r="G80" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H80" s="45"/>
-      <c r="I80" s="46">
-        <v>46124</v>
-      </c>
-      <c r="J80" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3365,26 +3366,26 @@
         <v>0</v>
       </c>
       <c r="D81" s="55">
+        <v>3</v>
+      </c>
+      <c r="E81" s="55">
+        <v>8</v>
+      </c>
+      <c r="F81" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="G81" s="55"/>
+      <c r="H81" s="57">
+        <v>46124</v>
+      </c>
+      <c r="I81" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K81" s="55">
         <v>54</v>
-      </c>
-      <c r="E81" s="55">
-        <v>3</v>
-      </c>
-      <c r="F81" s="55">
-        <v>8</v>
-      </c>
-      <c r="G81" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="H81" s="55"/>
-      <c r="I81" s="57">
-        <v>46124</v>
-      </c>
-      <c r="J81" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3398,26 +3399,26 @@
         <v>0</v>
       </c>
       <c r="D82" s="55">
+        <v>1</v>
+      </c>
+      <c r="E82" s="55">
+        <v>10</v>
+      </c>
+      <c r="F82" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="55"/>
+      <c r="H82" s="57">
+        <v>46124</v>
+      </c>
+      <c r="I82" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K82" s="55">
         <v>30</v>
-      </c>
-      <c r="E82" s="55">
-        <v>1</v>
-      </c>
-      <c r="F82" s="55">
-        <v>10</v>
-      </c>
-      <c r="G82" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="H82" s="55"/>
-      <c r="I82" s="57">
-        <v>46124</v>
-      </c>
-      <c r="J82" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3431,26 +3432,26 @@
         <v>0</v>
       </c>
       <c r="D83" s="55">
+        <v>2</v>
+      </c>
+      <c r="E83" s="55">
+        <v>9</v>
+      </c>
+      <c r="F83" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="55"/>
+      <c r="H83" s="57">
+        <v>46124</v>
+      </c>
+      <c r="I83" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K83" s="55">
         <v>39</v>
-      </c>
-      <c r="E83" s="55">
-        <v>2</v>
-      </c>
-      <c r="F83" s="55">
-        <v>9</v>
-      </c>
-      <c r="G83" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="H83" s="55"/>
-      <c r="I83" s="57">
-        <v>46124</v>
-      </c>
-      <c r="J83" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3464,26 +3465,26 @@
         <v>24</v>
       </c>
       <c r="D84" s="60">
+        <v>3</v>
+      </c>
+      <c r="E84" s="60">
+        <v>8</v>
+      </c>
+      <c r="F84" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G84" s="60"/>
+      <c r="H84" s="58">
+        <v>46124</v>
+      </c>
+      <c r="I84" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="J84" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K84" s="60">
         <v>26</v>
-      </c>
-      <c r="E84" s="60">
-        <v>3</v>
-      </c>
-      <c r="F84" s="60">
-        <v>8</v>
-      </c>
-      <c r="G84" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="H84" s="60"/>
-      <c r="I84" s="58">
-        <v>46124</v>
-      </c>
-      <c r="J84" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K84" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3497,26 +3498,26 @@
         <v>30</v>
       </c>
       <c r="D85" s="60">
+        <v>1</v>
+      </c>
+      <c r="E85" s="60">
+        <v>10</v>
+      </c>
+      <c r="F85" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85" s="60"/>
+      <c r="H85" s="58">
+        <v>46124</v>
+      </c>
+      <c r="I85" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="J85" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K85" s="60">
         <v>16</v>
-      </c>
-      <c r="E85" s="60">
-        <v>1</v>
-      </c>
-      <c r="F85" s="60">
-        <v>10</v>
-      </c>
-      <c r="G85" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="H85" s="60"/>
-      <c r="I85" s="58">
-        <v>46124</v>
-      </c>
-      <c r="J85" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K85" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3530,26 +3531,26 @@
         <v>19</v>
       </c>
       <c r="D86" s="60">
+        <v>2</v>
+      </c>
+      <c r="E86" s="60">
+        <v>9</v>
+      </c>
+      <c r="F86" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G86" s="60"/>
+      <c r="H86" s="58">
+        <v>46124</v>
+      </c>
+      <c r="I86" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="J86" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K86" s="60">
         <v>24</v>
-      </c>
-      <c r="E86" s="60">
-        <v>2</v>
-      </c>
-      <c r="F86" s="60">
-        <v>9</v>
-      </c>
-      <c r="G86" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="H86" s="60"/>
-      <c r="I86" s="58">
-        <v>46124</v>
-      </c>
-      <c r="J86" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="K86" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:11" s="48" customFormat="1">
@@ -3563,26 +3564,26 @@
         <v>0</v>
       </c>
       <c r="D87" s="63">
+        <v>1</v>
+      </c>
+      <c r="E87" s="63">
+        <v>10</v>
+      </c>
+      <c r="F87" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="G87" s="63"/>
+      <c r="H87" s="64">
+        <v>46152</v>
+      </c>
+      <c r="I87" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="J87" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K87" s="63">
         <v>27</v>
-      </c>
-      <c r="E87" s="63">
-        <v>1</v>
-      </c>
-      <c r="F87" s="63">
-        <v>10</v>
-      </c>
-      <c r="G87" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="H87" s="63"/>
-      <c r="I87" s="64">
-        <v>46152</v>
-      </c>
-      <c r="J87" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="K87" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:11" s="48" customFormat="1">
@@ -3596,26 +3597,26 @@
         <v>0</v>
       </c>
       <c r="D88" s="63">
+        <v>2</v>
+      </c>
+      <c r="E88" s="63">
+        <v>9</v>
+      </c>
+      <c r="F88" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="G88" s="63"/>
+      <c r="H88" s="64">
+        <v>46152</v>
+      </c>
+      <c r="I88" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="J88" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K88" s="63">
         <v>32</v>
-      </c>
-      <c r="E88" s="63">
-        <v>2</v>
-      </c>
-      <c r="F88" s="63">
-        <v>9</v>
-      </c>
-      <c r="G88" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="H88" s="63"/>
-      <c r="I88" s="64">
-        <v>46152</v>
-      </c>
-      <c r="J88" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="K88" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="48" customFormat="1">
@@ -3629,26 +3630,26 @@
         <v>0</v>
       </c>
       <c r="D89" s="63">
+        <v>4</v>
+      </c>
+      <c r="E89" s="63">
+        <v>7</v>
+      </c>
+      <c r="F89" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="G89" s="63"/>
+      <c r="H89" s="64">
+        <v>46152</v>
+      </c>
+      <c r="I89" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="J89" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K89" s="63">
         <v>37</v>
-      </c>
-      <c r="E89" s="63">
-        <v>4</v>
-      </c>
-      <c r="F89" s="63">
-        <v>7</v>
-      </c>
-      <c r="G89" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="H89" s="63"/>
-      <c r="I89" s="64">
-        <v>46152</v>
-      </c>
-      <c r="J89" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="K89" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:11" s="48" customFormat="1">
@@ -3662,26 +3663,26 @@
         <v>13</v>
       </c>
       <c r="D90" s="53">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="53">
         <v>5</v>
       </c>
-      <c r="F90" s="53">
-        <v>5</v>
-      </c>
-      <c r="G90" s="53" t="s">
+      <c r="F90" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="H90" s="53"/>
-      <c r="I90" s="54">
+      <c r="G90" s="53"/>
+      <c r="H90" s="54">
         <v>46152</v>
       </c>
-      <c r="J90" s="53" t="s">
+      <c r="I90" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="K90" s="48" t="s">
-        <v>61</v>
+      <c r="J90" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K90" s="53">
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:11" s="48" customFormat="1">
@@ -3695,26 +3696,26 @@
         <v>25</v>
       </c>
       <c r="D91" s="53">
+        <v>1</v>
+      </c>
+      <c r="E91" s="53">
+        <v>10</v>
+      </c>
+      <c r="F91" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G91" s="53"/>
+      <c r="H91" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I91" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="J91" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K91" s="53">
         <v>19</v>
-      </c>
-      <c r="E91" s="53">
-        <v>1</v>
-      </c>
-      <c r="F91" s="53">
-        <v>10</v>
-      </c>
-      <c r="G91" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="H91" s="53"/>
-      <c r="I91" s="54">
-        <v>46152</v>
-      </c>
-      <c r="J91" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="K91" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="48" customFormat="1">
@@ -3728,26 +3729,26 @@
         <v>24</v>
       </c>
       <c r="D92" s="53">
+        <v>2</v>
+      </c>
+      <c r="E92" s="53">
+        <v>9</v>
+      </c>
+      <c r="F92" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" s="53"/>
+      <c r="H92" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I92" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="J92" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K92" s="53">
         <v>22</v>
-      </c>
-      <c r="E92" s="53">
-        <v>2</v>
-      </c>
-      <c r="F92" s="53">
-        <v>9</v>
-      </c>
-      <c r="G92" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="H92" s="53"/>
-      <c r="I92" s="54">
-        <v>46152</v>
-      </c>
-      <c r="J92" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="K92" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:11" s="48" customFormat="1">
@@ -3761,26 +3762,26 @@
         <v>14</v>
       </c>
       <c r="D93" s="53">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E93" s="53">
         <v>6</v>
       </c>
-      <c r="F93" s="53">
-        <v>6</v>
-      </c>
-      <c r="G93" s="53" t="s">
+      <c r="F93" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="H93" s="53"/>
-      <c r="I93" s="54">
+      <c r="G93" s="53"/>
+      <c r="H93" s="54">
         <v>46152</v>
       </c>
-      <c r="J93" s="53" t="s">
+      <c r="I93" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="K93" s="48" t="s">
-        <v>61</v>
+      <c r="J93" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K93" s="53">
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="48" customFormat="1">
@@ -3794,26 +3795,26 @@
         <v>24</v>
       </c>
       <c r="D94" s="53">
+        <v>2</v>
+      </c>
+      <c r="E94" s="53">
+        <v>9</v>
+      </c>
+      <c r="F94" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" s="53"/>
+      <c r="H94" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I94" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="J94" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K94" s="53">
         <v>22</v>
-      </c>
-      <c r="E94" s="53">
-        <v>2</v>
-      </c>
-      <c r="F94" s="53">
-        <v>9</v>
-      </c>
-      <c r="G94" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="H94" s="53"/>
-      <c r="I94" s="54">
-        <v>46152</v>
-      </c>
-      <c r="J94" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="K94" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:11" s="48" customFormat="1">
@@ -3827,26 +3828,26 @@
         <v>25</v>
       </c>
       <c r="D95" s="53">
+        <v>4</v>
+      </c>
+      <c r="E95" s="53">
+        <v>7</v>
+      </c>
+      <c r="F95" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G95" s="53"/>
+      <c r="H95" s="54">
+        <v>46152</v>
+      </c>
+      <c r="I95" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="J95" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K95" s="53">
         <v>24</v>
-      </c>
-      <c r="E95" s="53">
-        <v>4</v>
-      </c>
-      <c r="F95" s="53">
-        <v>7</v>
-      </c>
-      <c r="G95" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="H95" s="53"/>
-      <c r="I95" s="54">
-        <v>46152</v>
-      </c>
-      <c r="J95" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="K95" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:11" s="48" customFormat="1">
@@ -3860,26 +3861,26 @@
         <v>0</v>
       </c>
       <c r="D96" s="61">
+        <v>1</v>
+      </c>
+      <c r="E96" s="61">
+        <v>10</v>
+      </c>
+      <c r="F96" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G96" s="61"/>
+      <c r="H96" s="62">
+        <v>46152</v>
+      </c>
+      <c r="I96" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="J96" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K96" s="61">
         <v>46</v>
-      </c>
-      <c r="E96" s="61">
-        <v>1</v>
-      </c>
-      <c r="F96" s="61">
-        <v>10</v>
-      </c>
-      <c r="G96" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="H96" s="61"/>
-      <c r="I96" s="62">
-        <v>46152</v>
-      </c>
-      <c r="J96" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="K96" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:11" s="48" customFormat="1">
@@ -3893,26 +3894,26 @@
         <v>0</v>
       </c>
       <c r="D97" s="61">
+        <v>2</v>
+      </c>
+      <c r="E97" s="61">
+        <v>9</v>
+      </c>
+      <c r="F97" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G97" s="61"/>
+      <c r="H97" s="62">
+        <v>46152</v>
+      </c>
+      <c r="I97" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="J97" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K97" s="61">
         <v>48</v>
-      </c>
-      <c r="E97" s="61">
-        <v>2</v>
-      </c>
-      <c r="F97" s="61">
-        <v>9</v>
-      </c>
-      <c r="G97" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="H97" s="61"/>
-      <c r="I97" s="62">
-        <v>46152</v>
-      </c>
-      <c r="J97" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="K97" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -3926,26 +3927,26 @@
         <v>0</v>
       </c>
       <c r="D98" s="61">
+        <v>3</v>
+      </c>
+      <c r="E98" s="61">
+        <v>8</v>
+      </c>
+      <c r="F98" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G98" s="61"/>
+      <c r="H98" s="62">
+        <v>46152</v>
+      </c>
+      <c r="I98" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="J98" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K98" s="61">
         <v>53</v>
-      </c>
-      <c r="E98" s="61">
-        <v>3</v>
-      </c>
-      <c r="F98" s="61">
-        <v>8</v>
-      </c>
-      <c r="G98" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="H98" s="61"/>
-      <c r="I98" s="62">
-        <v>46152</v>
-      </c>
-      <c r="J98" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="K98" s="48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -3959,39 +3960,39 @@
         <v>0</v>
       </c>
       <c r="D99" s="61">
+        <v>4</v>
+      </c>
+      <c r="E99" s="61">
+        <v>7</v>
+      </c>
+      <c r="F99" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G99" s="61"/>
+      <c r="H99" s="62">
+        <v>46152</v>
+      </c>
+      <c r="I99" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="J99" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K99" s="61">
         <v>72</v>
       </c>
-      <c r="E99" s="61">
-        <v>4</v>
-      </c>
-      <c r="F99" s="61">
-        <v>7</v>
-      </c>
-      <c r="G99" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="H99" s="61"/>
-      <c r="I99" s="62">
-        <v>46152</v>
-      </c>
-      <c r="J99" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="K99" s="48" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="100" spans="1:11">
-      <c r="I100" s="1"/>
+      <c r="H100" s="1"/>
     </row>
     <row r="101" spans="1:11">
-      <c r="I101" s="1"/>
+      <c r="H101" s="1"/>
     </row>
     <row r="102" spans="1:11">
-      <c r="I102" s="1"/>
+      <c r="H102" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:I99"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>

--- a/data/leaguedata.xlsx
+++ b/data/leaguedata.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>May   Sixes (Beginners)</t>
+  </si>
+  <si>
+    <t>Competition</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1034,9 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
